--- a/passress-mis/PASSRESS_MIS.xlsx
+++ b/passress-mis/PASSRESS_MIS.xlsx
@@ -24,25 +24,27 @@
     <sheet name="15_Settings" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="RAW_Orders" sheetId="16" state="hidden" r:id="rId16"/>
     <sheet name="RAW_OrderLines" sheetId="17" state="hidden" r:id="rId17"/>
-    <sheet name="RAW_Refunds" sheetId="18" state="hidden" r:id="rId18"/>
-    <sheet name="RAW_Products" sheetId="19" state="hidden" r:id="rId19"/>
-    <sheet name="RAW_Variants" sheetId="20" state="hidden" r:id="rId20"/>
-    <sheet name="RAW_InventoryLevels" sheetId="21" state="hidden" r:id="rId21"/>
-    <sheet name="RAW_Customers" sheetId="22" state="hidden" r:id="rId22"/>
-    <sheet name="RAW_Collections" sheetId="23" state="hidden" r:id="rId23"/>
-    <sheet name="DIM_Date" sheetId="24" state="hidden" r:id="rId24"/>
-    <sheet name="DIM_Product" sheetId="25" state="hidden" r:id="rId25"/>
-    <sheet name="DIM_Customer" sheetId="26" state="hidden" r:id="rId26"/>
-    <sheet name="DIM_Location" sheetId="27" state="hidden" r:id="rId27"/>
-    <sheet name="DIM_Collection" sheetId="28" state="hidden" r:id="rId28"/>
-    <sheet name="DIM_Parameters" sheetId="29" state="hidden" r:id="rId29"/>
-    <sheet name="FACT_OrderLines" sheetId="30" state="hidden" r:id="rId30"/>
-    <sheet name="FACT_Refunds" sheetId="31" state="hidden" r:id="rId31"/>
-    <sheet name="FACT_InventoryMovements" sheetId="32" state="hidden" r:id="rId32"/>
-    <sheet name="FACT_Payments" sheetId="33" state="hidden" r:id="rId33"/>
-    <sheet name="FACT_ManualExpenses" sheetId="34" state="hidden" r:id="rId34"/>
-    <sheet name="LOG_RefreshHistory" sheetId="35" state="hidden" r:id="rId35"/>
-    <sheet name="LOG_DataQuality" sheetId="36" state="hidden" r:id="rId36"/>
+    <sheet name="RAW_Transactions" sheetId="18" state="hidden" r:id="rId18"/>
+    <sheet name="RAW_Refunds" sheetId="19" state="hidden" r:id="rId19"/>
+    <sheet name="RAW_Products" sheetId="20" state="hidden" r:id="rId20"/>
+    <sheet name="RAW_Variants" sheetId="21" state="hidden" r:id="rId21"/>
+    <sheet name="RAW_InventoryLevels" sheetId="22" state="hidden" r:id="rId22"/>
+    <sheet name="RAW_Customers" sheetId="23" state="hidden" r:id="rId23"/>
+    <sheet name="RAW_Collections" sheetId="24" state="hidden" r:id="rId24"/>
+    <sheet name="RAW_Discounts" sheetId="25" state="hidden" r:id="rId25"/>
+    <sheet name="DIM_Date" sheetId="26" state="hidden" r:id="rId26"/>
+    <sheet name="DIM_Product" sheetId="27" state="hidden" r:id="rId27"/>
+    <sheet name="DIM_Customer" sheetId="28" state="hidden" r:id="rId28"/>
+    <sheet name="DIM_Location" sheetId="29" state="hidden" r:id="rId29"/>
+    <sheet name="DIM_Collection" sheetId="30" state="hidden" r:id="rId30"/>
+    <sheet name="DIM_Parameters" sheetId="31" state="hidden" r:id="rId31"/>
+    <sheet name="FACT_OrderLines" sheetId="32" state="hidden" r:id="rId32"/>
+    <sheet name="FACT_Refunds" sheetId="33" state="hidden" r:id="rId33"/>
+    <sheet name="FACT_InventoryMovements" sheetId="34" state="hidden" r:id="rId34"/>
+    <sheet name="FACT_Payments" sheetId="35" state="hidden" r:id="rId35"/>
+    <sheet name="FACT_ManualExpenses" sheetId="36" state="hidden" r:id="rId36"/>
+    <sheet name="LOG_RefreshHistory" sheetId="37" state="hidden" r:id="rId37"/>
+    <sheet name="LOG_DataQuality" sheetId="38" state="hidden" r:id="rId38"/>
   </sheets>
   <definedNames>
     <definedName name="SetCompanyName">'15_Settings'!$C$13</definedName>
@@ -54,6 +56,8 @@
     <definedName name="SetShopifyStoreDomain">'15_Settings'!$C$23</definedName>
     <definedName name="SetShopifyAPIVersion">'15_Settings'!$C$24</definedName>
     <definedName name="SetLookbackDaysIncrementalRefresh">'15_Settings'!$C$25</definedName>
+    <definedName name="SetHistoricalBackfillStartDate">'15_Settings'!$C$26</definedName>
+    <definedName name="SetMaxPagesPerRefreshSafetyCap">'15_Settings'!$C$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -116,6 +120,12 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
       <color rgb="00595959"/>
       <sz val="10"/>
     </font>
@@ -157,12 +167,6 @@
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00C55A11"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <i val="1"/>
-      <color rgb="007F7F7F"/>
       <sz val="9"/>
     </font>
     <font>
@@ -299,8 +303,11 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -308,28 +315,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -448,41 +454,64 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="tbl_RAW_Refunds" displayName="tbl_RAW_Refunds" ref="B11:H12" headerRowCount="1">
-  <autoFilter ref="B11:H12"/>
-  <tableColumns count="7">
-    <tableColumn id="2" name="RefundID"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="tbl_RAW_Transactions" displayName="tbl_RAW_Transactions" ref="B11:K12" headerRowCount="1">
+  <autoFilter ref="B11:K12"/>
+  <tableColumns count="10">
+    <tableColumn id="2" name="TransactionID"/>
     <tableColumn id="3" name="OrderID"/>
-    <tableColumn id="4" name="LineItemID"/>
-    <tableColumn id="5" name="Quantity"/>
-    <tableColumn id="6" name="RefundAmount"/>
-    <tableColumn id="7" name="RefundedAt"/>
-    <tableColumn id="8" name="Reason"/>
+    <tableColumn id="4" name="Kind"/>
+    <tableColumn id="5" name="Status"/>
+    <tableColumn id="6" name="Gateway"/>
+    <tableColumn id="7" name="AmountShop"/>
+    <tableColumn id="8" name="CurrencyShop"/>
+    <tableColumn id="9" name="CreatedAt"/>
+    <tableColumn id="10" name="ProcessedAt"/>
+    <tableColumn id="11" name="Test"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="tbl_RAW_Products" displayName="tbl_RAW_Products" ref="B11:H12" headerRowCount="1">
-  <autoFilter ref="B11:H12"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="tbl_RAW_Refunds" displayName="tbl_RAW_Refunds" ref="B11:K12" headerRowCount="1">
+  <autoFilter ref="B11:K12"/>
+  <tableColumns count="10">
+    <tableColumn id="2" name="RefundLineItemID"/>
+    <tableColumn id="3" name="RefundID"/>
+    <tableColumn id="4" name="OrderID"/>
+    <tableColumn id="5" name="LineItemID"/>
+    <tableColumn id="6" name="Quantity"/>
+    <tableColumn id="7" name="SubtotalAmount"/>
+    <tableColumn id="8" name="TaxAmount"/>
+    <tableColumn id="9" name="RefundCreatedAt"/>
+    <tableColumn id="10" name="RefundProcessedAt"/>
+    <tableColumn id="11" name="Note"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tbl_RAW_Products" displayName="tbl_RAW_Products" ref="B11:I12" headerRowCount="1">
+  <autoFilter ref="B11:I12"/>
+  <tableColumns count="8">
     <tableColumn id="2" name="ProductID"/>
     <tableColumn id="3" name="Title"/>
     <tableColumn id="4" name="ProductType"/>
     <tableColumn id="5" name="Vendor"/>
     <tableColumn id="6" name="CollectionIDs"/>
     <tableColumn id="7" name="CreatedAt"/>
-    <tableColumn id="8" name="Status"/>
+    <tableColumn id="8" name="UpdatedAt"/>
+    <tableColumn id="9" name="Status"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tbl_RAW_Variants" displayName="tbl_RAW_Variants" ref="B11:I12" headerRowCount="1">
-  <autoFilter ref="B11:I12"/>
-  <tableColumns count="8">
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="tbl_RAW_Variants" displayName="tbl_RAW_Variants" ref="B11:K12" headerRowCount="1">
+  <autoFilter ref="B11:K12"/>
+  <tableColumns count="10">
     <tableColumn id="2" name="VariantID"/>
     <tableColumn id="3" name="ProductID"/>
     <tableColumn id="4" name="SKU"/>
@@ -491,43 +520,47 @@
     <tableColumn id="7" name="CompareAtPrice"/>
     <tableColumn id="8" name="InventoryItemID"/>
     <tableColumn id="9" name="UnitCost"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="tbl_RAW_InventoryLevels" displayName="tbl_RAW_InventoryLevels" ref="B11:E12" headerRowCount="1">
-  <autoFilter ref="B11:E12"/>
-  <tableColumns count="4">
-    <tableColumn id="2" name="InventoryItemID"/>
-    <tableColumn id="3" name="LocationID"/>
-    <tableColumn id="4" name="Available"/>
-    <tableColumn id="5" name="UpdatedAt"/>
+    <tableColumn id="10" name="CreatedAt"/>
+    <tableColumn id="11" name="UpdatedAt"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="tbl_RAW_Customers" displayName="tbl_RAW_Customers" ref="B11:I12" headerRowCount="1">
-  <autoFilter ref="B11:I12"/>
-  <tableColumns count="8">
-    <tableColumn id="2" name="CustomerID"/>
-    <tableColumn id="3" name="FirstName"/>
-    <tableColumn id="4" name="LastName"/>
-    <tableColumn id="5" name="Email"/>
-    <tableColumn id="6" name="CreatedAt"/>
-    <tableColumn id="7" name="OrdersCount"/>
-    <tableColumn id="8" name="TotalSpent"/>
-    <tableColumn id="9" name="DefaultAddressCountry"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="tbl_RAW_InventoryLevels" displayName="tbl_RAW_InventoryLevels" ref="B11:F12" headerRowCount="1">
+  <autoFilter ref="B11:F12"/>
+  <tableColumns count="5">
+    <tableColumn id="2" name="InventoryItemID"/>
+    <tableColumn id="3" name="SKU"/>
+    <tableColumn id="4" name="LocationID"/>
+    <tableColumn id="5" name="Available"/>
+    <tableColumn id="6" name="UpdatedAt"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="tbl_RAW_Collections" displayName="tbl_RAW_Collections" ref="B11:D12" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="tbl_RAW_Customers" displayName="tbl_RAW_Customers" ref="B11:J12" headerRowCount="1">
+  <autoFilter ref="B11:J12"/>
+  <tableColumns count="9">
+    <tableColumn id="2" name="CustomerID"/>
+    <tableColumn id="3" name="FirstName"/>
+    <tableColumn id="4" name="LastName"/>
+    <tableColumn id="5" name="Email"/>
+    <tableColumn id="6" name="CreatedAt"/>
+    <tableColumn id="7" name="UpdatedAt"/>
+    <tableColumn id="8" name="OrdersCount"/>
+    <tableColumn id="9" name="TotalSpent"/>
+    <tableColumn id="10" name="DefaultAddressCountry"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="tbl_RAW_Collections" displayName="tbl_RAW_Collections" ref="B11:D12" headerRowCount="1">
   <autoFilter ref="B11:D12"/>
   <tableColumns count="3">
     <tableColumn id="2" name="CollectionID"/>
@@ -538,8 +571,29 @@
 </table>
 </file>
 
-<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="tbl_DIM_Date" displayName="tbl_DIM_Date" ref="B11:L12" headerRowCount="1">
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="tbl_RAW_Discounts" displayName="tbl_RAW_Discounts" ref="B11:M12" headerRowCount="1">
+  <autoFilter ref="B11:M12"/>
+  <tableColumns count="12">
+    <tableColumn id="2" name="DiscountNodeID"/>
+    <tableColumn id="3" name="Typename"/>
+    <tableColumn id="4" name="Title"/>
+    <tableColumn id="5" name="Status"/>
+    <tableColumn id="6" name="Summary"/>
+    <tableColumn id="7" name="Code"/>
+    <tableColumn id="8" name="StartsAt"/>
+    <tableColumn id="9" name="EndsAt"/>
+    <tableColumn id="10" name="UsageLimit"/>
+    <tableColumn id="11" name="AsyncUsageCount"/>
+    <tableColumn id="12" name="CreatedAt"/>
+    <tableColumn id="13" name="UpdatedAt"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tbl_DIM_Date" displayName="tbl_DIM_Date" ref="B11:L12" headerRowCount="1">
   <autoFilter ref="B11:L12"/>
   <tableColumns count="11">
     <tableColumn id="2" name="DateKey"/>
@@ -553,40 +607,6 @@
     <tableColumn id="10" name="Day"/>
     <tableColumn id="11" name="DayName"/>
     <tableColumn id="12" name="IsWeekend"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="tbl_DIM_Product" displayName="tbl_DIM_Product" ref="B11:J12" headerRowCount="1">
-  <autoFilter ref="B11:J12"/>
-  <tableColumns count="9">
-    <tableColumn id="2" name="ProductKey"/>
-    <tableColumn id="3" name="ProductID"/>
-    <tableColumn id="4" name="SKU"/>
-    <tableColumn id="5" name="Title"/>
-    <tableColumn id="6" name="ProductType"/>
-    <tableColumn id="7" name="Vendor"/>
-    <tableColumn id="8" name="Collection"/>
-    <tableColumn id="9" name="UnitCost"/>
-    <tableColumn id="10" name="Status"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tbl_DIM_Customer" displayName="tbl_DIM_Customer" ref="B11:H12" headerRowCount="1">
-  <autoFilter ref="B11:H12"/>
-  <tableColumns count="7">
-    <tableColumn id="2" name="CustomerKey"/>
-    <tableColumn id="3" name="CustomerID"/>
-    <tableColumn id="4" name="Name"/>
-    <tableColumn id="5" name="Email"/>
-    <tableColumn id="6" name="Country"/>
-    <tableColumn id="7" name="FirstOrderDate"/>
-    <tableColumn id="8" name="CustomerSegment"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -607,7 +627,41 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="tbl_DIM_Location" displayName="tbl_DIM_Location" ref="B11:F12" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="tbl_DIM_Product" displayName="tbl_DIM_Product" ref="B11:J12" headerRowCount="1">
+  <autoFilter ref="B11:J12"/>
+  <tableColumns count="9">
+    <tableColumn id="2" name="ProductKey"/>
+    <tableColumn id="3" name="ProductID"/>
+    <tableColumn id="4" name="SKU"/>
+    <tableColumn id="5" name="Title"/>
+    <tableColumn id="6" name="ProductType"/>
+    <tableColumn id="7" name="Vendor"/>
+    <tableColumn id="8" name="Collection"/>
+    <tableColumn id="9" name="UnitCost"/>
+    <tableColumn id="10" name="Status"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="tbl_DIM_Customer" displayName="tbl_DIM_Customer" ref="B11:H12" headerRowCount="1">
+  <autoFilter ref="B11:H12"/>
+  <tableColumns count="7">
+    <tableColumn id="2" name="CustomerKey"/>
+    <tableColumn id="3" name="CustomerID"/>
+    <tableColumn id="4" name="Name"/>
+    <tableColumn id="5" name="Email"/>
+    <tableColumn id="6" name="Country"/>
+    <tableColumn id="7" name="FirstOrderDate"/>
+    <tableColumn id="8" name="CustomerSegment"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="tbl_DIM_Location" displayName="tbl_DIM_Location" ref="B11:F12" headerRowCount="1">
   <autoFilter ref="B11:F12"/>
   <tableColumns count="5">
     <tableColumn id="2" name="LocationKey"/>
@@ -620,8 +674,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="tbl_DIM_Collection" displayName="tbl_DIM_Collection" ref="B11:E12" headerRowCount="1">
+<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="tbl_DIM_Collection" displayName="tbl_DIM_Collection" ref="B11:E12" headerRowCount="1">
   <autoFilter ref="B11:E12"/>
   <tableColumns count="4">
     <tableColumn id="2" name="CollectionKey"/>
@@ -633,8 +687,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="tbl_DIM_Parameters" displayName="tbl_DIM_Parameters" ref="B11:C12" headerRowCount="1">
+<file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="tbl_DIM_Parameters" displayName="tbl_DIM_Parameters" ref="B11:C12" headerRowCount="1">
   <autoFilter ref="B11:C12"/>
   <tableColumns count="2">
     <tableColumn id="2" name="ParameterName"/>
@@ -644,8 +698,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="tbl_FACT_OrderLines" displayName="tbl_FACT_OrderLines" ref="B11:O12" headerRowCount="1">
+<file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="tbl_FACT_OrderLines" displayName="tbl_FACT_OrderLines" ref="B11:O12" headerRowCount="1">
   <autoFilter ref="B11:O12"/>
   <tableColumns count="14">
     <tableColumn id="2" name="OrderLineKey"/>
@@ -667,8 +721,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="tbl_FACT_Refunds" displayName="tbl_FACT_Refunds" ref="B11:F12" headerRowCount="1">
+<file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="tbl_FACT_Refunds" displayName="tbl_FACT_Refunds" ref="B11:F12" headerRowCount="1">
   <autoFilter ref="B11:F12"/>
   <tableColumns count="5">
     <tableColumn id="2" name="RefundKey"/>
@@ -681,8 +735,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="tbl_FACT_InventoryMovements" displayName="tbl_FACT_InventoryMovements" ref="B11:H12" headerRowCount="1">
+<file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="tbl_FACT_InventoryMovements" displayName="tbl_FACT_InventoryMovements" ref="B11:H12" headerRowCount="1">
   <autoFilter ref="B11:H12"/>
   <tableColumns count="7">
     <tableColumn id="2" name="MovementKey"/>
@@ -697,8 +751,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="tbl_FACT_Payments" displayName="tbl_FACT_Payments" ref="B11:H12" headerRowCount="1">
+<file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="tbl_FACT_Payments" displayName="tbl_FACT_Payments" ref="B11:H12" headerRowCount="1">
   <autoFilter ref="B11:H12"/>
   <tableColumns count="7">
     <tableColumn id="2" name="PaymentKey"/>
@@ -713,8 +767,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="tbl_FACT_ManualExpenses" displayName="tbl_FACT_ManualExpenses" ref="B11:I12" headerRowCount="1">
+<file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="29" name="tbl_FACT_ManualExpenses" displayName="tbl_FACT_ManualExpenses" ref="B11:I12" headerRowCount="1">
   <autoFilter ref="B11:I12"/>
   <tableColumns count="8">
     <tableColumn id="2" name="ExpenseKey"/>
@@ -730,8 +784,23 @@
 </table>
 </file>
 
-<file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="tbl_LOG_RefreshHistory" displayName="tbl_LOG_RefreshHistory" ref="B11:I12" headerRowCount="1">
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tbl_SupplierMaster" displayName="tbl_SupplierMaster" ref="B17:G18" headerRowCount="1">
+  <autoFilter ref="B17:G18"/>
+  <tableColumns count="6">
+    <tableColumn id="2" name="Supplier ID"/>
+    <tableColumn id="3" name="Supplier Name"/>
+    <tableColumn id="4" name="Contact"/>
+    <tableColumn id="5" name="Category"/>
+    <tableColumn id="6" name="Lead Time (Days)"/>
+    <tableColumn id="7" name="Status"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="30" name="tbl_LOG_RefreshHistory" displayName="tbl_LOG_RefreshHistory" ref="B11:I12" headerRowCount="1">
   <autoFilter ref="B11:I12"/>
   <tableColumns count="8">
     <tableColumn id="2" name="RefreshID"/>
@@ -747,8 +816,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="29" name="tbl_LOG_DataQuality" displayName="tbl_LOG_DataQuality" ref="B11:G12" headerRowCount="1">
+<file path=xl/tables/table31.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="31" name="tbl_LOG_DataQuality" displayName="tbl_LOG_DataQuality" ref="B11:G12" headerRowCount="1">
   <autoFilter ref="B11:G12"/>
   <tableColumns count="6">
     <tableColumn id="2" name="CheckID"/>
@@ -757,21 +826,6 @@
     <tableColumn id="5" name="TableName"/>
     <tableColumn id="6" name="Status"/>
     <tableColumn id="7" name="Details"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tbl_SupplierMaster" displayName="tbl_SupplierMaster" ref="B17:G18" headerRowCount="1">
-  <autoFilter ref="B17:G18"/>
-  <tableColumns count="6">
-    <tableColumn id="2" name="Supplier ID"/>
-    <tableColumn id="3" name="Supplier Name"/>
-    <tableColumn id="4" name="Contact"/>
-    <tableColumn id="5" name="Category"/>
-    <tableColumn id="6" name="Lead Time (Days)"/>
-    <tableColumn id="7" name="Status"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -819,8 +873,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tbl_ChartOfAccounts" displayName="tbl_ChartOfAccounts" ref="B29:F30" headerRowCount="1">
-  <autoFilter ref="B29:F30"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tbl_ChartOfAccounts" displayName="tbl_ChartOfAccounts" ref="B31:F32" headerRowCount="1">
+  <autoFilter ref="B31:F32"/>
   <tableColumns count="5">
     <tableColumn id="2" name="Account Code"/>
     <tableColumn id="3" name="Account Name"/>
@@ -833,8 +887,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tbl_VersionLog" displayName="tbl_VersionLog" ref="B34:E35" headerRowCount="1">
-  <autoFilter ref="B34:E35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tbl_VersionLog" displayName="tbl_VersionLog" ref="B36:E39" headerRowCount="1">
+  <autoFilter ref="B36:E39"/>
   <tableColumns count="4">
     <tableColumn id="2" name="Version"/>
     <tableColumn id="3" name="Date"/>
@@ -1296,16 +1350,14 @@
         </is>
       </c>
       <c r="E12" s="7" t="n"/>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F12" s="8">
+        <f>INDEX(tbl_VersionLog[Version],COUNTA(tbl_VersionLog[Version]))</f>
+        <v/>
       </c>
       <c r="G12" s="7" t="n"/>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H12" s="9">
+        <f>INDEX(tbl_VersionLog[Phase],COUNTA(tbl_VersionLog[Phase]))</f>
+        <v/>
       </c>
       <c r="I12" s="7" t="n"/>
     </row>
@@ -1320,35 +1372,35 @@
       <c r="I13" s="7" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>NAVIGATION</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>02
 Partner Dashboard</t>
         </is>
       </c>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>03
 CEO Dashboard</t>
         </is>
       </c>
       <c r="E16" s="7" t="n"/>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>04
 Sales</t>
         </is>
       </c>
       <c r="G16" s="7" t="n"/>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H16" s="11" t="inlineStr">
         <is>
           <t>05
 Products</t>
@@ -1367,28 +1419,28 @@
       <c r="I17" s="7" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>06
 Customers</t>
         </is>
       </c>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>07
 Inventory</t>
         </is>
       </c>
       <c r="E19" s="7" t="n"/>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>08
 Finance</t>
         </is>
       </c>
       <c r="G19" s="7" t="n"/>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H19" s="11" t="inlineStr">
         <is>
           <t>09
 Profitability</t>
@@ -1407,28 +1459,28 @@
       <c r="I20" s="7" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>10
 Expenses</t>
         </is>
       </c>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>11
 Capital</t>
         </is>
       </c>
       <c r="E22" s="7" t="n"/>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>12
 Suppliers</t>
         </is>
       </c>
       <c r="G22" s="7" t="n"/>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>13
 Marketing</t>
@@ -1447,14 +1499,14 @@
       <c r="I23" s="7" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>14
 Data Quality</t>
         </is>
       </c>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>15
 Settings</t>
@@ -1469,7 +1521,7 @@
       <c r="E26" s="7" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Phase 1 build — structure only. No live Shopify data, no calculations, no DAX measures yet. See 15_Settings for workbook version and roadmap.</t>
         </is>
@@ -1695,79 +1747,79 @@
       <c r="I13" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>MANUAL EXPENSE ENTRY  (green cells = type here)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>Cost Center</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>Amount (EGP)</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="15" t="inlineStr">
         <is>
           <t>Payment Method</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="H17" s="15" t="inlineStr">
         <is>
           <t>Entered By</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>Rent</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Head Office</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>EXAMPLE — January office rent</t>
         </is>
       </c>
-      <c r="F18" s="15" t="n">
+      <c r="F18" s="16" t="n">
         <v>15000</v>
       </c>
-      <c r="G18" s="15" t="inlineStr">
+      <c r="G18" s="16" t="inlineStr">
         <is>
           <t>Bank Transfer</t>
         </is>
       </c>
-      <c r="H18" s="15" t="inlineStr">
+      <c r="H18" s="16" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
@@ -1964,59 +2016,59 @@
       <c r="I13" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>CAPITAL TRANSACTIONS  (green cells = type here)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>Type (Contribution/Withdrawal)</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>Amount (EGP)</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>Entered By</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>Contribution</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>EXAMPLE — founder capital injection</t>
         </is>
       </c>
-      <c r="E18" s="15" t="n">
+      <c r="E18" s="16" t="n">
         <v>50000</v>
       </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
@@ -2214,138 +2266,138 @@
       <c r="I13" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>SUPPLIER MASTER  (green cells = type here)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>Supplier ID</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>Supplier Name</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>Lead Time (Days)</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="15" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>SUP-001</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>EXAMPLE — ABC Textiles</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>contact@example.com</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>Fabric</t>
         </is>
       </c>
-      <c r="F18" s="15" t="n">
+      <c r="F18" s="16" t="n">
         <v>14</v>
       </c>
-      <c r="G18" s="15" t="inlineStr">
+      <c r="G18" s="16" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>PURCHASE ORDER LOG  (green cells = type here)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>PO Number</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>Supplier ID</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>Amount (EGP)</t>
         </is>
       </c>
-      <c r="F22" s="14" t="inlineStr">
+      <c r="F22" s="15" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G22" s="14" t="inlineStr">
+      <c r="G22" s="15" t="inlineStr">
         <is>
           <t>Expected Delivery</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>PO-2026-001</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>SUP-001</t>
         </is>
       </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>2026-01-10</t>
         </is>
       </c>
-      <c r="E23" s="15" t="n">
+      <c r="E23" s="16" t="n">
         <v>20000</v>
       </c>
-      <c r="F23" s="15" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>Ordered</t>
         </is>
       </c>
-      <c r="G23" s="15" t="inlineStr">
+      <c r="G23" s="16" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
@@ -2549,246 +2601,246 @@
       <c r="I13" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>TRENDS &amp; BREAKDOWNS</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>[ Discount Trend (Chart)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="13" t="n"/>
-      <c r="H17" s="13" t="n"/>
-      <c r="I17" s="13" t="n"/>
-      <c r="J17" s="13" t="n"/>
-      <c r="K17" s="13" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="14" t="n"/>
+      <c r="I17" s="14" t="n"/>
+      <c r="J17" s="14" t="n"/>
+      <c r="K17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="13" t="n"/>
-      <c r="H18" s="13" t="n"/>
-      <c r="I18" s="13" t="n"/>
-      <c r="J18" s="13" t="n"/>
-      <c r="K18" s="13" t="n"/>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="14" t="n"/>
+      <c r="I18" s="14" t="n"/>
+      <c r="J18" s="14" t="n"/>
+      <c r="K18" s="14" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="13" t="n"/>
-      <c r="H19" s="13" t="n"/>
-      <c r="I19" s="13" t="n"/>
-      <c r="J19" s="13" t="n"/>
-      <c r="K19" s="13" t="n"/>
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="14" t="n"/>
+      <c r="E19" s="14" t="n"/>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="14" t="n"/>
+      <c r="H19" s="14" t="n"/>
+      <c r="I19" s="14" t="n"/>
+      <c r="J19" s="14" t="n"/>
+      <c r="K19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="13" t="n"/>
-      <c r="H20" s="13" t="n"/>
-      <c r="I20" s="13" t="n"/>
-      <c r="J20" s="13" t="n"/>
-      <c r="K20" s="13" t="n"/>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="14" t="n"/>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="14" t="n"/>
+      <c r="H20" s="14" t="n"/>
+      <c r="I20" s="14" t="n"/>
+      <c r="J20" s="14" t="n"/>
+      <c r="K20" s="14" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="13" t="n"/>
-      <c r="H21" s="13" t="n"/>
-      <c r="I21" s="13" t="n"/>
-      <c r="J21" s="13" t="n"/>
-      <c r="K21" s="13" t="n"/>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="14" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="14" t="n"/>
+      <c r="H21" s="14" t="n"/>
+      <c r="I21" s="14" t="n"/>
+      <c r="J21" s="14" t="n"/>
+      <c r="K21" s="14" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="13" t="n"/>
-      <c r="H22" s="13" t="n"/>
-      <c r="I22" s="13" t="n"/>
-      <c r="J22" s="13" t="n"/>
-      <c r="K22" s="13" t="n"/>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="14" t="n"/>
+      <c r="I22" s="14" t="n"/>
+      <c r="J22" s="14" t="n"/>
+      <c r="K22" s="14" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="13" t="n"/>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="13" t="n"/>
-      <c r="J23" s="13" t="n"/>
-      <c r="K23" s="13" t="n"/>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="14" t="n"/>
+      <c r="I23" s="14" t="n"/>
+      <c r="J23" s="14" t="n"/>
+      <c r="K23" s="14" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="13" t="n"/>
-      <c r="H24" s="13" t="n"/>
-      <c r="I24" s="13" t="n"/>
-      <c r="J24" s="13" t="n"/>
-      <c r="K24" s="13" t="n"/>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="14" t="n"/>
+      <c r="I24" s="14" t="n"/>
+      <c r="J24" s="14" t="n"/>
+      <c r="K24" s="14" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>DETAIL (PIVOTTABLES)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>[ Campaign Performance (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="C28" s="13" t="n"/>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="13" t="inlineStr">
         <is>
           <t>[ Discount Code Usage (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="H28" s="13" t="n"/>
-      <c r="I28" s="13" t="n"/>
-      <c r="J28" s="13" t="n"/>
-      <c r="K28" s="13" t="n"/>
+      <c r="H28" s="14" t="n"/>
+      <c r="I28" s="14" t="n"/>
+      <c r="J28" s="14" t="n"/>
+      <c r="K28" s="14" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="13" t="n"/>
-      <c r="H29" s="13" t="n"/>
-      <c r="I29" s="13" t="n"/>
-      <c r="J29" s="13" t="n"/>
-      <c r="K29" s="13" t="n"/>
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="14" t="n"/>
+      <c r="H29" s="14" t="n"/>
+      <c r="I29" s="14" t="n"/>
+      <c r="J29" s="14" t="n"/>
+      <c r="K29" s="14" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="13" t="n"/>
-      <c r="H30" s="13" t="n"/>
-      <c r="I30" s="13" t="n"/>
-      <c r="J30" s="13" t="n"/>
-      <c r="K30" s="13" t="n"/>
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="14" t="n"/>
+      <c r="I30" s="14" t="n"/>
+      <c r="J30" s="14" t="n"/>
+      <c r="K30" s="14" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="13" t="n"/>
-      <c r="C31" s="13" t="n"/>
-      <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
-      <c r="G31" s="13" t="n"/>
-      <c r="H31" s="13" t="n"/>
-      <c r="I31" s="13" t="n"/>
-      <c r="J31" s="13" t="n"/>
-      <c r="K31" s="13" t="n"/>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="14" t="n"/>
+      <c r="I31" s="14" t="n"/>
+      <c r="J31" s="14" t="n"/>
+      <c r="K31" s="14" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="13" t="n"/>
-      <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="13" t="n"/>
-      <c r="H32" s="13" t="n"/>
-      <c r="I32" s="13" t="n"/>
-      <c r="J32" s="13" t="n"/>
-      <c r="K32" s="13" t="n"/>
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="14" t="n"/>
+      <c r="H32" s="14" t="n"/>
+      <c r="I32" s="14" t="n"/>
+      <c r="J32" s="14" t="n"/>
+      <c r="K32" s="14" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="13" t="n"/>
-      <c r="H33" s="13" t="n"/>
-      <c r="I33" s="13" t="n"/>
-      <c r="J33" s="13" t="n"/>
-      <c r="K33" s="13" t="n"/>
+      <c r="B33" s="14" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="14" t="n"/>
+      <c r="E33" s="14" t="n"/>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="14" t="n"/>
+      <c r="H33" s="14" t="n"/>
+      <c r="I33" s="14" t="n"/>
+      <c r="J33" s="14" t="n"/>
+      <c r="K33" s="14" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="13" t="n"/>
-      <c r="C34" s="13" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="13" t="n"/>
-      <c r="H34" s="13" t="n"/>
-      <c r="I34" s="13" t="n"/>
-      <c r="J34" s="13" t="n"/>
-      <c r="K34" s="13" t="n"/>
+      <c r="B34" s="14" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="14" t="n"/>
+      <c r="E34" s="14" t="n"/>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="14" t="n"/>
+      <c r="H34" s="14" t="n"/>
+      <c r="I34" s="14" t="n"/>
+      <c r="J34" s="14" t="n"/>
+      <c r="K34" s="14" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="13" t="n"/>
-      <c r="C35" s="13" t="n"/>
-      <c r="D35" s="13" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="13" t="n"/>
-      <c r="H35" s="13" t="n"/>
-      <c r="I35" s="13" t="n"/>
-      <c r="J35" s="13" t="n"/>
-      <c r="K35" s="13" t="n"/>
+      <c r="B35" s="14" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="14" t="n"/>
+      <c r="F35" s="14" t="n"/>
+      <c r="G35" s="14" t="n"/>
+      <c r="H35" s="14" t="n"/>
+      <c r="I35" s="14" t="n"/>
+      <c r="J35" s="14" t="n"/>
+      <c r="K35" s="14" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="13" t="n"/>
-      <c r="D36" s="13" t="n"/>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="13" t="n"/>
-      <c r="H36" s="13" t="n"/>
-      <c r="I36" s="13" t="n"/>
-      <c r="J36" s="13" t="n"/>
-      <c r="K36" s="13" t="n"/>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="14" t="n"/>
+      <c r="F36" s="14" t="n"/>
+      <c r="G36" s="14" t="n"/>
+      <c r="H36" s="14" t="n"/>
+      <c r="I36" s="14" t="n"/>
+      <c r="J36" s="14" t="n"/>
+      <c r="K36" s="14" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="13" t="n"/>
-      <c r="C37" s="13" t="n"/>
-      <c r="D37" s="13" t="n"/>
-      <c r="E37" s="13" t="n"/>
-      <c r="F37" s="13" t="n"/>
-      <c r="G37" s="13" t="n"/>
-      <c r="H37" s="13" t="n"/>
-      <c r="I37" s="13" t="n"/>
-      <c r="J37" s="13" t="n"/>
-      <c r="K37" s="13" t="n"/>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="14" t="n"/>
+      <c r="G37" s="14" t="n"/>
+      <c r="H37" s="14" t="n"/>
+      <c r="I37" s="14" t="n"/>
+      <c r="J37" s="14" t="n"/>
+      <c r="K37" s="14" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -2980,90 +3032,90 @@
       <c r="I13" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>VALIDATION RULES  (orange cells = configurable)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Rule ID</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>Check Name</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>Applies To</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>Threshold</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>DQ-001</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>No orders older than lookback window missing</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D18" s="18" t="inlineStr">
         <is>
           <t>RAW_Orders</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>0 gaps</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>REFRESH STATUS SUMMARY  (calculated — Phase 2)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>Table</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>Last Refreshed</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>Row Count</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="E22" s="19" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="19" t="n"/>
-      <c r="C23" s="19" t="n"/>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="19" t="n"/>
+      <c r="B23" s="20" t="n"/>
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="20" t="n"/>
+      <c r="E23" s="20" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -3100,7 +3152,7 @@
     <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3193,315 +3245,393 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11">
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>GENERAL SETTINGS  (orange cells = configurable)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>Company Name</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>Passress</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="24" t="inlineStr">
         <is>
           <t>Legal/trading name shown across dashboards.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>Base Currency</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>Currency all imported Shopify data is stored in.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>Reporting Currency</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="24" t="inlineStr">
         <is>
           <t>Currency used for dashboard display. Phase 1: same as base.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>Fiscal Year Start Month</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>January</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>First month of fiscal year, used for YTD/FY calculations.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>Default VAT Rate</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>Egypt standard VAT — used for tax reconciliation.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>Target Gross Margin %</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>Benchmark used for profitability flags (Phase 3).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>SHOPIFY CONNECTION SETTINGS  (placeholders — wired live in Phase 2)</t>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>SHOPIFY CONNECTION SETTINGS  (fill in Store Domain to go live; token is never stored here)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>Shopify Store Domain</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>your-store.myshopify.com</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
-        <is>
-          <t>Set when connecting Power Query in Phase 2. No token is ever stored in this workbook.</t>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>Set this to your real *.myshopify.com domain to go live. The access token itself is never stored in this workbook — see power-query/README.md.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>Shopify API Version</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="24" t="inlineStr">
         <is>
           <t>Admin GraphQL API version pinned for Power Query — reviewed twice a year.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>Lookback Days (Incremental Refresh)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D25" s="23" t="inlineStr">
-        <is>
-          <t>Days of history re-pulled on each incremental refresh.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="9" t="inlineStr">
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>Rolling re-check window: days of history re-pulled on every refresh so late-updated records are never missed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>Historical Backfill Start Date</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>Earliest date fetched on a first-ever run (empty staging table). Ignored once a table has data — Lookback Days takes over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>Max Pages Per Refresh (Safety Cap)</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>Hard stop on pagination per query per refresh (500 pages x 250 records ≈ 125,000 rows), so a misconfigured filter can't run away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>CHART OF ACCOUNTS MAPPING  (orange cells = configurable)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="16" t="inlineStr">
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>Account Code</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>Statement</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>P&amp;L / BS Line</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F31" s="17" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="17" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="18" t="inlineStr">
         <is>
           <t>4000</t>
         </is>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C32" s="18" t="inlineStr">
         <is>
           <t>EXAMPLE — Net Sales</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D32" s="18" t="inlineStr">
         <is>
           <t>P&amp;L</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="E32" s="18" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="F30" s="17" t="inlineStr">
+      <c r="F32" s="18" t="inlineStr">
         <is>
           <t>FACT_OrderLines</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>WORKBOOK VERSION LOG  (system-maintained)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="B34" s="18" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>WORKBOOK VERSION LOG  (system-maintained — every phase appends a row here)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C36" s="19" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D34" s="18" t="inlineStr">
+      <c r="D36" s="19" t="inlineStr">
         <is>
           <t>Phase</t>
         </is>
       </c>
-      <c r="E34" s="18" t="inlineStr">
+      <c r="E36" s="19" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="24" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="20" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="C35" s="24" t="inlineStr">
+      <c r="C37" s="20" t="inlineStr">
         <is>
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="D35" s="24" t="inlineStr">
+      <c r="D37" s="20" t="inlineStr">
         <is>
           <t>Phase 1 — Workbook Foundation</t>
         </is>
       </c>
-      <c r="E35" s="24" t="inlineStr">
+      <c r="E37" s="20" t="inlineStr">
         <is>
           <t>Structure, tables, named ranges, documentation. No live data, no calculations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>Phase 1 Finalization</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>01_Home's Workbook Version / Phase Completed KPI cards now read this table's last row live via formula — every future phase appends a row here and Home updates automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>Phase 2 — Shopify GraphQL Ingestion Layer</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>Complete Power Query M layer: authentication (Extension.CurrentCredential, no hardcoded tokens), automatic cursor pagination, incremental refresh, HTTP/GraphQL error handling with backoff. Covers Products, Variants, Orders, Order Lines, Customers, Collections, Inventory Levels, Transactions, Refunds, Discounts — read-only (GraphQL query operations only). Added RAW_Transactions and RAW_Discounts staging sheets; revised RAW_Refunds and RAW_InventoryLevels to match verified Shopify Admin API schema. See /passress-mis/power-query/README.md and DOCUMENTATION.md. No dashboards yet.</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3722,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Shopify Admin GraphQL API (fn_ShopifyGraphQL — Phase 2).</t>
+          <t>Shopify Admin GraphQL API, via the fn_ShopifyGraphQL / fn_ShopifyPagedConnection shared functions.</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3734,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Feeds the Data Model fact/dimension tables built from this resource.</t>
+          <t>Feeds the Data Model fact/dimension tables built from this resource (Phase 3).</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3746,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Connection-only in Excel; loaded to the Data Model, not to a worksheet grid, once Power Query is wired.</t>
+          <t>Connection-only in Excel; loaded to the Data Model, not to a worksheet grid, once wired in Excel.</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3758,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Shopify Admin GraphQL API, via Power Query — Phase 2.</t>
+          <t>Live now: paste passress-mis/power-query/staging/RAW_Orders.pq into this query in Excel's Power Query Advanced Editor (Data &gt; Get Data &gt; Launch Power Query Editor &gt; New Query &gt; Blank Query). See passress-mis/power-query/README.md for full setup and passress-mis/power-query/DOCUMENTATION.md for the field-by-field mapping.</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3929,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Shopify Admin GraphQL API (fn_ShopifyGraphQL — Phase 2).</t>
+          <t>Shopify Admin GraphQL API, via the fn_ShopifyGraphQL / fn_ShopifyPagedConnection shared functions.</t>
         </is>
       </c>
     </row>
@@ -3811,7 +3941,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Feeds the Data Model fact/dimension tables built from this resource.</t>
+          <t>Feeds the Data Model fact/dimension tables built from this resource (Phase 3).</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3953,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Connection-only in Excel; loaded to the Data Model, not to a worksheet grid, once Power Query is wired.</t>
+          <t>Connection-only in Excel; loaded to the Data Model, not to a worksheet grid, once wired in Excel.</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3965,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Shopify Admin GraphQL API, via Power Query — Phase 2.</t>
+          <t>Live now: paste passress-mis/power-query/staging/RAW_OrderLines.pq into this query in Excel's Power Query Advanced Editor (Data &gt; Get Data &gt; Launch Power Query Editor &gt; New Query &gt; Blank Query). See passress-mis/power-query/README.md for full setup and passress-mis/power-query/DOCUMENTATION.md for the field-by-field mapping.</t>
         </is>
       </c>
     </row>
@@ -3931,7 +4061,7 @@
     <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3942,19 +4072,22 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAW_Refunds</t>
+          <t>RAW_Transactions</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PASSRESS MIS   |   Home ▸ RAW_Refunds</t>
+          <t>PASSRESS MIS   |   Home ▸ RAW_Transactions</t>
         </is>
       </c>
     </row>
@@ -3973,7 +4106,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Power Query staging landing zone for the Shopify Refunds resource. Shape-only transforms (type casting, flattening) happen here — no business logic.</t>
+          <t>Power Query staging landing zone for the Shopify Transactions resource. Shape-only transforms (type casting, flattening) happen here — no business logic.</t>
         </is>
       </c>
     </row>
@@ -3985,7 +4118,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Shopify Admin GraphQL API (fn_ShopifyGraphQL — Phase 2).</t>
+          <t>Shopify Admin GraphQL API, via the fn_ShopifyGraphQL / fn_ShopifyPagedConnection shared functions.</t>
         </is>
       </c>
     </row>
@@ -3997,7 +4130,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Feeds the Data Model fact/dimension tables built from this resource.</t>
+          <t>Feeds the Data Model fact/dimension tables built from this resource (Phase 3).</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4142,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Connection-only in Excel; loaded to the Data Model, not to a worksheet grid, once Power Query is wired.</t>
+          <t>Connection-only in Excel; loaded to the Data Model, not to a worksheet grid, once wired in Excel.</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4154,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Shopify Admin GraphQL API, via Power Query — Phase 2.</t>
+          <t>Live now: paste passress-mis/power-query/staging/RAW_Transactions.pq into this query in Excel's Power Query Advanced Editor (Data &gt; Get Data &gt; Launch Power Query Editor &gt; New Query &gt; Blank Query). See passress-mis/power-query/README.md for full setup and passress-mis/power-query/DOCUMENTATION.md for the field-by-field mapping.</t>
         </is>
       </c>
     </row>
@@ -4030,7 +4163,7 @@
     <row r="11" ht="18" customHeight="1">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>RefundID</t>
+          <t>TransactionID</t>
         </is>
       </c>
       <c r="C11" s="25" t="inlineStr">
@@ -4040,27 +4173,42 @@
       </c>
       <c r="D11" s="25" t="inlineStr">
         <is>
-          <t>LineItemID</t>
+          <t>Kind</t>
         </is>
       </c>
       <c r="E11" s="25" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>RefundAmount</t>
+          <t>Gateway</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>RefundedAt</t>
+          <t>AmountShop</t>
         </is>
       </c>
       <c r="H11" s="25" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>CurrencyShop</t>
+        </is>
+      </c>
+      <c r="I11" s="25" t="inlineStr">
+        <is>
+          <t>CreatedAt</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="inlineStr">
+        <is>
+          <t>ProcessedAt</t>
+        </is>
+      </c>
+      <c r="K11" s="25" t="inlineStr">
+        <is>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -4072,18 +4220,21 @@
       <c r="F12" s="26" t="n"/>
       <c r="G12" s="26" t="n"/>
       <c r="H12" s="26" t="n"/>
+      <c r="I12" s="26" t="n"/>
+      <c r="J12" s="26" t="n"/>
+      <c r="K12" s="26" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
   <mergeCells count="8">
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B8:K8"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="B7:K7"/>
+    <mergeCell ref="B6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B5:K5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -4099,7 +4250,7 @@
     <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4110,19 +4261,22 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAW_Products</t>
+          <t>RAW_Refunds</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PASSRESS MIS   |   Home ▸ RAW_Products</t>
+          <t>PASSRESS MIS   |   Home ▸ RAW_Refunds</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4295,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Power Query staging landing zone for the Shopify Products resource. Shape-only transforms (type casting, flattening) happen here — no business logic.</t>
+          <t>Power Query staging landing zone for the Shopify Refunds resource. Shape-only transforms (type casting, flattening) happen here — no business logic.</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4307,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Shopify Admin GraphQL API (fn_ShopifyGraphQL — Phase 2).</t>
+          <t>Shopify Admin GraphQL API, via the fn_ShopifyGraphQL / fn_ShopifyPagedConnection shared functions.</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4319,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Feeds the Data Model fact/dimension tables built from this resource.</t>
+          <t>Feeds the Data Model fact/dimension tables built from this resource (Phase 3).</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4331,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Connection-only in Excel; loaded to the Data Model, not to a worksheet grid, once Power Query is wired.</t>
+          <t>Connection-only in Excel; loaded to the Data Model, not to a worksheet grid, once wired in Excel.</t>
         </is>
       </c>
     </row>
@@ -4189,7 +4343,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Shopify Admin GraphQL API, via Power Query — Phase 2.</t>
+          <t>Live now: paste passress-mis/power-query/staging/RAW_Refunds.pq into this query in Excel's Power Query Advanced Editor (Data &gt; Get Data &gt; Launch Power Query Editor &gt; New Query &gt; Blank Query). See passress-mis/power-query/README.md for full setup and passress-mis/power-query/DOCUMENTATION.md for the field-by-field mapping.</t>
         </is>
       </c>
     </row>
@@ -4198,37 +4352,52 @@
     <row r="11" ht="18" customHeight="1">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>ProductID</t>
+          <t>RefundLineItemID</t>
         </is>
       </c>
       <c r="C11" s="25" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>RefundID</t>
         </is>
       </c>
       <c r="D11" s="25" t="inlineStr">
         <is>
-          <t>ProductType</t>
+          <t>OrderID</t>
         </is>
       </c>
       <c r="E11" s="25" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>LineItemID</t>
         </is>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>CollectionIDs</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>CreatedAt</t>
+          <t>SubtotalAmount</t>
         </is>
       </c>
       <c r="H11" s="25" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>TaxAmount</t>
+        </is>
+      </c>
+      <c r="I11" s="25" t="inlineStr">
+        <is>
+          <t>RefundCreatedAt</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="inlineStr">
+        <is>
+          <t>RefundProcessedAt</t>
+        </is>
+      </c>
+      <c r="K11" s="25" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
@@ -4240,18 +4409,21 @@
       <c r="F12" s="26" t="n"/>
       <c r="G12" s="26" t="n"/>
       <c r="H12" s="26" t="n"/>
+      <c r="I12" s="26" t="n"/>
+      <c r="J12" s="26" t="n"/>
+      <c r="K12" s="26" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
   <mergeCells count="8">
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B8:K8"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="B7:K7"/>
+    <mergeCell ref="B6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B5:K5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -4458,292 +4630,292 @@
       <c r="M13" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>TRENDS &amp; BREAKDOWNS</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>[ Revenue Trend (Chart)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="13" t="n"/>
-      <c r="H17" s="13" t="n"/>
-      <c r="I17" s="13" t="n"/>
-      <c r="J17" s="13" t="n"/>
-      <c r="K17" s="13" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="14" t="n"/>
+      <c r="I17" s="14" t="n"/>
+      <c r="J17" s="14" t="n"/>
+      <c r="K17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="13" t="n"/>
-      <c r="H18" s="13" t="n"/>
-      <c r="I18" s="13" t="n"/>
-      <c r="J18" s="13" t="n"/>
-      <c r="K18" s="13" t="n"/>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="14" t="n"/>
+      <c r="I18" s="14" t="n"/>
+      <c r="J18" s="14" t="n"/>
+      <c r="K18" s="14" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="13" t="n"/>
-      <c r="H19" s="13" t="n"/>
-      <c r="I19" s="13" t="n"/>
-      <c r="J19" s="13" t="n"/>
-      <c r="K19" s="13" t="n"/>
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="14" t="n"/>
+      <c r="E19" s="14" t="n"/>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="14" t="n"/>
+      <c r="H19" s="14" t="n"/>
+      <c r="I19" s="14" t="n"/>
+      <c r="J19" s="14" t="n"/>
+      <c r="K19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="13" t="n"/>
-      <c r="H20" s="13" t="n"/>
-      <c r="I20" s="13" t="n"/>
-      <c r="J20" s="13" t="n"/>
-      <c r="K20" s="13" t="n"/>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="14" t="n"/>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="14" t="n"/>
+      <c r="H20" s="14" t="n"/>
+      <c r="I20" s="14" t="n"/>
+      <c r="J20" s="14" t="n"/>
+      <c r="K20" s="14" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="13" t="n"/>
-      <c r="H21" s="13" t="n"/>
-      <c r="I21" s="13" t="n"/>
-      <c r="J21" s="13" t="n"/>
-      <c r="K21" s="13" t="n"/>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="14" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="14" t="n"/>
+      <c r="H21" s="14" t="n"/>
+      <c r="I21" s="14" t="n"/>
+      <c r="J21" s="14" t="n"/>
+      <c r="K21" s="14" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="13" t="n"/>
-      <c r="H22" s="13" t="n"/>
-      <c r="I22" s="13" t="n"/>
-      <c r="J22" s="13" t="n"/>
-      <c r="K22" s="13" t="n"/>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="14" t="n"/>
+      <c r="I22" s="14" t="n"/>
+      <c r="J22" s="14" t="n"/>
+      <c r="K22" s="14" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="13" t="n"/>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="13" t="n"/>
-      <c r="J23" s="13" t="n"/>
-      <c r="K23" s="13" t="n"/>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="14" t="n"/>
+      <c r="I23" s="14" t="n"/>
+      <c r="J23" s="14" t="n"/>
+      <c r="K23" s="14" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="13" t="n"/>
-      <c r="H24" s="13" t="n"/>
-      <c r="I24" s="13" t="n"/>
-      <c r="J24" s="13" t="n"/>
-      <c r="K24" s="13" t="n"/>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="14" t="n"/>
+      <c r="I24" s="14" t="n"/>
+      <c r="J24" s="14" t="n"/>
+      <c r="K24" s="14" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>[ Expense Breakdown (Chart)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="13" t="n"/>
-      <c r="H26" s="13" t="n"/>
-      <c r="I26" s="13" t="n"/>
-      <c r="J26" s="13" t="n"/>
-      <c r="K26" s="13" t="n"/>
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="14" t="n"/>
+      <c r="E26" s="14" t="n"/>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="14" t="n"/>
+      <c r="H26" s="14" t="n"/>
+      <c r="I26" s="14" t="n"/>
+      <c r="J26" s="14" t="n"/>
+      <c r="K26" s="14" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="13" t="n"/>
-      <c r="C27" s="13" t="n"/>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="13" t="n"/>
-      <c r="G27" s="13" t="n"/>
-      <c r="H27" s="13" t="n"/>
-      <c r="I27" s="13" t="n"/>
-      <c r="J27" s="13" t="n"/>
-      <c r="K27" s="13" t="n"/>
+      <c r="B27" s="14" t="n"/>
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="14" t="n"/>
+      <c r="E27" s="14" t="n"/>
+      <c r="F27" s="14" t="n"/>
+      <c r="G27" s="14" t="n"/>
+      <c r="H27" s="14" t="n"/>
+      <c r="I27" s="14" t="n"/>
+      <c r="J27" s="14" t="n"/>
+      <c r="K27" s="14" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="13" t="n"/>
-      <c r="C28" s="13" t="n"/>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="13" t="n"/>
-      <c r="H28" s="13" t="n"/>
-      <c r="I28" s="13" t="n"/>
-      <c r="J28" s="13" t="n"/>
-      <c r="K28" s="13" t="n"/>
+      <c r="B28" s="14" t="n"/>
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="14" t="n"/>
+      <c r="H28" s="14" t="n"/>
+      <c r="I28" s="14" t="n"/>
+      <c r="J28" s="14" t="n"/>
+      <c r="K28" s="14" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="13" t="n"/>
-      <c r="H29" s="13" t="n"/>
-      <c r="I29" s="13" t="n"/>
-      <c r="J29" s="13" t="n"/>
-      <c r="K29" s="13" t="n"/>
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="14" t="n"/>
+      <c r="H29" s="14" t="n"/>
+      <c r="I29" s="14" t="n"/>
+      <c r="J29" s="14" t="n"/>
+      <c r="K29" s="14" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="13" t="n"/>
-      <c r="H30" s="13" t="n"/>
-      <c r="I30" s="13" t="n"/>
-      <c r="J30" s="13" t="n"/>
-      <c r="K30" s="13" t="n"/>
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="14" t="n"/>
+      <c r="I30" s="14" t="n"/>
+      <c r="J30" s="14" t="n"/>
+      <c r="K30" s="14" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="13" t="n"/>
-      <c r="C31" s="13" t="n"/>
-      <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
-      <c r="G31" s="13" t="n"/>
-      <c r="H31" s="13" t="n"/>
-      <c r="I31" s="13" t="n"/>
-      <c r="J31" s="13" t="n"/>
-      <c r="K31" s="13" t="n"/>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="14" t="n"/>
+      <c r="I31" s="14" t="n"/>
+      <c r="J31" s="14" t="n"/>
+      <c r="K31" s="14" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="13" t="n"/>
-      <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="13" t="n"/>
-      <c r="H32" s="13" t="n"/>
-      <c r="I32" s="13" t="n"/>
-      <c r="J32" s="13" t="n"/>
-      <c r="K32" s="13" t="n"/>
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="14" t="n"/>
+      <c r="H32" s="14" t="n"/>
+      <c r="I32" s="14" t="n"/>
+      <c r="J32" s="14" t="n"/>
+      <c r="K32" s="14" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="13" t="n"/>
-      <c r="H33" s="13" t="n"/>
-      <c r="I33" s="13" t="n"/>
-      <c r="J33" s="13" t="n"/>
-      <c r="K33" s="13" t="n"/>
+      <c r="B33" s="14" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="14" t="n"/>
+      <c r="E33" s="14" t="n"/>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="14" t="n"/>
+      <c r="H33" s="14" t="n"/>
+      <c r="I33" s="14" t="n"/>
+      <c r="J33" s="14" t="n"/>
+      <c r="K33" s="14" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>DETAIL (PIVOTTABLES)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>[ Financial Summary (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="C37" s="13" t="n"/>
-      <c r="D37" s="13" t="n"/>
-      <c r="E37" s="13" t="n"/>
-      <c r="F37" s="13" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="14" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="13" t="n"/>
-      <c r="C38" s="13" t="n"/>
-      <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
+      <c r="B38" s="14" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="14" t="n"/>
+      <c r="E38" s="14" t="n"/>
+      <c r="F38" s="14" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="13" t="n"/>
-      <c r="C39" s="13" t="n"/>
-      <c r="D39" s="13" t="n"/>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="n"/>
+      <c r="B39" s="14" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n"/>
+      <c r="E39" s="14" t="n"/>
+      <c r="F39" s="14" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="13" t="n"/>
-      <c r="C40" s="13" t="n"/>
-      <c r="D40" s="13" t="n"/>
-      <c r="E40" s="13" t="n"/>
-      <c r="F40" s="13" t="n"/>
+      <c r="B40" s="14" t="n"/>
+      <c r="C40" s="14" t="n"/>
+      <c r="D40" s="14" t="n"/>
+      <c r="E40" s="14" t="n"/>
+      <c r="F40" s="14" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="13" t="n"/>
-      <c r="C41" s="13" t="n"/>
-      <c r="D41" s="13" t="n"/>
-      <c r="E41" s="13" t="n"/>
-      <c r="F41" s="13" t="n"/>
+      <c r="B41" s="14" t="n"/>
+      <c r="C41" s="14" t="n"/>
+      <c r="D41" s="14" t="n"/>
+      <c r="E41" s="14" t="n"/>
+      <c r="F41" s="14" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="13" t="n"/>
-      <c r="C42" s="13" t="n"/>
-      <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
+      <c r="B42" s="14" t="n"/>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="14" t="n"/>
+      <c r="E42" s="14" t="n"/>
+      <c r="F42" s="14" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="13" t="n"/>
-      <c r="C43" s="13" t="n"/>
-      <c r="D43" s="13" t="n"/>
-      <c r="E43" s="13" t="n"/>
-      <c r="F43" s="13" t="n"/>
+      <c r="B43" s="14" t="n"/>
+      <c r="C43" s="14" t="n"/>
+      <c r="D43" s="14" t="n"/>
+      <c r="E43" s="14" t="n"/>
+      <c r="F43" s="14" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="13" t="n"/>
-      <c r="C44" s="13" t="n"/>
-      <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
+      <c r="B44" s="14" t="n"/>
+      <c r="C44" s="14" t="n"/>
+      <c r="D44" s="14" t="n"/>
+      <c r="E44" s="14" t="n"/>
+      <c r="F44" s="14" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="13" t="n"/>
-      <c r="C45" s="13" t="n"/>
-      <c r="D45" s="13" t="n"/>
-      <c r="E45" s="13" t="n"/>
-      <c r="F45" s="13" t="n"/>
+      <c r="B45" s="14" t="n"/>
+      <c r="C45" s="14" t="n"/>
+      <c r="D45" s="14" t="n"/>
+      <c r="E45" s="14" t="n"/>
+      <c r="F45" s="14" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="13" t="n"/>
-      <c r="C46" s="13" t="n"/>
-      <c r="D46" s="13" t="n"/>
-      <c r="E46" s="13" t="n"/>
-      <c r="F46" s="13" t="n"/>
+      <c r="B46" s="14" t="n"/>
+      <c r="C46" s="14" t="n"/>
+      <c r="D46" s="14" t="n"/>
+      <c r="E46" s="14" t="n"/>
+      <c r="F46" s="14" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -4800,14 +4972,14 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAW_Variants</t>
+          <t>RAW_Products</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PASSRESS MIS   |   Home ▸ RAW_Variants</t>
+          <t>PASSRESS MIS   |   Home ▸ RAW_Products</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4998,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Power Query staging landing zone for the Shopify Variants resource. Shape-only transforms (type casting, flattening) happen here — no business logic.</t>
+          <t>Power Query staging landing zone for the Shopify Products resource. Shape-only transforms (type casting, flattening) happen here — no business logic.</t>
         </is>
       </c>
     </row>
@@ -4838,7 +5010,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Shopify Admin GraphQL API (fn_ShopifyGraphQL — Phase 2).</t>
+          <t>Shopify Admin GraphQL API, via the fn_ShopifyGraphQL / fn_ShopifyPagedConnection shared functions.</t>
         </is>
       </c>
     </row>
@@ -4850,7 +5022,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Feeds the Data Model fact/dimension tables built from this resource.</t>
+          <t>Feeds the Data Model fact/dimension tables built from this resource (Phase 3).</t>
         </is>
       </c>
     </row>
@@ -4862,7 +5034,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Connection-only in Excel; loaded to the Data Model, not to a worksheet grid, once Power Query is wired.</t>
+          <t>Connection-only in Excel; loaded to the Data Model, not to a worksheet grid, once wired in Excel.</t>
         </is>
       </c>
     </row>
@@ -4874,7 +5046,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Shopify Admin GraphQL API, via Power Query — Phase 2.</t>
+          <t>Live now: paste passress-mis/power-query/staging/RAW_Products.pq into this query in Excel's Power Query Advanced Editor (Data &gt; Get Data &gt; Launch Power Query Editor &gt; New Query &gt; Blank Query). See passress-mis/power-query/README.md for full setup and passress-mis/power-query/DOCUMENTATION.md for the field-by-field mapping.</t>
         </is>
       </c>
     </row>
@@ -4883,42 +5055,42 @@
     <row r="11" ht="18" customHeight="1">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>VariantID</t>
+          <t>ProductID</t>
         </is>
       </c>
       <c r="C11" s="25" t="inlineStr">
         <is>
-          <t>ProductID</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D11" s="25" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>ProductType</t>
         </is>
       </c>
       <c r="E11" s="25" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>CollectionIDs</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>CompareAtPrice</t>
+          <t>CreatedAt</t>
         </is>
       </c>
       <c r="H11" s="25" t="inlineStr">
         <is>
-          <t>InventoryItemID</t>
+          <t>UpdatedAt</t>
         </is>
       </c>
       <c r="I11" s="25" t="inlineStr">
         <is>
-          <t>UnitCost</t>
+          <t>Status</t>
         </is>
       </c>
     </row>
@@ -4958,7 +5130,7 @@
     <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4966,19 +5138,25 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAW_InventoryLevels</t>
+          <t>RAW_Variants</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PASSRESS MIS   |   Home ▸ RAW_InventoryLevels</t>
+          <t>PASSRESS MIS   |   Home ▸ RAW_Variants</t>
         </is>
       </c>
     </row>
@@ -4997,7 +5175,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Power Query staging landing zone for the Shopify InventoryLevels resource. Shape-only transforms (type casting, flattening) happen here — no business logic.</t>
+          <t>Power Query staging landing zone for the Shopify Variants resource. Shape-only transforms (type casting, flattening) happen here — no business logic.</t>
         </is>
       </c>
     </row>
@@ -5009,7 +5187,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Shopify Admin GraphQL API (fn_ShopifyGraphQL — Phase 2).</t>
+          <t>Shopify Admin GraphQL API, via the fn_ShopifyGraphQL / fn_ShopifyPagedConnection shared functions.</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5199,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Feeds the Data Model fact/dimension tables built from this resource.</t>
+          <t>Feeds the Data Model fact/dimension tables built from this resource (Phase 3).</t>
         </is>
       </c>
     </row>
@@ -5033,7 +5211,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Connection-only in Excel; loaded to the Data Model, not to a worksheet grid, once Power Query is wired.</t>
+          <t>Connection-only in Excel; loaded to the Data Model, not to a worksheet grid, once wired in Excel.</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5223,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Shopify Admin GraphQL API, via Power Query — Phase 2.</t>
+          <t>Live now: paste passress-mis/power-query/staging/RAW_Variants.pq into this query in Excel's Power Query Advanced Editor (Data &gt; Get Data &gt; Launch Power Query Editor &gt; New Query &gt; Blank Query). See passress-mis/power-query/README.md for full setup and passress-mis/power-query/DOCUMENTATION.md for the field-by-field mapping.</t>
         </is>
       </c>
     </row>
@@ -5054,20 +5232,50 @@
     <row r="11" ht="18" customHeight="1">
       <c r="B11" s="25" t="inlineStr">
         <is>
+          <t>VariantID</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="inlineStr">
+        <is>
+          <t>ProductID</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="F11" s="25" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="G11" s="25" t="inlineStr">
+        <is>
+          <t>CompareAtPrice</t>
+        </is>
+      </c>
+      <c r="H11" s="25" t="inlineStr">
+        <is>
           <t>InventoryItemID</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
-        <is>
-          <t>LocationID</t>
-        </is>
-      </c>
-      <c r="D11" s="25" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="I11" s="25" t="inlineStr">
+        <is>
+          <t>UnitCost</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="inlineStr">
+        <is>
+          <t>CreatedAt</t>
+        </is>
+      </c>
+      <c r="K11" s="25" t="inlineStr">
         <is>
           <t>UpdatedAt</t>
         </is>
@@ -5078,18 +5286,24 @@
       <c r="C12" s="26" t="n"/>
       <c r="D12" s="26" t="n"/>
       <c r="E12" s="26" t="n"/>
+      <c r="F12" s="26" t="n"/>
+      <c r="G12" s="26" t="n"/>
+      <c r="H12" s="26" t="n"/>
+      <c r="I12" s="26" t="n"/>
+      <c r="J12" s="26" t="n"/>
+      <c r="K12" s="26" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
   <mergeCells count="8">
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B8:K8"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="B7:K7"/>
+    <mergeCell ref="B6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B5:K5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -5105,7 +5319,161 @@
     <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>RAW_InventoryLevels</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PASSRESS MIS   |   Home ▸ RAW_InventoryLevels</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sheet Documentation  (use the  +  outline control at left to expand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Power Query staging landing zone for the Shopify InventoryLevels resource. Shape-only transforms (type casting, flattening) happen here — no business logic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Input tables</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Shopify Admin GraphQL API, via the fn_ShopifyGraphQL / fn_ShopifyPagedConnection shared functions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Output tables</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Feeds the Data Model fact/dimension tables built from this resource (Phase 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Relationships</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Connection-only in Excel; loaded to the Data Model, not to a worksheet grid, once wired in Excel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Future data source</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Live now: paste passress-mis/power-query/staging/RAW_InventoryLevels.pq into this query in Excel's Power Query Advanced Editor (Data &gt; Get Data &gt; Launch Power Query Editor &gt; New Query &gt; Blank Query). See passress-mis/power-query/README.md for full setup and passress-mis/power-query/DOCUMENTATION.md for the field-by-field mapping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" hidden="1" outlineLevel="1"/>
+    <row r="10" ht="6" customHeight="1"/>
+    <row r="11" ht="18" customHeight="1">
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>InventoryItemID</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>LocationID</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="F11" s="25" t="inlineStr">
+        <is>
+          <t>UpdatedAt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="26" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="26" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
+  <mergeCells count="8">
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="A3:F3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000070C0"/>
+    <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5117,6 +5485,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -5160,7 +5529,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Shopify Admin GraphQL API (fn_ShopifyGraphQL — Phase 2).</t>
+          <t>Shopify Admin GraphQL API, via the fn_ShopifyGraphQL / fn_ShopifyPagedConnection shared functions.</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5541,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Feeds the Data Model fact/dimension tables built from this resource.</t>
+          <t>Feeds the Data Model fact/dimension tables built from this resource (Phase 3).</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5553,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Connection-only in Excel; loaded to the Data Model, not to a worksheet grid, once Power Query is wired.</t>
+          <t>Connection-only in Excel; loaded to the Data Model, not to a worksheet grid, once wired in Excel.</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5565,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Shopify Admin GraphQL API, via Power Query — Phase 2.</t>
+          <t>Live now: paste passress-mis/power-query/staging/RAW_Customers.pq into this query in Excel's Power Query Advanced Editor (Data &gt; Get Data &gt; Launch Power Query Editor &gt; New Query &gt; Blank Query). See passress-mis/power-query/README.md for full setup and passress-mis/power-query/DOCUMENTATION.md for the field-by-field mapping.</t>
         </is>
       </c>
     </row>
@@ -5230,15 +5599,20 @@
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
+          <t>UpdatedAt</t>
+        </is>
+      </c>
+      <c r="H11" s="25" t="inlineStr">
+        <is>
           <t>OrdersCount</t>
         </is>
       </c>
-      <c r="H11" s="25" t="inlineStr">
+      <c r="I11" s="25" t="inlineStr">
         <is>
           <t>TotalSpent</t>
         </is>
       </c>
-      <c r="I11" s="25" t="inlineStr">
+      <c r="J11" s="25" t="inlineStr">
         <is>
           <t>DefaultAddressCountry</t>
         </is>
@@ -5253,18 +5627,19 @@
       <c r="G12" s="26" t="n"/>
       <c r="H12" s="26" t="n"/>
       <c r="I12" s="26" t="n"/>
+      <c r="J12" s="26" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
   <mergeCells count="8">
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B6:I6"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B7:J7"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="B8:J8"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="B6:J6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -5273,7 +5648,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000070C0"/>
@@ -5330,7 +5705,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Shopify Admin GraphQL API (fn_ShopifyGraphQL — Phase 2).</t>
+          <t>Shopify Admin GraphQL API, via the fn_ShopifyGraphQL / fn_ShopifyPagedConnection shared functions.</t>
         </is>
       </c>
     </row>
@@ -5342,7 +5717,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Feeds the Data Model fact/dimension tables built from this resource.</t>
+          <t>Feeds the Data Model fact/dimension tables built from this resource (Phase 3).</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5729,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Connection-only in Excel; loaded to the Data Model, not to a worksheet grid, once Power Query is wired.</t>
+          <t>Connection-only in Excel; loaded to the Data Model, not to a worksheet grid, once wired in Excel.</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5741,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Shopify Admin GraphQL API, via Power Query — Phase 2.</t>
+          <t>Live now: paste passress-mis/power-query/staging/RAW_Collections.pq into this query in Excel's Power Query Advanced Editor (Data &gt; Get Data &gt; Launch Power Query Editor &gt; New Query &gt; Blank Query). See passress-mis/power-query/README.md for full setup and passress-mis/power-query/DOCUMENTATION.md for the field-by-field mapping.</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5788,210 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000070C0"/>
+    <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>RAW_Discounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PASSRESS MIS   |   Home ▸ RAW_Discounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sheet Documentation  (use the  +  outline control at left to expand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Power Query staging landing zone for the Shopify Discounts resource. Shape-only transforms (type casting, flattening) happen here — no business logic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Input tables</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Shopify Admin GraphQL API, via the fn_ShopifyGraphQL / fn_ShopifyPagedConnection shared functions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Output tables</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Feeds the Data Model fact/dimension tables built from this resource (Phase 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Relationships</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Connection-only in Excel; loaded to the Data Model, not to a worksheet grid, once wired in Excel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Future data source</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Live now: paste passress-mis/power-query/staging/RAW_Discounts.pq into this query in Excel's Power Query Advanced Editor (Data &gt; Get Data &gt; Launch Power Query Editor &gt; New Query &gt; Blank Query). See passress-mis/power-query/README.md for full setup and passress-mis/power-query/DOCUMENTATION.md for the field-by-field mapping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" hidden="1" outlineLevel="1"/>
+    <row r="10" ht="6" customHeight="1"/>
+    <row r="11" ht="18" customHeight="1">
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>DiscountNodeID</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="inlineStr">
+        <is>
+          <t>Typename</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F11" s="25" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="G11" s="25" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="H11" s="25" t="inlineStr">
+        <is>
+          <t>StartsAt</t>
+        </is>
+      </c>
+      <c r="I11" s="25" t="inlineStr">
+        <is>
+          <t>EndsAt</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="inlineStr">
+        <is>
+          <t>UsageLimit</t>
+        </is>
+      </c>
+      <c r="K11" s="25" t="inlineStr">
+        <is>
+          <t>AsyncUsageCount</t>
+        </is>
+      </c>
+      <c r="L11" s="25" t="inlineStr">
+        <is>
+          <t>CreatedAt</t>
+        </is>
+      </c>
+      <c r="M11" s="25" t="inlineStr">
+        <is>
+          <t>UpdatedAt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="26" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="26" t="n"/>
+      <c r="G12" s="26" t="n"/>
+      <c r="H12" s="26" t="n"/>
+      <c r="I12" s="26" t="n"/>
+      <c r="J12" s="26" t="n"/>
+      <c r="K12" s="26" t="n"/>
+      <c r="L12" s="26" t="n"/>
+      <c r="M12" s="26" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
+  <mergeCells count="8">
+    <mergeCell ref="B6:M6"/>
+    <mergeCell ref="B7:M7"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="B5:M5"/>
+    <mergeCell ref="B8:M8"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="B4:M4"/>
+    <mergeCell ref="A2:M2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007F7F7F"/>
@@ -5521,74 +6099,74 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>DateKey</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>FiscalYear</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>Quarter</t>
         </is>
       </c>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="H11" s="19" t="inlineStr">
         <is>
           <t>MonthName</t>
         </is>
       </c>
-      <c r="I11" s="18" t="inlineStr">
+      <c r="I11" s="19" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
       </c>
-      <c r="J11" s="18" t="inlineStr">
+      <c r="J11" s="19" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="K11" s="18" t="inlineStr">
+      <c r="K11" s="19" t="inlineStr">
         <is>
           <t>DayName</t>
         </is>
       </c>
-      <c r="L11" s="18" t="inlineStr">
+      <c r="L11" s="19" t="inlineStr">
         <is>
           <t>IsWeekend</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="19" t="n"/>
-      <c r="H12" s="19" t="n"/>
-      <c r="I12" s="19" t="n"/>
-      <c r="J12" s="19" t="n"/>
-      <c r="K12" s="19" t="n"/>
-      <c r="L12" s="19" t="n"/>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20" t="n"/>
+      <c r="I12" s="20" t="n"/>
+      <c r="J12" s="20" t="n"/>
+      <c r="K12" s="20" t="n"/>
+      <c r="L12" s="20" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -5609,7 +6187,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007F7F7F"/>
@@ -5715,62 +6293,62 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>ProductKey</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>ProductID</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>ProductType</t>
         </is>
       </c>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="H11" s="19" t="inlineStr">
         <is>
           <t>Collection</t>
         </is>
       </c>
-      <c r="I11" s="18" t="inlineStr">
+      <c r="I11" s="19" t="inlineStr">
         <is>
           <t>UnitCost</t>
         </is>
       </c>
-      <c r="J11" s="18" t="inlineStr">
+      <c r="J11" s="19" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="19" t="n"/>
-      <c r="H12" s="19" t="n"/>
-      <c r="I12" s="19" t="n"/>
-      <c r="J12" s="19" t="n"/>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20" t="n"/>
+      <c r="I12" s="20" t="n"/>
+      <c r="J12" s="20" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -5791,7 +6369,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007F7F7F"/>
@@ -5895,50 +6473,50 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>CustomerKey</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>CustomerID</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>FirstOrderDate</t>
         </is>
       </c>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="H11" s="19" t="inlineStr">
         <is>
           <t>CustomerSegment</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="19" t="n"/>
-      <c r="H12" s="19" t="n"/>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -5959,7 +6537,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007F7F7F"/>
@@ -6061,38 +6639,38 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>LocationKey</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>LocationID</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>LocationName</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -6105,286 +6683,6 @@
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="A3:F3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="007F7F7F"/>
-    <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>DIM_Collection</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>PASSRESS MIS   |   Home ▸ DIM_Collection</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="14" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Sheet Documentation  (use the  +  outline control at left to expand)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" hidden="1" outlineLevel="1" ht="13" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Dimension table for the star schema — describes the 'Collection' entity that FACT_ tables relate to.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" hidden="1" outlineLevel="1" ht="13" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Input tables</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Derived from the matching RAW_ staging table(s).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" hidden="1" outlineLevel="1" ht="13" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Output tables</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Related to FACT_ tables in the Data Model (one-to-many).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" hidden="1" outlineLevel="1" ht="13" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Relationships</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>One-to-many into the relevant FACT_ table(s) on this dimension's key column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" hidden="1" outlineLevel="1" ht="13" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Future data source</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Built from RAW_ staging data in Power Query — Phase 2/3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" hidden="1" outlineLevel="1"/>
-    <row r="10" ht="6" customHeight="1"/>
-    <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>CollectionKey</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>CollectionID</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>Handle</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
-  <mergeCells count="8">
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A3:E3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="007F7F7F"/>
-    <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>DIM_Parameters</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>PASSRESS MIS   |   Home ▸ DIM_Parameters</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="14" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Sheet Documentation  (use the  +  outline control at left to expand)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" hidden="1" outlineLevel="1" ht="13" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Disconnected mirror of 15_Settings, used so DAX measures can reference configurable constants without creating a relationship into the star schema.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" hidden="1" outlineLevel="1" ht="13" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Input tables</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>15_Settings (linked manually / via Power Query, Phase 2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" hidden="1" outlineLevel="1" ht="13" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Output tables</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Referenced by DAX measures across all dashboards.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" hidden="1" outlineLevel="1" ht="13" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Relationships</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>N/A — disconnected table by design.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" hidden="1" outlineLevel="1" ht="13" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Future data source</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Manual link to 15_Settings — Phase 3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" hidden="1" outlineLevel="1"/>
-    <row r="10" ht="6" customHeight="1"/>
-    <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>ParameterName</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>ParameterValue</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
-  <mergeCells count="8">
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -6619,492 +6917,492 @@
       <c r="Q13" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>TRENDS &amp; BREAKDOWNS</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>[ Sales Trend (Chart)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="13" t="n"/>
-      <c r="H17" s="13" t="n"/>
-      <c r="I17" s="13" t="n"/>
-      <c r="J17" s="13" t="n"/>
-      <c r="K17" s="13" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="14" t="n"/>
+      <c r="I17" s="14" t="n"/>
+      <c r="J17" s="14" t="n"/>
+      <c r="K17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="13" t="n"/>
-      <c r="H18" s="13" t="n"/>
-      <c r="I18" s="13" t="n"/>
-      <c r="J18" s="13" t="n"/>
-      <c r="K18" s="13" t="n"/>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="14" t="n"/>
+      <c r="I18" s="14" t="n"/>
+      <c r="J18" s="14" t="n"/>
+      <c r="K18" s="14" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="13" t="n"/>
-      <c r="H19" s="13" t="n"/>
-      <c r="I19" s="13" t="n"/>
-      <c r="J19" s="13" t="n"/>
-      <c r="K19" s="13" t="n"/>
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="14" t="n"/>
+      <c r="E19" s="14" t="n"/>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="14" t="n"/>
+      <c r="H19" s="14" t="n"/>
+      <c r="I19" s="14" t="n"/>
+      <c r="J19" s="14" t="n"/>
+      <c r="K19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="13" t="n"/>
-      <c r="H20" s="13" t="n"/>
-      <c r="I20" s="13" t="n"/>
-      <c r="J20" s="13" t="n"/>
-      <c r="K20" s="13" t="n"/>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="14" t="n"/>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="14" t="n"/>
+      <c r="H20" s="14" t="n"/>
+      <c r="I20" s="14" t="n"/>
+      <c r="J20" s="14" t="n"/>
+      <c r="K20" s="14" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="13" t="n"/>
-      <c r="H21" s="13" t="n"/>
-      <c r="I21" s="13" t="n"/>
-      <c r="J21" s="13" t="n"/>
-      <c r="K21" s="13" t="n"/>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="14" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="14" t="n"/>
+      <c r="H21" s="14" t="n"/>
+      <c r="I21" s="14" t="n"/>
+      <c r="J21" s="14" t="n"/>
+      <c r="K21" s="14" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="13" t="n"/>
-      <c r="H22" s="13" t="n"/>
-      <c r="I22" s="13" t="n"/>
-      <c r="J22" s="13" t="n"/>
-      <c r="K22" s="13" t="n"/>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="14" t="n"/>
+      <c r="I22" s="14" t="n"/>
+      <c r="J22" s="14" t="n"/>
+      <c r="K22" s="14" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="13" t="n"/>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="13" t="n"/>
-      <c r="J23" s="13" t="n"/>
-      <c r="K23" s="13" t="n"/>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="14" t="n"/>
+      <c r="I23" s="14" t="n"/>
+      <c r="J23" s="14" t="n"/>
+      <c r="K23" s="14" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="13" t="n"/>
-      <c r="H24" s="13" t="n"/>
-      <c r="I24" s="13" t="n"/>
-      <c r="J24" s="13" t="n"/>
-      <c r="K24" s="13" t="n"/>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="14" t="n"/>
+      <c r="I24" s="14" t="n"/>
+      <c r="J24" s="14" t="n"/>
+      <c r="K24" s="14" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>[ Sales by Collection (Chart)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="13" t="n"/>
-      <c r="H26" s="13" t="n"/>
-      <c r="I26" s="13" t="n"/>
-      <c r="J26" s="13" t="n"/>
-      <c r="K26" s="13" t="n"/>
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="14" t="n"/>
+      <c r="E26" s="14" t="n"/>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="14" t="n"/>
+      <c r="H26" s="14" t="n"/>
+      <c r="I26" s="14" t="n"/>
+      <c r="J26" s="14" t="n"/>
+      <c r="K26" s="14" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="13" t="n"/>
-      <c r="C27" s="13" t="n"/>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="13" t="n"/>
-      <c r="G27" s="13" t="n"/>
-      <c r="H27" s="13" t="n"/>
-      <c r="I27" s="13" t="n"/>
-      <c r="J27" s="13" t="n"/>
-      <c r="K27" s="13" t="n"/>
+      <c r="B27" s="14" t="n"/>
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="14" t="n"/>
+      <c r="E27" s="14" t="n"/>
+      <c r="F27" s="14" t="n"/>
+      <c r="G27" s="14" t="n"/>
+      <c r="H27" s="14" t="n"/>
+      <c r="I27" s="14" t="n"/>
+      <c r="J27" s="14" t="n"/>
+      <c r="K27" s="14" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="13" t="n"/>
-      <c r="C28" s="13" t="n"/>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="13" t="n"/>
-      <c r="H28" s="13" t="n"/>
-      <c r="I28" s="13" t="n"/>
-      <c r="J28" s="13" t="n"/>
-      <c r="K28" s="13" t="n"/>
+      <c r="B28" s="14" t="n"/>
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="14" t="n"/>
+      <c r="H28" s="14" t="n"/>
+      <c r="I28" s="14" t="n"/>
+      <c r="J28" s="14" t="n"/>
+      <c r="K28" s="14" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="13" t="n"/>
-      <c r="H29" s="13" t="n"/>
-      <c r="I29" s="13" t="n"/>
-      <c r="J29" s="13" t="n"/>
-      <c r="K29" s="13" t="n"/>
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="14" t="n"/>
+      <c r="H29" s="14" t="n"/>
+      <c r="I29" s="14" t="n"/>
+      <c r="J29" s="14" t="n"/>
+      <c r="K29" s="14" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="13" t="n"/>
-      <c r="H30" s="13" t="n"/>
-      <c r="I30" s="13" t="n"/>
-      <c r="J30" s="13" t="n"/>
-      <c r="K30" s="13" t="n"/>
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="14" t="n"/>
+      <c r="I30" s="14" t="n"/>
+      <c r="J30" s="14" t="n"/>
+      <c r="K30" s="14" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="13" t="n"/>
-      <c r="C31" s="13" t="n"/>
-      <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
-      <c r="G31" s="13" t="n"/>
-      <c r="H31" s="13" t="n"/>
-      <c r="I31" s="13" t="n"/>
-      <c r="J31" s="13" t="n"/>
-      <c r="K31" s="13" t="n"/>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="14" t="n"/>
+      <c r="I31" s="14" t="n"/>
+      <c r="J31" s="14" t="n"/>
+      <c r="K31" s="14" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="13" t="n"/>
-      <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="13" t="n"/>
-      <c r="H32" s="13" t="n"/>
-      <c r="I32" s="13" t="n"/>
-      <c r="J32" s="13" t="n"/>
-      <c r="K32" s="13" t="n"/>
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="14" t="n"/>
+      <c r="H32" s="14" t="n"/>
+      <c r="I32" s="14" t="n"/>
+      <c r="J32" s="14" t="n"/>
+      <c r="K32" s="14" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="13" t="n"/>
-      <c r="H33" s="13" t="n"/>
-      <c r="I33" s="13" t="n"/>
-      <c r="J33" s="13" t="n"/>
-      <c r="K33" s="13" t="n"/>
+      <c r="B33" s="14" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="14" t="n"/>
+      <c r="E33" s="14" t="n"/>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="14" t="n"/>
+      <c r="H33" s="14" t="n"/>
+      <c r="I33" s="14" t="n"/>
+      <c r="J33" s="14" t="n"/>
+      <c r="K33" s="14" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B35" s="13" t="inlineStr">
         <is>
           <t>[ Top Products (Chart)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="C35" s="13" t="n"/>
-      <c r="D35" s="13" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="13" t="n"/>
-      <c r="H35" s="13" t="n"/>
-      <c r="I35" s="13" t="n"/>
-      <c r="J35" s="13" t="n"/>
-      <c r="K35" s="13" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="14" t="n"/>
+      <c r="F35" s="14" t="n"/>
+      <c r="G35" s="14" t="n"/>
+      <c r="H35" s="14" t="n"/>
+      <c r="I35" s="14" t="n"/>
+      <c r="J35" s="14" t="n"/>
+      <c r="K35" s="14" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="13" t="n"/>
-      <c r="D36" s="13" t="n"/>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="13" t="n"/>
-      <c r="H36" s="13" t="n"/>
-      <c r="I36" s="13" t="n"/>
-      <c r="J36" s="13" t="n"/>
-      <c r="K36" s="13" t="n"/>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="14" t="n"/>
+      <c r="F36" s="14" t="n"/>
+      <c r="G36" s="14" t="n"/>
+      <c r="H36" s="14" t="n"/>
+      <c r="I36" s="14" t="n"/>
+      <c r="J36" s="14" t="n"/>
+      <c r="K36" s="14" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="13" t="n"/>
-      <c r="C37" s="13" t="n"/>
-      <c r="D37" s="13" t="n"/>
-      <c r="E37" s="13" t="n"/>
-      <c r="F37" s="13" t="n"/>
-      <c r="G37" s="13" t="n"/>
-      <c r="H37" s="13" t="n"/>
-      <c r="I37" s="13" t="n"/>
-      <c r="J37" s="13" t="n"/>
-      <c r="K37" s="13" t="n"/>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="14" t="n"/>
+      <c r="G37" s="14" t="n"/>
+      <c r="H37" s="14" t="n"/>
+      <c r="I37" s="14" t="n"/>
+      <c r="J37" s="14" t="n"/>
+      <c r="K37" s="14" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="13" t="n"/>
-      <c r="C38" s="13" t="n"/>
-      <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
-      <c r="G38" s="13" t="n"/>
-      <c r="H38" s="13" t="n"/>
-      <c r="I38" s="13" t="n"/>
-      <c r="J38" s="13" t="n"/>
-      <c r="K38" s="13" t="n"/>
+      <c r="B38" s="14" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="14" t="n"/>
+      <c r="E38" s="14" t="n"/>
+      <c r="F38" s="14" t="n"/>
+      <c r="G38" s="14" t="n"/>
+      <c r="H38" s="14" t="n"/>
+      <c r="I38" s="14" t="n"/>
+      <c r="J38" s="14" t="n"/>
+      <c r="K38" s="14" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="13" t="n"/>
-      <c r="C39" s="13" t="n"/>
-      <c r="D39" s="13" t="n"/>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="n"/>
-      <c r="G39" s="13" t="n"/>
-      <c r="H39" s="13" t="n"/>
-      <c r="I39" s="13" t="n"/>
-      <c r="J39" s="13" t="n"/>
-      <c r="K39" s="13" t="n"/>
+      <c r="B39" s="14" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n"/>
+      <c r="E39" s="14" t="n"/>
+      <c r="F39" s="14" t="n"/>
+      <c r="G39" s="14" t="n"/>
+      <c r="H39" s="14" t="n"/>
+      <c r="I39" s="14" t="n"/>
+      <c r="J39" s="14" t="n"/>
+      <c r="K39" s="14" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="13" t="n"/>
-      <c r="C40" s="13" t="n"/>
-      <c r="D40" s="13" t="n"/>
-      <c r="E40" s="13" t="n"/>
-      <c r="F40" s="13" t="n"/>
-      <c r="G40" s="13" t="n"/>
-      <c r="H40" s="13" t="n"/>
-      <c r="I40" s="13" t="n"/>
-      <c r="J40" s="13" t="n"/>
-      <c r="K40" s="13" t="n"/>
+      <c r="B40" s="14" t="n"/>
+      <c r="C40" s="14" t="n"/>
+      <c r="D40" s="14" t="n"/>
+      <c r="E40" s="14" t="n"/>
+      <c r="F40" s="14" t="n"/>
+      <c r="G40" s="14" t="n"/>
+      <c r="H40" s="14" t="n"/>
+      <c r="I40" s="14" t="n"/>
+      <c r="J40" s="14" t="n"/>
+      <c r="K40" s="14" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="13" t="n"/>
-      <c r="C41" s="13" t="n"/>
-      <c r="D41" s="13" t="n"/>
-      <c r="E41" s="13" t="n"/>
-      <c r="F41" s="13" t="n"/>
-      <c r="G41" s="13" t="n"/>
-      <c r="H41" s="13" t="n"/>
-      <c r="I41" s="13" t="n"/>
-      <c r="J41" s="13" t="n"/>
-      <c r="K41" s="13" t="n"/>
+      <c r="B41" s="14" t="n"/>
+      <c r="C41" s="14" t="n"/>
+      <c r="D41" s="14" t="n"/>
+      <c r="E41" s="14" t="n"/>
+      <c r="F41" s="14" t="n"/>
+      <c r="G41" s="14" t="n"/>
+      <c r="H41" s="14" t="n"/>
+      <c r="I41" s="14" t="n"/>
+      <c r="J41" s="14" t="n"/>
+      <c r="K41" s="14" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="13" t="n"/>
-      <c r="C42" s="13" t="n"/>
-      <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
-      <c r="G42" s="13" t="n"/>
-      <c r="H42" s="13" t="n"/>
-      <c r="I42" s="13" t="n"/>
-      <c r="J42" s="13" t="n"/>
-      <c r="K42" s="13" t="n"/>
+      <c r="B42" s="14" t="n"/>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="14" t="n"/>
+      <c r="E42" s="14" t="n"/>
+      <c r="F42" s="14" t="n"/>
+      <c r="G42" s="14" t="n"/>
+      <c r="H42" s="14" t="n"/>
+      <c r="I42" s="14" t="n"/>
+      <c r="J42" s="14" t="n"/>
+      <c r="K42" s="14" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="12" t="inlineStr">
+      <c r="B44" s="13" t="inlineStr">
         <is>
           <t>[ Geography (Chart)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="C44" s="13" t="n"/>
-      <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
-      <c r="G44" s="13" t="n"/>
-      <c r="H44" s="13" t="n"/>
-      <c r="I44" s="13" t="n"/>
-      <c r="J44" s="13" t="n"/>
-      <c r="K44" s="13" t="n"/>
+      <c r="C44" s="14" t="n"/>
+      <c r="D44" s="14" t="n"/>
+      <c r="E44" s="14" t="n"/>
+      <c r="F44" s="14" t="n"/>
+      <c r="G44" s="14" t="n"/>
+      <c r="H44" s="14" t="n"/>
+      <c r="I44" s="14" t="n"/>
+      <c r="J44" s="14" t="n"/>
+      <c r="K44" s="14" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="13" t="n"/>
-      <c r="C45" s="13" t="n"/>
-      <c r="D45" s="13" t="n"/>
-      <c r="E45" s="13" t="n"/>
-      <c r="F45" s="13" t="n"/>
-      <c r="G45" s="13" t="n"/>
-      <c r="H45" s="13" t="n"/>
-      <c r="I45" s="13" t="n"/>
-      <c r="J45" s="13" t="n"/>
-      <c r="K45" s="13" t="n"/>
+      <c r="B45" s="14" t="n"/>
+      <c r="C45" s="14" t="n"/>
+      <c r="D45" s="14" t="n"/>
+      <c r="E45" s="14" t="n"/>
+      <c r="F45" s="14" t="n"/>
+      <c r="G45" s="14" t="n"/>
+      <c r="H45" s="14" t="n"/>
+      <c r="I45" s="14" t="n"/>
+      <c r="J45" s="14" t="n"/>
+      <c r="K45" s="14" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="13" t="n"/>
-      <c r="C46" s="13" t="n"/>
-      <c r="D46" s="13" t="n"/>
-      <c r="E46" s="13" t="n"/>
-      <c r="F46" s="13" t="n"/>
-      <c r="G46" s="13" t="n"/>
-      <c r="H46" s="13" t="n"/>
-      <c r="I46" s="13" t="n"/>
-      <c r="J46" s="13" t="n"/>
-      <c r="K46" s="13" t="n"/>
+      <c r="B46" s="14" t="n"/>
+      <c r="C46" s="14" t="n"/>
+      <c r="D46" s="14" t="n"/>
+      <c r="E46" s="14" t="n"/>
+      <c r="F46" s="14" t="n"/>
+      <c r="G46" s="14" t="n"/>
+      <c r="H46" s="14" t="n"/>
+      <c r="I46" s="14" t="n"/>
+      <c r="J46" s="14" t="n"/>
+      <c r="K46" s="14" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="13" t="n"/>
-      <c r="C47" s="13" t="n"/>
-      <c r="D47" s="13" t="n"/>
-      <c r="E47" s="13" t="n"/>
-      <c r="F47" s="13" t="n"/>
-      <c r="G47" s="13" t="n"/>
-      <c r="H47" s="13" t="n"/>
-      <c r="I47" s="13" t="n"/>
-      <c r="J47" s="13" t="n"/>
-      <c r="K47" s="13" t="n"/>
+      <c r="B47" s="14" t="n"/>
+      <c r="C47" s="14" t="n"/>
+      <c r="D47" s="14" t="n"/>
+      <c r="E47" s="14" t="n"/>
+      <c r="F47" s="14" t="n"/>
+      <c r="G47" s="14" t="n"/>
+      <c r="H47" s="14" t="n"/>
+      <c r="I47" s="14" t="n"/>
+      <c r="J47" s="14" t="n"/>
+      <c r="K47" s="14" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="13" t="n"/>
-      <c r="C48" s="13" t="n"/>
-      <c r="D48" s="13" t="n"/>
-      <c r="E48" s="13" t="n"/>
-      <c r="F48" s="13" t="n"/>
-      <c r="G48" s="13" t="n"/>
-      <c r="H48" s="13" t="n"/>
-      <c r="I48" s="13" t="n"/>
-      <c r="J48" s="13" t="n"/>
-      <c r="K48" s="13" t="n"/>
+      <c r="B48" s="14" t="n"/>
+      <c r="C48" s="14" t="n"/>
+      <c r="D48" s="14" t="n"/>
+      <c r="E48" s="14" t="n"/>
+      <c r="F48" s="14" t="n"/>
+      <c r="G48" s="14" t="n"/>
+      <c r="H48" s="14" t="n"/>
+      <c r="I48" s="14" t="n"/>
+      <c r="J48" s="14" t="n"/>
+      <c r="K48" s="14" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="13" t="n"/>
-      <c r="C49" s="13" t="n"/>
-      <c r="D49" s="13" t="n"/>
-      <c r="E49" s="13" t="n"/>
-      <c r="F49" s="13" t="n"/>
-      <c r="G49" s="13" t="n"/>
-      <c r="H49" s="13" t="n"/>
-      <c r="I49" s="13" t="n"/>
-      <c r="J49" s="13" t="n"/>
-      <c r="K49" s="13" t="n"/>
+      <c r="B49" s="14" t="n"/>
+      <c r="C49" s="14" t="n"/>
+      <c r="D49" s="14" t="n"/>
+      <c r="E49" s="14" t="n"/>
+      <c r="F49" s="14" t="n"/>
+      <c r="G49" s="14" t="n"/>
+      <c r="H49" s="14" t="n"/>
+      <c r="I49" s="14" t="n"/>
+      <c r="J49" s="14" t="n"/>
+      <c r="K49" s="14" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="13" t="n"/>
-      <c r="C50" s="13" t="n"/>
-      <c r="D50" s="13" t="n"/>
-      <c r="E50" s="13" t="n"/>
-      <c r="F50" s="13" t="n"/>
-      <c r="G50" s="13" t="n"/>
-      <c r="H50" s="13" t="n"/>
-      <c r="I50" s="13" t="n"/>
-      <c r="J50" s="13" t="n"/>
-      <c r="K50" s="13" t="n"/>
+      <c r="B50" s="14" t="n"/>
+      <c r="C50" s="14" t="n"/>
+      <c r="D50" s="14" t="n"/>
+      <c r="E50" s="14" t="n"/>
+      <c r="F50" s="14" t="n"/>
+      <c r="G50" s="14" t="n"/>
+      <c r="H50" s="14" t="n"/>
+      <c r="I50" s="14" t="n"/>
+      <c r="J50" s="14" t="n"/>
+      <c r="K50" s="14" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="13" t="n"/>
-      <c r="C51" s="13" t="n"/>
-      <c r="D51" s="13" t="n"/>
-      <c r="E51" s="13" t="n"/>
-      <c r="F51" s="13" t="n"/>
-      <c r="G51" s="13" t="n"/>
-      <c r="H51" s="13" t="n"/>
-      <c r="I51" s="13" t="n"/>
-      <c r="J51" s="13" t="n"/>
-      <c r="K51" s="13" t="n"/>
+      <c r="B51" s="14" t="n"/>
+      <c r="C51" s="14" t="n"/>
+      <c r="D51" s="14" t="n"/>
+      <c r="E51" s="14" t="n"/>
+      <c r="F51" s="14" t="n"/>
+      <c r="G51" s="14" t="n"/>
+      <c r="H51" s="14" t="n"/>
+      <c r="I51" s="14" t="n"/>
+      <c r="J51" s="14" t="n"/>
+      <c r="K51" s="14" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="9" t="inlineStr">
+      <c r="B54" s="10" t="inlineStr">
         <is>
           <t>DETAIL (PIVOTTABLES)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="12" t="inlineStr">
+      <c r="B55" s="13" t="inlineStr">
         <is>
           <t>[ Executive Summary (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="C55" s="13" t="n"/>
-      <c r="D55" s="13" t="n"/>
-      <c r="E55" s="13" t="n"/>
-      <c r="F55" s="13" t="n"/>
+      <c r="C55" s="14" t="n"/>
+      <c r="D55" s="14" t="n"/>
+      <c r="E55" s="14" t="n"/>
+      <c r="F55" s="14" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" s="13" t="n"/>
-      <c r="C56" s="13" t="n"/>
-      <c r="D56" s="13" t="n"/>
-      <c r="E56" s="13" t="n"/>
-      <c r="F56" s="13" t="n"/>
+      <c r="B56" s="14" t="n"/>
+      <c r="C56" s="14" t="n"/>
+      <c r="D56" s="14" t="n"/>
+      <c r="E56" s="14" t="n"/>
+      <c r="F56" s="14" t="n"/>
     </row>
     <row r="57">
-      <c r="B57" s="13" t="n"/>
-      <c r="C57" s="13" t="n"/>
-      <c r="D57" s="13" t="n"/>
-      <c r="E57" s="13" t="n"/>
-      <c r="F57" s="13" t="n"/>
+      <c r="B57" s="14" t="n"/>
+      <c r="C57" s="14" t="n"/>
+      <c r="D57" s="14" t="n"/>
+      <c r="E57" s="14" t="n"/>
+      <c r="F57" s="14" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="13" t="n"/>
-      <c r="C58" s="13" t="n"/>
-      <c r="D58" s="13" t="n"/>
-      <c r="E58" s="13" t="n"/>
-      <c r="F58" s="13" t="n"/>
+      <c r="B58" s="14" t="n"/>
+      <c r="C58" s="14" t="n"/>
+      <c r="D58" s="14" t="n"/>
+      <c r="E58" s="14" t="n"/>
+      <c r="F58" s="14" t="n"/>
     </row>
     <row r="59">
-      <c r="B59" s="13" t="n"/>
-      <c r="C59" s="13" t="n"/>
-      <c r="D59" s="13" t="n"/>
-      <c r="E59" s="13" t="n"/>
-      <c r="F59" s="13" t="n"/>
+      <c r="B59" s="14" t="n"/>
+      <c r="C59" s="14" t="n"/>
+      <c r="D59" s="14" t="n"/>
+      <c r="E59" s="14" t="n"/>
+      <c r="F59" s="14" t="n"/>
     </row>
     <row r="60">
-      <c r="B60" s="13" t="n"/>
-      <c r="C60" s="13" t="n"/>
-      <c r="D60" s="13" t="n"/>
-      <c r="E60" s="13" t="n"/>
-      <c r="F60" s="13" t="n"/>
+      <c r="B60" s="14" t="n"/>
+      <c r="C60" s="14" t="n"/>
+      <c r="D60" s="14" t="n"/>
+      <c r="E60" s="14" t="n"/>
+      <c r="F60" s="14" t="n"/>
     </row>
     <row r="61">
-      <c r="B61" s="13" t="n"/>
-      <c r="C61" s="13" t="n"/>
-      <c r="D61" s="13" t="n"/>
-      <c r="E61" s="13" t="n"/>
-      <c r="F61" s="13" t="n"/>
+      <c r="B61" s="14" t="n"/>
+      <c r="C61" s="14" t="n"/>
+      <c r="D61" s="14" t="n"/>
+      <c r="E61" s="14" t="n"/>
+      <c r="F61" s="14" t="n"/>
     </row>
     <row r="62">
-      <c r="B62" s="13" t="n"/>
-      <c r="C62" s="13" t="n"/>
-      <c r="D62" s="13" t="n"/>
-      <c r="E62" s="13" t="n"/>
-      <c r="F62" s="13" t="n"/>
+      <c r="B62" s="14" t="n"/>
+      <c r="C62" s="14" t="n"/>
+      <c r="D62" s="14" t="n"/>
+      <c r="E62" s="14" t="n"/>
+      <c r="F62" s="14" t="n"/>
     </row>
     <row r="63">
-      <c r="B63" s="13" t="n"/>
-      <c r="C63" s="13" t="n"/>
-      <c r="D63" s="13" t="n"/>
-      <c r="E63" s="13" t="n"/>
-      <c r="F63" s="13" t="n"/>
+      <c r="B63" s="14" t="n"/>
+      <c r="C63" s="14" t="n"/>
+      <c r="D63" s="14" t="n"/>
+      <c r="E63" s="14" t="n"/>
+      <c r="F63" s="14" t="n"/>
     </row>
     <row r="64">
-      <c r="B64" s="13" t="n"/>
-      <c r="C64" s="13" t="n"/>
-      <c r="D64" s="13" t="n"/>
-      <c r="E64" s="13" t="n"/>
-      <c r="F64" s="13" t="n"/>
+      <c r="B64" s="14" t="n"/>
+      <c r="C64" s="14" t="n"/>
+      <c r="D64" s="14" t="n"/>
+      <c r="E64" s="14" t="n"/>
+      <c r="F64" s="14" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -7146,6 +7444,286 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007F7F7F"/>
+    <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DIM_Collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PASSRESS MIS   |   Home ▸ DIM_Collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sheet Documentation  (use the  +  outline control at left to expand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Dimension table for the star schema — describes the 'Collection' entity that FACT_ tables relate to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Input tables</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Derived from the matching RAW_ staging table(s).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Output tables</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Related to FACT_ tables in the Data Model (one-to-many).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Relationships</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>One-to-many into the relevant FACT_ table(s) on this dimension's key column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Future data source</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Built from RAW_ staging data in Power Query — Phase 2/3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" hidden="1" outlineLevel="1"/>
+    <row r="10" ht="6" customHeight="1"/>
+    <row r="11" ht="18" customHeight="1">
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>CollectionKey</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>CollectionID</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>Handle</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
+  <mergeCells count="8">
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007F7F7F"/>
+    <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DIM_Parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PASSRESS MIS   |   Home ▸ DIM_Parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sheet Documentation  (use the  +  outline control at left to expand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Disconnected mirror of 15_Settings, used so DAX measures can reference configurable constants without creating a relationship into the star schema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Input tables</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>15_Settings (linked manually / via Power Query, Phase 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Output tables</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Referenced by DAX measures across all dashboards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Relationships</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>N/A — disconnected table by design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Future data source</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Manual link to 15_Settings — Phase 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" hidden="1" outlineLevel="1"/>
+    <row r="10" ht="6" customHeight="1"/>
+    <row r="11" ht="18" customHeight="1">
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>ParameterName</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>ParameterValue</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
+  <mergeCells count="8">
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00595959"/>
     <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
@@ -7254,92 +7832,92 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>OrderLineKey</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>OrderID</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>DateKey</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>ProductKey</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>CustomerKey</t>
         </is>
       </c>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>LocationKey</t>
         </is>
       </c>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="H11" s="19" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="I11" s="18" t="inlineStr">
+      <c r="I11" s="19" t="inlineStr">
         <is>
           <t>UnitPrice</t>
         </is>
       </c>
-      <c r="J11" s="18" t="inlineStr">
+      <c r="J11" s="19" t="inlineStr">
         <is>
           <t>GrossAmount</t>
         </is>
       </c>
-      <c r="K11" s="18" t="inlineStr">
+      <c r="K11" s="19" t="inlineStr">
         <is>
           <t>DiscountAmount</t>
         </is>
       </c>
-      <c r="L11" s="18" t="inlineStr">
+      <c r="L11" s="19" t="inlineStr">
         <is>
           <t>TaxAmount</t>
         </is>
       </c>
-      <c r="M11" s="18" t="inlineStr">
+      <c r="M11" s="19" t="inlineStr">
         <is>
           <t>NetAmount</t>
         </is>
       </c>
-      <c r="N11" s="18" t="inlineStr">
+      <c r="N11" s="19" t="inlineStr">
         <is>
           <t>UnitCost</t>
         </is>
       </c>
-      <c r="O11" s="18" t="inlineStr">
+      <c r="O11" s="19" t="inlineStr">
         <is>
           <t>COGS</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="19" t="n"/>
-      <c r="H12" s="19" t="n"/>
-      <c r="I12" s="19" t="n"/>
-      <c r="J12" s="19" t="n"/>
-      <c r="K12" s="19" t="n"/>
-      <c r="L12" s="19" t="n"/>
-      <c r="M12" s="19" t="n"/>
-      <c r="N12" s="19" t="n"/>
-      <c r="O12" s="19" t="n"/>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20" t="n"/>
+      <c r="I12" s="20" t="n"/>
+      <c r="J12" s="20" t="n"/>
+      <c r="K12" s="20" t="n"/>
+      <c r="L12" s="20" t="n"/>
+      <c r="M12" s="20" t="n"/>
+      <c r="N12" s="20" t="n"/>
+      <c r="O12" s="20" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -7360,7 +7938,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>
@@ -7462,38 +8040,38 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>RefundKey</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>OrderLineKey</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>DateKey</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>RefundAmount</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -7514,7 +8092,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>
@@ -7618,50 +8196,50 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>MovementKey</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>DateKey</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>ProductKey</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>LocationKey</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>MovementType</t>
         </is>
       </c>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>QuantityChange</t>
         </is>
       </c>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="H11" s="19" t="inlineStr">
         <is>
           <t>ResultingOnHand</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="19" t="n"/>
-      <c r="H12" s="19" t="n"/>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -7682,7 +8260,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>
@@ -7786,50 +8364,50 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>PaymentKey</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>OrderID</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>DateKey</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>PaymentMethod</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="H11" s="19" t="inlineStr">
         <is>
           <t>PresentmentAmount</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="19" t="n"/>
-      <c r="H12" s="19" t="n"/>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -7850,7 +8428,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>
@@ -7955,42 +8533,42 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>ExpenseKey</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>CostCenter</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="H11" s="15" t="inlineStr">
         <is>
           <t>PaymentMethod</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I11" s="15" t="inlineStr">
         <is>
           <t>EnteredBy</t>
         </is>
@@ -8025,7 +8603,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C55A11"/>
@@ -8130,56 +8708,56 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>RefreshID</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>RowsLoaded</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>RowsUpdated</t>
         </is>
       </c>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>Errors</t>
         </is>
       </c>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="H11" s="19" t="inlineStr">
         <is>
           <t>DurationSeconds</t>
         </is>
       </c>
-      <c r="I11" s="18" t="inlineStr">
+      <c r="I11" s="19" t="inlineStr">
         <is>
           <t>TriggeredBy</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="19" t="n"/>
-      <c r="H12" s="19" t="n"/>
-      <c r="I12" s="19" t="n"/>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20" t="n"/>
+      <c r="I12" s="20" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -8200,7 +8778,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C55A11"/>
@@ -8303,44 +8881,44 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>CheckID</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>CheckName</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>TableName</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>Details</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="19" t="n"/>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -8531,374 +9109,374 @@
       <c r="I13" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>TRENDS &amp; BREAKDOWNS</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>[ Sales Trend (Chart)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="13" t="n"/>
-      <c r="H17" s="13" t="n"/>
-      <c r="I17" s="13" t="n"/>
-      <c r="J17" s="13" t="n"/>
-      <c r="K17" s="13" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="14" t="n"/>
+      <c r="I17" s="14" t="n"/>
+      <c r="J17" s="14" t="n"/>
+      <c r="K17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="13" t="n"/>
-      <c r="H18" s="13" t="n"/>
-      <c r="I18" s="13" t="n"/>
-      <c r="J18" s="13" t="n"/>
-      <c r="K18" s="13" t="n"/>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="14" t="n"/>
+      <c r="I18" s="14" t="n"/>
+      <c r="J18" s="14" t="n"/>
+      <c r="K18" s="14" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="13" t="n"/>
-      <c r="H19" s="13" t="n"/>
-      <c r="I19" s="13" t="n"/>
-      <c r="J19" s="13" t="n"/>
-      <c r="K19" s="13" t="n"/>
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="14" t="n"/>
+      <c r="E19" s="14" t="n"/>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="14" t="n"/>
+      <c r="H19" s="14" t="n"/>
+      <c r="I19" s="14" t="n"/>
+      <c r="J19" s="14" t="n"/>
+      <c r="K19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="13" t="n"/>
-      <c r="H20" s="13" t="n"/>
-      <c r="I20" s="13" t="n"/>
-      <c r="J20" s="13" t="n"/>
-      <c r="K20" s="13" t="n"/>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="14" t="n"/>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="14" t="n"/>
+      <c r="H20" s="14" t="n"/>
+      <c r="I20" s="14" t="n"/>
+      <c r="J20" s="14" t="n"/>
+      <c r="K20" s="14" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="13" t="n"/>
-      <c r="H21" s="13" t="n"/>
-      <c r="I21" s="13" t="n"/>
-      <c r="J21" s="13" t="n"/>
-      <c r="K21" s="13" t="n"/>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="14" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="14" t="n"/>
+      <c r="H21" s="14" t="n"/>
+      <c r="I21" s="14" t="n"/>
+      <c r="J21" s="14" t="n"/>
+      <c r="K21" s="14" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="13" t="n"/>
-      <c r="H22" s="13" t="n"/>
-      <c r="I22" s="13" t="n"/>
-      <c r="J22" s="13" t="n"/>
-      <c r="K22" s="13" t="n"/>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="14" t="n"/>
+      <c r="I22" s="14" t="n"/>
+      <c r="J22" s="14" t="n"/>
+      <c r="K22" s="14" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="13" t="n"/>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="13" t="n"/>
-      <c r="J23" s="13" t="n"/>
-      <c r="K23" s="13" t="n"/>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="14" t="n"/>
+      <c r="I23" s="14" t="n"/>
+      <c r="J23" s="14" t="n"/>
+      <c r="K23" s="14" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="13" t="n"/>
-      <c r="H24" s="13" t="n"/>
-      <c r="I24" s="13" t="n"/>
-      <c r="J24" s="13" t="n"/>
-      <c r="K24" s="13" t="n"/>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="14" t="n"/>
+      <c r="I24" s="14" t="n"/>
+      <c r="J24" s="14" t="n"/>
+      <c r="K24" s="14" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>DETAIL (PIVOTTABLES)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>[ Sales by Date (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="C28" s="13" t="n"/>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="13" t="inlineStr">
         <is>
           <t>[ Sales by Product (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="H28" s="13" t="n"/>
-      <c r="I28" s="13" t="n"/>
-      <c r="J28" s="13" t="n"/>
-      <c r="K28" s="13" t="n"/>
+      <c r="H28" s="14" t="n"/>
+      <c r="I28" s="14" t="n"/>
+      <c r="J28" s="14" t="n"/>
+      <c r="K28" s="14" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="13" t="n"/>
-      <c r="H29" s="13" t="n"/>
-      <c r="I29" s="13" t="n"/>
-      <c r="J29" s="13" t="n"/>
-      <c r="K29" s="13" t="n"/>
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="14" t="n"/>
+      <c r="H29" s="14" t="n"/>
+      <c r="I29" s="14" t="n"/>
+      <c r="J29" s="14" t="n"/>
+      <c r="K29" s="14" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="13" t="n"/>
-      <c r="H30" s="13" t="n"/>
-      <c r="I30" s="13" t="n"/>
-      <c r="J30" s="13" t="n"/>
-      <c r="K30" s="13" t="n"/>
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="14" t="n"/>
+      <c r="I30" s="14" t="n"/>
+      <c r="J30" s="14" t="n"/>
+      <c r="K30" s="14" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="13" t="n"/>
-      <c r="C31" s="13" t="n"/>
-      <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
-      <c r="G31" s="13" t="n"/>
-      <c r="H31" s="13" t="n"/>
-      <c r="I31" s="13" t="n"/>
-      <c r="J31" s="13" t="n"/>
-      <c r="K31" s="13" t="n"/>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="14" t="n"/>
+      <c r="I31" s="14" t="n"/>
+      <c r="J31" s="14" t="n"/>
+      <c r="K31" s="14" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="13" t="n"/>
-      <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="13" t="n"/>
-      <c r="H32" s="13" t="n"/>
-      <c r="I32" s="13" t="n"/>
-      <c r="J32" s="13" t="n"/>
-      <c r="K32" s="13" t="n"/>
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="14" t="n"/>
+      <c r="H32" s="14" t="n"/>
+      <c r="I32" s="14" t="n"/>
+      <c r="J32" s="14" t="n"/>
+      <c r="K32" s="14" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="13" t="n"/>
-      <c r="H33" s="13" t="n"/>
-      <c r="I33" s="13" t="n"/>
-      <c r="J33" s="13" t="n"/>
-      <c r="K33" s="13" t="n"/>
+      <c r="B33" s="14" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="14" t="n"/>
+      <c r="E33" s="14" t="n"/>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="14" t="n"/>
+      <c r="H33" s="14" t="n"/>
+      <c r="I33" s="14" t="n"/>
+      <c r="J33" s="14" t="n"/>
+      <c r="K33" s="14" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="13" t="n"/>
-      <c r="C34" s="13" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="13" t="n"/>
-      <c r="H34" s="13" t="n"/>
-      <c r="I34" s="13" t="n"/>
-      <c r="J34" s="13" t="n"/>
-      <c r="K34" s="13" t="n"/>
+      <c r="B34" s="14" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="14" t="n"/>
+      <c r="E34" s="14" t="n"/>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="14" t="n"/>
+      <c r="H34" s="14" t="n"/>
+      <c r="I34" s="14" t="n"/>
+      <c r="J34" s="14" t="n"/>
+      <c r="K34" s="14" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="13" t="n"/>
-      <c r="C35" s="13" t="n"/>
-      <c r="D35" s="13" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="13" t="n"/>
-      <c r="H35" s="13" t="n"/>
-      <c r="I35" s="13" t="n"/>
-      <c r="J35" s="13" t="n"/>
-      <c r="K35" s="13" t="n"/>
+      <c r="B35" s="14" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="14" t="n"/>
+      <c r="F35" s="14" t="n"/>
+      <c r="G35" s="14" t="n"/>
+      <c r="H35" s="14" t="n"/>
+      <c r="I35" s="14" t="n"/>
+      <c r="J35" s="14" t="n"/>
+      <c r="K35" s="14" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="13" t="n"/>
-      <c r="D36" s="13" t="n"/>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="13" t="n"/>
-      <c r="H36" s="13" t="n"/>
-      <c r="I36" s="13" t="n"/>
-      <c r="J36" s="13" t="n"/>
-      <c r="K36" s="13" t="n"/>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="14" t="n"/>
+      <c r="F36" s="14" t="n"/>
+      <c r="G36" s="14" t="n"/>
+      <c r="H36" s="14" t="n"/>
+      <c r="I36" s="14" t="n"/>
+      <c r="J36" s="14" t="n"/>
+      <c r="K36" s="14" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="13" t="n"/>
-      <c r="C37" s="13" t="n"/>
-      <c r="D37" s="13" t="n"/>
-      <c r="E37" s="13" t="n"/>
-      <c r="F37" s="13" t="n"/>
-      <c r="G37" s="13" t="n"/>
-      <c r="H37" s="13" t="n"/>
-      <c r="I37" s="13" t="n"/>
-      <c r="J37" s="13" t="n"/>
-      <c r="K37" s="13" t="n"/>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="14" t="n"/>
+      <c r="G37" s="14" t="n"/>
+      <c r="H37" s="14" t="n"/>
+      <c r="I37" s="14" t="n"/>
+      <c r="J37" s="14" t="n"/>
+      <c r="K37" s="14" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B39" s="13" t="inlineStr">
         <is>
           <t>[ Sales by Collection (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="C39" s="13" t="n"/>
-      <c r="D39" s="13" t="n"/>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="n"/>
-      <c r="G39" s="12" t="inlineStr">
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n"/>
+      <c r="E39" s="14" t="n"/>
+      <c r="F39" s="14" t="n"/>
+      <c r="G39" s="13" t="inlineStr">
         <is>
           <t>[ Order List (Table)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="H39" s="13" t="n"/>
-      <c r="I39" s="13" t="n"/>
-      <c r="J39" s="13" t="n"/>
-      <c r="K39" s="13" t="n"/>
+      <c r="H39" s="14" t="n"/>
+      <c r="I39" s="14" t="n"/>
+      <c r="J39" s="14" t="n"/>
+      <c r="K39" s="14" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="13" t="n"/>
-      <c r="C40" s="13" t="n"/>
-      <c r="D40" s="13" t="n"/>
-      <c r="E40" s="13" t="n"/>
-      <c r="F40" s="13" t="n"/>
-      <c r="G40" s="13" t="n"/>
-      <c r="H40" s="13" t="n"/>
-      <c r="I40" s="13" t="n"/>
-      <c r="J40" s="13" t="n"/>
-      <c r="K40" s="13" t="n"/>
+      <c r="B40" s="14" t="n"/>
+      <c r="C40" s="14" t="n"/>
+      <c r="D40" s="14" t="n"/>
+      <c r="E40" s="14" t="n"/>
+      <c r="F40" s="14" t="n"/>
+      <c r="G40" s="14" t="n"/>
+      <c r="H40" s="14" t="n"/>
+      <c r="I40" s="14" t="n"/>
+      <c r="J40" s="14" t="n"/>
+      <c r="K40" s="14" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="13" t="n"/>
-      <c r="C41" s="13" t="n"/>
-      <c r="D41" s="13" t="n"/>
-      <c r="E41" s="13" t="n"/>
-      <c r="F41" s="13" t="n"/>
-      <c r="G41" s="13" t="n"/>
-      <c r="H41" s="13" t="n"/>
-      <c r="I41" s="13" t="n"/>
-      <c r="J41" s="13" t="n"/>
-      <c r="K41" s="13" t="n"/>
+      <c r="B41" s="14" t="n"/>
+      <c r="C41" s="14" t="n"/>
+      <c r="D41" s="14" t="n"/>
+      <c r="E41" s="14" t="n"/>
+      <c r="F41" s="14" t="n"/>
+      <c r="G41" s="14" t="n"/>
+      <c r="H41" s="14" t="n"/>
+      <c r="I41" s="14" t="n"/>
+      <c r="J41" s="14" t="n"/>
+      <c r="K41" s="14" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="13" t="n"/>
-      <c r="C42" s="13" t="n"/>
-      <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
-      <c r="G42" s="13" t="n"/>
-      <c r="H42" s="13" t="n"/>
-      <c r="I42" s="13" t="n"/>
-      <c r="J42" s="13" t="n"/>
-      <c r="K42" s="13" t="n"/>
+      <c r="B42" s="14" t="n"/>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="14" t="n"/>
+      <c r="E42" s="14" t="n"/>
+      <c r="F42" s="14" t="n"/>
+      <c r="G42" s="14" t="n"/>
+      <c r="H42" s="14" t="n"/>
+      <c r="I42" s="14" t="n"/>
+      <c r="J42" s="14" t="n"/>
+      <c r="K42" s="14" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="13" t="n"/>
-      <c r="C43" s="13" t="n"/>
-      <c r="D43" s="13" t="n"/>
-      <c r="E43" s="13" t="n"/>
-      <c r="F43" s="13" t="n"/>
-      <c r="G43" s="13" t="n"/>
-      <c r="H43" s="13" t="n"/>
-      <c r="I43" s="13" t="n"/>
-      <c r="J43" s="13" t="n"/>
-      <c r="K43" s="13" t="n"/>
+      <c r="B43" s="14" t="n"/>
+      <c r="C43" s="14" t="n"/>
+      <c r="D43" s="14" t="n"/>
+      <c r="E43" s="14" t="n"/>
+      <c r="F43" s="14" t="n"/>
+      <c r="G43" s="14" t="n"/>
+      <c r="H43" s="14" t="n"/>
+      <c r="I43" s="14" t="n"/>
+      <c r="J43" s="14" t="n"/>
+      <c r="K43" s="14" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="13" t="n"/>
-      <c r="C44" s="13" t="n"/>
-      <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
-      <c r="G44" s="13" t="n"/>
-      <c r="H44" s="13" t="n"/>
-      <c r="I44" s="13" t="n"/>
-      <c r="J44" s="13" t="n"/>
-      <c r="K44" s="13" t="n"/>
+      <c r="B44" s="14" t="n"/>
+      <c r="C44" s="14" t="n"/>
+      <c r="D44" s="14" t="n"/>
+      <c r="E44" s="14" t="n"/>
+      <c r="F44" s="14" t="n"/>
+      <c r="G44" s="14" t="n"/>
+      <c r="H44" s="14" t="n"/>
+      <c r="I44" s="14" t="n"/>
+      <c r="J44" s="14" t="n"/>
+      <c r="K44" s="14" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="13" t="n"/>
-      <c r="C45" s="13" t="n"/>
-      <c r="D45" s="13" t="n"/>
-      <c r="E45" s="13" t="n"/>
-      <c r="F45" s="13" t="n"/>
-      <c r="G45" s="13" t="n"/>
-      <c r="H45" s="13" t="n"/>
-      <c r="I45" s="13" t="n"/>
-      <c r="J45" s="13" t="n"/>
-      <c r="K45" s="13" t="n"/>
+      <c r="B45" s="14" t="n"/>
+      <c r="C45" s="14" t="n"/>
+      <c r="D45" s="14" t="n"/>
+      <c r="E45" s="14" t="n"/>
+      <c r="F45" s="14" t="n"/>
+      <c r="G45" s="14" t="n"/>
+      <c r="H45" s="14" t="n"/>
+      <c r="I45" s="14" t="n"/>
+      <c r="J45" s="14" t="n"/>
+      <c r="K45" s="14" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="13" t="n"/>
-      <c r="C46" s="13" t="n"/>
-      <c r="D46" s="13" t="n"/>
-      <c r="E46" s="13" t="n"/>
-      <c r="F46" s="13" t="n"/>
-      <c r="G46" s="13" t="n"/>
-      <c r="H46" s="13" t="n"/>
-      <c r="I46" s="13" t="n"/>
-      <c r="J46" s="13" t="n"/>
-      <c r="K46" s="13" t="n"/>
+      <c r="B46" s="14" t="n"/>
+      <c r="C46" s="14" t="n"/>
+      <c r="D46" s="14" t="n"/>
+      <c r="E46" s="14" t="n"/>
+      <c r="F46" s="14" t="n"/>
+      <c r="G46" s="14" t="n"/>
+      <c r="H46" s="14" t="n"/>
+      <c r="I46" s="14" t="n"/>
+      <c r="J46" s="14" t="n"/>
+      <c r="K46" s="14" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="13" t="n"/>
-      <c r="C47" s="13" t="n"/>
-      <c r="D47" s="13" t="n"/>
-      <c r="E47" s="13" t="n"/>
-      <c r="F47" s="13" t="n"/>
-      <c r="G47" s="13" t="n"/>
-      <c r="H47" s="13" t="n"/>
-      <c r="I47" s="13" t="n"/>
-      <c r="J47" s="13" t="n"/>
-      <c r="K47" s="13" t="n"/>
+      <c r="B47" s="14" t="n"/>
+      <c r="C47" s="14" t="n"/>
+      <c r="D47" s="14" t="n"/>
+      <c r="E47" s="14" t="n"/>
+      <c r="F47" s="14" t="n"/>
+      <c r="G47" s="14" t="n"/>
+      <c r="H47" s="14" t="n"/>
+      <c r="I47" s="14" t="n"/>
+      <c r="J47" s="14" t="n"/>
+      <c r="K47" s="14" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="13" t="n"/>
-      <c r="C48" s="13" t="n"/>
-      <c r="D48" s="13" t="n"/>
-      <c r="E48" s="13" t="n"/>
-      <c r="F48" s="13" t="n"/>
-      <c r="G48" s="13" t="n"/>
-      <c r="H48" s="13" t="n"/>
-      <c r="I48" s="13" t="n"/>
-      <c r="J48" s="13" t="n"/>
-      <c r="K48" s="13" t="n"/>
+      <c r="B48" s="14" t="n"/>
+      <c r="C48" s="14" t="n"/>
+      <c r="D48" s="14" t="n"/>
+      <c r="E48" s="14" t="n"/>
+      <c r="F48" s="14" t="n"/>
+      <c r="G48" s="14" t="n"/>
+      <c r="H48" s="14" t="n"/>
+      <c r="I48" s="14" t="n"/>
+      <c r="J48" s="14" t="n"/>
+      <c r="K48" s="14" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -9099,246 +9677,246 @@
       <c r="I13" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>TRENDS &amp; BREAKDOWNS</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>[ Top 10 Products (Chart)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="13" t="n"/>
-      <c r="H17" s="13" t="n"/>
-      <c r="I17" s="13" t="n"/>
-      <c r="J17" s="13" t="n"/>
-      <c r="K17" s="13" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="14" t="n"/>
+      <c r="I17" s="14" t="n"/>
+      <c r="J17" s="14" t="n"/>
+      <c r="K17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="13" t="n"/>
-      <c r="H18" s="13" t="n"/>
-      <c r="I18" s="13" t="n"/>
-      <c r="J18" s="13" t="n"/>
-      <c r="K18" s="13" t="n"/>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="14" t="n"/>
+      <c r="I18" s="14" t="n"/>
+      <c r="J18" s="14" t="n"/>
+      <c r="K18" s="14" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="13" t="n"/>
-      <c r="H19" s="13" t="n"/>
-      <c r="I19" s="13" t="n"/>
-      <c r="J19" s="13" t="n"/>
-      <c r="K19" s="13" t="n"/>
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="14" t="n"/>
+      <c r="E19" s="14" t="n"/>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="14" t="n"/>
+      <c r="H19" s="14" t="n"/>
+      <c r="I19" s="14" t="n"/>
+      <c r="J19" s="14" t="n"/>
+      <c r="K19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="13" t="n"/>
-      <c r="H20" s="13" t="n"/>
-      <c r="I20" s="13" t="n"/>
-      <c r="J20" s="13" t="n"/>
-      <c r="K20" s="13" t="n"/>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="14" t="n"/>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="14" t="n"/>
+      <c r="H20" s="14" t="n"/>
+      <c r="I20" s="14" t="n"/>
+      <c r="J20" s="14" t="n"/>
+      <c r="K20" s="14" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="13" t="n"/>
-      <c r="H21" s="13" t="n"/>
-      <c r="I21" s="13" t="n"/>
-      <c r="J21" s="13" t="n"/>
-      <c r="K21" s="13" t="n"/>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="14" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="14" t="n"/>
+      <c r="H21" s="14" t="n"/>
+      <c r="I21" s="14" t="n"/>
+      <c r="J21" s="14" t="n"/>
+      <c r="K21" s="14" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="13" t="n"/>
-      <c r="H22" s="13" t="n"/>
-      <c r="I22" s="13" t="n"/>
-      <c r="J22" s="13" t="n"/>
-      <c r="K22" s="13" t="n"/>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="14" t="n"/>
+      <c r="I22" s="14" t="n"/>
+      <c r="J22" s="14" t="n"/>
+      <c r="K22" s="14" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="13" t="n"/>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="13" t="n"/>
-      <c r="J23" s="13" t="n"/>
-      <c r="K23" s="13" t="n"/>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="14" t="n"/>
+      <c r="I23" s="14" t="n"/>
+      <c r="J23" s="14" t="n"/>
+      <c r="K23" s="14" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="13" t="n"/>
-      <c r="H24" s="13" t="n"/>
-      <c r="I24" s="13" t="n"/>
-      <c r="J24" s="13" t="n"/>
-      <c r="K24" s="13" t="n"/>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="14" t="n"/>
+      <c r="I24" s="14" t="n"/>
+      <c r="J24" s="14" t="n"/>
+      <c r="K24" s="14" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>DETAIL (PIVOTTABLES)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>[ Product Margin (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="C28" s="13" t="n"/>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="13" t="inlineStr">
         <is>
           <t>[ Variant Detail (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="H28" s="13" t="n"/>
-      <c r="I28" s="13" t="n"/>
-      <c r="J28" s="13" t="n"/>
-      <c r="K28" s="13" t="n"/>
+      <c r="H28" s="14" t="n"/>
+      <c r="I28" s="14" t="n"/>
+      <c r="J28" s="14" t="n"/>
+      <c r="K28" s="14" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="13" t="n"/>
-      <c r="H29" s="13" t="n"/>
-      <c r="I29" s="13" t="n"/>
-      <c r="J29" s="13" t="n"/>
-      <c r="K29" s="13" t="n"/>
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="14" t="n"/>
+      <c r="H29" s="14" t="n"/>
+      <c r="I29" s="14" t="n"/>
+      <c r="J29" s="14" t="n"/>
+      <c r="K29" s="14" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="13" t="n"/>
-      <c r="H30" s="13" t="n"/>
-      <c r="I30" s="13" t="n"/>
-      <c r="J30" s="13" t="n"/>
-      <c r="K30" s="13" t="n"/>
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="14" t="n"/>
+      <c r="I30" s="14" t="n"/>
+      <c r="J30" s="14" t="n"/>
+      <c r="K30" s="14" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="13" t="n"/>
-      <c r="C31" s="13" t="n"/>
-      <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
-      <c r="G31" s="13" t="n"/>
-      <c r="H31" s="13" t="n"/>
-      <c r="I31" s="13" t="n"/>
-      <c r="J31" s="13" t="n"/>
-      <c r="K31" s="13" t="n"/>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="14" t="n"/>
+      <c r="I31" s="14" t="n"/>
+      <c r="J31" s="14" t="n"/>
+      <c r="K31" s="14" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="13" t="n"/>
-      <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="13" t="n"/>
-      <c r="H32" s="13" t="n"/>
-      <c r="I32" s="13" t="n"/>
-      <c r="J32" s="13" t="n"/>
-      <c r="K32" s="13" t="n"/>
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="14" t="n"/>
+      <c r="H32" s="14" t="n"/>
+      <c r="I32" s="14" t="n"/>
+      <c r="J32" s="14" t="n"/>
+      <c r="K32" s="14" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="13" t="n"/>
-      <c r="H33" s="13" t="n"/>
-      <c r="I33" s="13" t="n"/>
-      <c r="J33" s="13" t="n"/>
-      <c r="K33" s="13" t="n"/>
+      <c r="B33" s="14" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="14" t="n"/>
+      <c r="E33" s="14" t="n"/>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="14" t="n"/>
+      <c r="H33" s="14" t="n"/>
+      <c r="I33" s="14" t="n"/>
+      <c r="J33" s="14" t="n"/>
+      <c r="K33" s="14" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="13" t="n"/>
-      <c r="C34" s="13" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="13" t="n"/>
-      <c r="H34" s="13" t="n"/>
-      <c r="I34" s="13" t="n"/>
-      <c r="J34" s="13" t="n"/>
-      <c r="K34" s="13" t="n"/>
+      <c r="B34" s="14" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="14" t="n"/>
+      <c r="E34" s="14" t="n"/>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="14" t="n"/>
+      <c r="H34" s="14" t="n"/>
+      <c r="I34" s="14" t="n"/>
+      <c r="J34" s="14" t="n"/>
+      <c r="K34" s="14" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="13" t="n"/>
-      <c r="C35" s="13" t="n"/>
-      <c r="D35" s="13" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="13" t="n"/>
-      <c r="H35" s="13" t="n"/>
-      <c r="I35" s="13" t="n"/>
-      <c r="J35" s="13" t="n"/>
-      <c r="K35" s="13" t="n"/>
+      <c r="B35" s="14" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="14" t="n"/>
+      <c r="F35" s="14" t="n"/>
+      <c r="G35" s="14" t="n"/>
+      <c r="H35" s="14" t="n"/>
+      <c r="I35" s="14" t="n"/>
+      <c r="J35" s="14" t="n"/>
+      <c r="K35" s="14" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="13" t="n"/>
-      <c r="D36" s="13" t="n"/>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="13" t="n"/>
-      <c r="H36" s="13" t="n"/>
-      <c r="I36" s="13" t="n"/>
-      <c r="J36" s="13" t="n"/>
-      <c r="K36" s="13" t="n"/>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="14" t="n"/>
+      <c r="F36" s="14" t="n"/>
+      <c r="G36" s="14" t="n"/>
+      <c r="H36" s="14" t="n"/>
+      <c r="I36" s="14" t="n"/>
+      <c r="J36" s="14" t="n"/>
+      <c r="K36" s="14" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="13" t="n"/>
-      <c r="C37" s="13" t="n"/>
-      <c r="D37" s="13" t="n"/>
-      <c r="E37" s="13" t="n"/>
-      <c r="F37" s="13" t="n"/>
-      <c r="G37" s="13" t="n"/>
-      <c r="H37" s="13" t="n"/>
-      <c r="I37" s="13" t="n"/>
-      <c r="J37" s="13" t="n"/>
-      <c r="K37" s="13" t="n"/>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="14" t="n"/>
+      <c r="G37" s="14" t="n"/>
+      <c r="H37" s="14" t="n"/>
+      <c r="I37" s="14" t="n"/>
+      <c r="J37" s="14" t="n"/>
+      <c r="K37" s="14" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -9537,320 +10115,320 @@
       <c r="I13" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>TRENDS &amp; BREAKDOWNS</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>[ Cohort Trend (Chart)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="13" t="n"/>
-      <c r="H17" s="13" t="n"/>
-      <c r="I17" s="13" t="n"/>
-      <c r="J17" s="13" t="n"/>
-      <c r="K17" s="13" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="14" t="n"/>
+      <c r="I17" s="14" t="n"/>
+      <c r="J17" s="14" t="n"/>
+      <c r="K17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="13" t="n"/>
-      <c r="H18" s="13" t="n"/>
-      <c r="I18" s="13" t="n"/>
-      <c r="J18" s="13" t="n"/>
-      <c r="K18" s="13" t="n"/>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="14" t="n"/>
+      <c r="I18" s="14" t="n"/>
+      <c r="J18" s="14" t="n"/>
+      <c r="K18" s="14" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="13" t="n"/>
-      <c r="H19" s="13" t="n"/>
-      <c r="I19" s="13" t="n"/>
-      <c r="J19" s="13" t="n"/>
-      <c r="K19" s="13" t="n"/>
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="14" t="n"/>
+      <c r="E19" s="14" t="n"/>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="14" t="n"/>
+      <c r="H19" s="14" t="n"/>
+      <c r="I19" s="14" t="n"/>
+      <c r="J19" s="14" t="n"/>
+      <c r="K19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="13" t="n"/>
-      <c r="H20" s="13" t="n"/>
-      <c r="I20" s="13" t="n"/>
-      <c r="J20" s="13" t="n"/>
-      <c r="K20" s="13" t="n"/>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="14" t="n"/>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="14" t="n"/>
+      <c r="H20" s="14" t="n"/>
+      <c r="I20" s="14" t="n"/>
+      <c r="J20" s="14" t="n"/>
+      <c r="K20" s="14" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="13" t="n"/>
-      <c r="H21" s="13" t="n"/>
-      <c r="I21" s="13" t="n"/>
-      <c r="J21" s="13" t="n"/>
-      <c r="K21" s="13" t="n"/>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="14" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="14" t="n"/>
+      <c r="H21" s="14" t="n"/>
+      <c r="I21" s="14" t="n"/>
+      <c r="J21" s="14" t="n"/>
+      <c r="K21" s="14" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="13" t="n"/>
-      <c r="H22" s="13" t="n"/>
-      <c r="I22" s="13" t="n"/>
-      <c r="J22" s="13" t="n"/>
-      <c r="K22" s="13" t="n"/>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="14" t="n"/>
+      <c r="I22" s="14" t="n"/>
+      <c r="J22" s="14" t="n"/>
+      <c r="K22" s="14" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="13" t="n"/>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="13" t="n"/>
-      <c r="J23" s="13" t="n"/>
-      <c r="K23" s="13" t="n"/>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="14" t="n"/>
+      <c r="I23" s="14" t="n"/>
+      <c r="J23" s="14" t="n"/>
+      <c r="K23" s="14" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="13" t="n"/>
-      <c r="H24" s="13" t="n"/>
-      <c r="I24" s="13" t="n"/>
-      <c r="J24" s="13" t="n"/>
-      <c r="K24" s="13" t="n"/>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="14" t="n"/>
+      <c r="I24" s="14" t="n"/>
+      <c r="J24" s="14" t="n"/>
+      <c r="K24" s="14" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>DETAIL (PIVOTTABLES)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>[ Cohort Table (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="C28" s="13" t="n"/>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="13" t="inlineStr">
         <is>
           <t>[ Top Customers (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="H28" s="13" t="n"/>
-      <c r="I28" s="13" t="n"/>
-      <c r="J28" s="13" t="n"/>
-      <c r="K28" s="13" t="n"/>
+      <c r="H28" s="14" t="n"/>
+      <c r="I28" s="14" t="n"/>
+      <c r="J28" s="14" t="n"/>
+      <c r="K28" s="14" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="13" t="n"/>
-      <c r="H29" s="13" t="n"/>
-      <c r="I29" s="13" t="n"/>
-      <c r="J29" s="13" t="n"/>
-      <c r="K29" s="13" t="n"/>
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="14" t="n"/>
+      <c r="H29" s="14" t="n"/>
+      <c r="I29" s="14" t="n"/>
+      <c r="J29" s="14" t="n"/>
+      <c r="K29" s="14" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="13" t="n"/>
-      <c r="H30" s="13" t="n"/>
-      <c r="I30" s="13" t="n"/>
-      <c r="J30" s="13" t="n"/>
-      <c r="K30" s="13" t="n"/>
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="14" t="n"/>
+      <c r="I30" s="14" t="n"/>
+      <c r="J30" s="14" t="n"/>
+      <c r="K30" s="14" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="13" t="n"/>
-      <c r="C31" s="13" t="n"/>
-      <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
-      <c r="G31" s="13" t="n"/>
-      <c r="H31" s="13" t="n"/>
-      <c r="I31" s="13" t="n"/>
-      <c r="J31" s="13" t="n"/>
-      <c r="K31" s="13" t="n"/>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="14" t="n"/>
+      <c r="I31" s="14" t="n"/>
+      <c r="J31" s="14" t="n"/>
+      <c r="K31" s="14" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="13" t="n"/>
-      <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="13" t="n"/>
-      <c r="H32" s="13" t="n"/>
-      <c r="I32" s="13" t="n"/>
-      <c r="J32" s="13" t="n"/>
-      <c r="K32" s="13" t="n"/>
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="14" t="n"/>
+      <c r="H32" s="14" t="n"/>
+      <c r="I32" s="14" t="n"/>
+      <c r="J32" s="14" t="n"/>
+      <c r="K32" s="14" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="13" t="n"/>
-      <c r="H33" s="13" t="n"/>
-      <c r="I33" s="13" t="n"/>
-      <c r="J33" s="13" t="n"/>
-      <c r="K33" s="13" t="n"/>
+      <c r="B33" s="14" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="14" t="n"/>
+      <c r="E33" s="14" t="n"/>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="14" t="n"/>
+      <c r="H33" s="14" t="n"/>
+      <c r="I33" s="14" t="n"/>
+      <c r="J33" s="14" t="n"/>
+      <c r="K33" s="14" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="13" t="n"/>
-      <c r="C34" s="13" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="13" t="n"/>
-      <c r="H34" s="13" t="n"/>
-      <c r="I34" s="13" t="n"/>
-      <c r="J34" s="13" t="n"/>
-      <c r="K34" s="13" t="n"/>
+      <c r="B34" s="14" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="14" t="n"/>
+      <c r="E34" s="14" t="n"/>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="14" t="n"/>
+      <c r="H34" s="14" t="n"/>
+      <c r="I34" s="14" t="n"/>
+      <c r="J34" s="14" t="n"/>
+      <c r="K34" s="14" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="13" t="n"/>
-      <c r="C35" s="13" t="n"/>
-      <c r="D35" s="13" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="13" t="n"/>
-      <c r="H35" s="13" t="n"/>
-      <c r="I35" s="13" t="n"/>
-      <c r="J35" s="13" t="n"/>
-      <c r="K35" s="13" t="n"/>
+      <c r="B35" s="14" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="14" t="n"/>
+      <c r="F35" s="14" t="n"/>
+      <c r="G35" s="14" t="n"/>
+      <c r="H35" s="14" t="n"/>
+      <c r="I35" s="14" t="n"/>
+      <c r="J35" s="14" t="n"/>
+      <c r="K35" s="14" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="13" t="n"/>
-      <c r="D36" s="13" t="n"/>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="13" t="n"/>
-      <c r="H36" s="13" t="n"/>
-      <c r="I36" s="13" t="n"/>
-      <c r="J36" s="13" t="n"/>
-      <c r="K36" s="13" t="n"/>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="14" t="n"/>
+      <c r="F36" s="14" t="n"/>
+      <c r="G36" s="14" t="n"/>
+      <c r="H36" s="14" t="n"/>
+      <c r="I36" s="14" t="n"/>
+      <c r="J36" s="14" t="n"/>
+      <c r="K36" s="14" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="13" t="n"/>
-      <c r="C37" s="13" t="n"/>
-      <c r="D37" s="13" t="n"/>
-      <c r="E37" s="13" t="n"/>
-      <c r="F37" s="13" t="n"/>
-      <c r="G37" s="13" t="n"/>
-      <c r="H37" s="13" t="n"/>
-      <c r="I37" s="13" t="n"/>
-      <c r="J37" s="13" t="n"/>
-      <c r="K37" s="13" t="n"/>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="14" t="n"/>
+      <c r="G37" s="14" t="n"/>
+      <c r="H37" s="14" t="n"/>
+      <c r="I37" s="14" t="n"/>
+      <c r="J37" s="14" t="n"/>
+      <c r="K37" s="14" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B39" s="13" t="inlineStr">
         <is>
           <t>[ Geography (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="C39" s="13" t="n"/>
-      <c r="D39" s="13" t="n"/>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n"/>
+      <c r="E39" s="14" t="n"/>
+      <c r="F39" s="14" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="13" t="n"/>
-      <c r="C40" s="13" t="n"/>
-      <c r="D40" s="13" t="n"/>
-      <c r="E40" s="13" t="n"/>
-      <c r="F40" s="13" t="n"/>
+      <c r="B40" s="14" t="n"/>
+      <c r="C40" s="14" t="n"/>
+      <c r="D40" s="14" t="n"/>
+      <c r="E40" s="14" t="n"/>
+      <c r="F40" s="14" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="13" t="n"/>
-      <c r="C41" s="13" t="n"/>
-      <c r="D41" s="13" t="n"/>
-      <c r="E41" s="13" t="n"/>
-      <c r="F41" s="13" t="n"/>
+      <c r="B41" s="14" t="n"/>
+      <c r="C41" s="14" t="n"/>
+      <c r="D41" s="14" t="n"/>
+      <c r="E41" s="14" t="n"/>
+      <c r="F41" s="14" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="13" t="n"/>
-      <c r="C42" s="13" t="n"/>
-      <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
+      <c r="B42" s="14" t="n"/>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="14" t="n"/>
+      <c r="E42" s="14" t="n"/>
+      <c r="F42" s="14" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="13" t="n"/>
-      <c r="C43" s="13" t="n"/>
-      <c r="D43" s="13" t="n"/>
-      <c r="E43" s="13" t="n"/>
-      <c r="F43" s="13" t="n"/>
+      <c r="B43" s="14" t="n"/>
+      <c r="C43" s="14" t="n"/>
+      <c r="D43" s="14" t="n"/>
+      <c r="E43" s="14" t="n"/>
+      <c r="F43" s="14" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="13" t="n"/>
-      <c r="C44" s="13" t="n"/>
-      <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
+      <c r="B44" s="14" t="n"/>
+      <c r="C44" s="14" t="n"/>
+      <c r="D44" s="14" t="n"/>
+      <c r="E44" s="14" t="n"/>
+      <c r="F44" s="14" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="13" t="n"/>
-      <c r="C45" s="13" t="n"/>
-      <c r="D45" s="13" t="n"/>
-      <c r="E45" s="13" t="n"/>
-      <c r="F45" s="13" t="n"/>
+      <c r="B45" s="14" t="n"/>
+      <c r="C45" s="14" t="n"/>
+      <c r="D45" s="14" t="n"/>
+      <c r="E45" s="14" t="n"/>
+      <c r="F45" s="14" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="13" t="n"/>
-      <c r="C46" s="13" t="n"/>
-      <c r="D46" s="13" t="n"/>
-      <c r="E46" s="13" t="n"/>
-      <c r="F46" s="13" t="n"/>
+      <c r="B46" s="14" t="n"/>
+      <c r="C46" s="14" t="n"/>
+      <c r="D46" s="14" t="n"/>
+      <c r="E46" s="14" t="n"/>
+      <c r="F46" s="14" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="13" t="n"/>
-      <c r="C47" s="13" t="n"/>
-      <c r="D47" s="13" t="n"/>
-      <c r="E47" s="13" t="n"/>
-      <c r="F47" s="13" t="n"/>
+      <c r="B47" s="14" t="n"/>
+      <c r="C47" s="14" t="n"/>
+      <c r="D47" s="14" t="n"/>
+      <c r="E47" s="14" t="n"/>
+      <c r="F47" s="14" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="13" t="n"/>
-      <c r="C48" s="13" t="n"/>
-      <c r="D48" s="13" t="n"/>
-      <c r="E48" s="13" t="n"/>
-      <c r="F48" s="13" t="n"/>
+      <c r="B48" s="14" t="n"/>
+      <c r="C48" s="14" t="n"/>
+      <c r="D48" s="14" t="n"/>
+      <c r="E48" s="14" t="n"/>
+      <c r="F48" s="14" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -10050,320 +10628,320 @@
       <c r="I13" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>TRENDS &amp; BREAKDOWNS</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>[ Stock Trend (Chart)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="13" t="n"/>
-      <c r="H17" s="13" t="n"/>
-      <c r="I17" s="13" t="n"/>
-      <c r="J17" s="13" t="n"/>
-      <c r="K17" s="13" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="14" t="n"/>
+      <c r="I17" s="14" t="n"/>
+      <c r="J17" s="14" t="n"/>
+      <c r="K17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="13" t="n"/>
-      <c r="H18" s="13" t="n"/>
-      <c r="I18" s="13" t="n"/>
-      <c r="J18" s="13" t="n"/>
-      <c r="K18" s="13" t="n"/>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="14" t="n"/>
+      <c r="I18" s="14" t="n"/>
+      <c r="J18" s="14" t="n"/>
+      <c r="K18" s="14" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="13" t="n"/>
-      <c r="H19" s="13" t="n"/>
-      <c r="I19" s="13" t="n"/>
-      <c r="J19" s="13" t="n"/>
-      <c r="K19" s="13" t="n"/>
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="14" t="n"/>
+      <c r="E19" s="14" t="n"/>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="14" t="n"/>
+      <c r="H19" s="14" t="n"/>
+      <c r="I19" s="14" t="n"/>
+      <c r="J19" s="14" t="n"/>
+      <c r="K19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="13" t="n"/>
-      <c r="H20" s="13" t="n"/>
-      <c r="I20" s="13" t="n"/>
-      <c r="J20" s="13" t="n"/>
-      <c r="K20" s="13" t="n"/>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="14" t="n"/>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="14" t="n"/>
+      <c r="H20" s="14" t="n"/>
+      <c r="I20" s="14" t="n"/>
+      <c r="J20" s="14" t="n"/>
+      <c r="K20" s="14" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="13" t="n"/>
-      <c r="H21" s="13" t="n"/>
-      <c r="I21" s="13" t="n"/>
-      <c r="J21" s="13" t="n"/>
-      <c r="K21" s="13" t="n"/>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="14" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="14" t="n"/>
+      <c r="H21" s="14" t="n"/>
+      <c r="I21" s="14" t="n"/>
+      <c r="J21" s="14" t="n"/>
+      <c r="K21" s="14" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="13" t="n"/>
-      <c r="H22" s="13" t="n"/>
-      <c r="I22" s="13" t="n"/>
-      <c r="J22" s="13" t="n"/>
-      <c r="K22" s="13" t="n"/>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="14" t="n"/>
+      <c r="I22" s="14" t="n"/>
+      <c r="J22" s="14" t="n"/>
+      <c r="K22" s="14" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="13" t="n"/>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="13" t="n"/>
-      <c r="J23" s="13" t="n"/>
-      <c r="K23" s="13" t="n"/>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="14" t="n"/>
+      <c r="I23" s="14" t="n"/>
+      <c r="J23" s="14" t="n"/>
+      <c r="K23" s="14" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="13" t="n"/>
-      <c r="H24" s="13" t="n"/>
-      <c r="I24" s="13" t="n"/>
-      <c r="J24" s="13" t="n"/>
-      <c r="K24" s="13" t="n"/>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="14" t="n"/>
+      <c r="I24" s="14" t="n"/>
+      <c r="J24" s="14" t="n"/>
+      <c r="K24" s="14" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>DETAIL (PIVOTTABLES)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>[ Stock by Location (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="C28" s="13" t="n"/>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="13" t="inlineStr">
         <is>
           <t>[ Low Stock List (Table)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="H28" s="13" t="n"/>
-      <c r="I28" s="13" t="n"/>
-      <c r="J28" s="13" t="n"/>
-      <c r="K28" s="13" t="n"/>
+      <c r="H28" s="14" t="n"/>
+      <c r="I28" s="14" t="n"/>
+      <c r="J28" s="14" t="n"/>
+      <c r="K28" s="14" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="13" t="n"/>
-      <c r="H29" s="13" t="n"/>
-      <c r="I29" s="13" t="n"/>
-      <c r="J29" s="13" t="n"/>
-      <c r="K29" s="13" t="n"/>
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="14" t="n"/>
+      <c r="H29" s="14" t="n"/>
+      <c r="I29" s="14" t="n"/>
+      <c r="J29" s="14" t="n"/>
+      <c r="K29" s="14" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="13" t="n"/>
-      <c r="H30" s="13" t="n"/>
-      <c r="I30" s="13" t="n"/>
-      <c r="J30" s="13" t="n"/>
-      <c r="K30" s="13" t="n"/>
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="14" t="n"/>
+      <c r="I30" s="14" t="n"/>
+      <c r="J30" s="14" t="n"/>
+      <c r="K30" s="14" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="13" t="n"/>
-      <c r="C31" s="13" t="n"/>
-      <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
-      <c r="G31" s="13" t="n"/>
-      <c r="H31" s="13" t="n"/>
-      <c r="I31" s="13" t="n"/>
-      <c r="J31" s="13" t="n"/>
-      <c r="K31" s="13" t="n"/>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="14" t="n"/>
+      <c r="I31" s="14" t="n"/>
+      <c r="J31" s="14" t="n"/>
+      <c r="K31" s="14" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="13" t="n"/>
-      <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="13" t="n"/>
-      <c r="H32" s="13" t="n"/>
-      <c r="I32" s="13" t="n"/>
-      <c r="J32" s="13" t="n"/>
-      <c r="K32" s="13" t="n"/>
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="14" t="n"/>
+      <c r="H32" s="14" t="n"/>
+      <c r="I32" s="14" t="n"/>
+      <c r="J32" s="14" t="n"/>
+      <c r="K32" s="14" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="13" t="n"/>
-      <c r="H33" s="13" t="n"/>
-      <c r="I33" s="13" t="n"/>
-      <c r="J33" s="13" t="n"/>
-      <c r="K33" s="13" t="n"/>
+      <c r="B33" s="14" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="14" t="n"/>
+      <c r="E33" s="14" t="n"/>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="14" t="n"/>
+      <c r="H33" s="14" t="n"/>
+      <c r="I33" s="14" t="n"/>
+      <c r="J33" s="14" t="n"/>
+      <c r="K33" s="14" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="13" t="n"/>
-      <c r="C34" s="13" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="13" t="n"/>
-      <c r="H34" s="13" t="n"/>
-      <c r="I34" s="13" t="n"/>
-      <c r="J34" s="13" t="n"/>
-      <c r="K34" s="13" t="n"/>
+      <c r="B34" s="14" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="14" t="n"/>
+      <c r="E34" s="14" t="n"/>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="14" t="n"/>
+      <c r="H34" s="14" t="n"/>
+      <c r="I34" s="14" t="n"/>
+      <c r="J34" s="14" t="n"/>
+      <c r="K34" s="14" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="13" t="n"/>
-      <c r="C35" s="13" t="n"/>
-      <c r="D35" s="13" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="13" t="n"/>
-      <c r="H35" s="13" t="n"/>
-      <c r="I35" s="13" t="n"/>
-      <c r="J35" s="13" t="n"/>
-      <c r="K35" s="13" t="n"/>
+      <c r="B35" s="14" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="14" t="n"/>
+      <c r="F35" s="14" t="n"/>
+      <c r="G35" s="14" t="n"/>
+      <c r="H35" s="14" t="n"/>
+      <c r="I35" s="14" t="n"/>
+      <c r="J35" s="14" t="n"/>
+      <c r="K35" s="14" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="13" t="n"/>
-      <c r="D36" s="13" t="n"/>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="13" t="n"/>
-      <c r="H36" s="13" t="n"/>
-      <c r="I36" s="13" t="n"/>
-      <c r="J36" s="13" t="n"/>
-      <c r="K36" s="13" t="n"/>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="14" t="n"/>
+      <c r="F36" s="14" t="n"/>
+      <c r="G36" s="14" t="n"/>
+      <c r="H36" s="14" t="n"/>
+      <c r="I36" s="14" t="n"/>
+      <c r="J36" s="14" t="n"/>
+      <c r="K36" s="14" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="13" t="n"/>
-      <c r="C37" s="13" t="n"/>
-      <c r="D37" s="13" t="n"/>
-      <c r="E37" s="13" t="n"/>
-      <c r="F37" s="13" t="n"/>
-      <c r="G37" s="13" t="n"/>
-      <c r="H37" s="13" t="n"/>
-      <c r="I37" s="13" t="n"/>
-      <c r="J37" s="13" t="n"/>
-      <c r="K37" s="13" t="n"/>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="14" t="n"/>
+      <c r="G37" s="14" t="n"/>
+      <c r="H37" s="14" t="n"/>
+      <c r="I37" s="14" t="n"/>
+      <c r="J37" s="14" t="n"/>
+      <c r="K37" s="14" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B39" s="13" t="inlineStr">
         <is>
           <t>[ Inventory Valuation (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="C39" s="13" t="n"/>
-      <c r="D39" s="13" t="n"/>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n"/>
+      <c r="E39" s="14" t="n"/>
+      <c r="F39" s="14" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="13" t="n"/>
-      <c r="C40" s="13" t="n"/>
-      <c r="D40" s="13" t="n"/>
-      <c r="E40" s="13" t="n"/>
-      <c r="F40" s="13" t="n"/>
+      <c r="B40" s="14" t="n"/>
+      <c r="C40" s="14" t="n"/>
+      <c r="D40" s="14" t="n"/>
+      <c r="E40" s="14" t="n"/>
+      <c r="F40" s="14" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="13" t="n"/>
-      <c r="C41" s="13" t="n"/>
-      <c r="D41" s="13" t="n"/>
-      <c r="E41" s="13" t="n"/>
-      <c r="F41" s="13" t="n"/>
+      <c r="B41" s="14" t="n"/>
+      <c r="C41" s="14" t="n"/>
+      <c r="D41" s="14" t="n"/>
+      <c r="E41" s="14" t="n"/>
+      <c r="F41" s="14" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="13" t="n"/>
-      <c r="C42" s="13" t="n"/>
-      <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
+      <c r="B42" s="14" t="n"/>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="14" t="n"/>
+      <c r="E42" s="14" t="n"/>
+      <c r="F42" s="14" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="13" t="n"/>
-      <c r="C43" s="13" t="n"/>
-      <c r="D43" s="13" t="n"/>
-      <c r="E43" s="13" t="n"/>
-      <c r="F43" s="13" t="n"/>
+      <c r="B43" s="14" t="n"/>
+      <c r="C43" s="14" t="n"/>
+      <c r="D43" s="14" t="n"/>
+      <c r="E43" s="14" t="n"/>
+      <c r="F43" s="14" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="13" t="n"/>
-      <c r="C44" s="13" t="n"/>
-      <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
+      <c r="B44" s="14" t="n"/>
+      <c r="C44" s="14" t="n"/>
+      <c r="D44" s="14" t="n"/>
+      <c r="E44" s="14" t="n"/>
+      <c r="F44" s="14" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="13" t="n"/>
-      <c r="C45" s="13" t="n"/>
-      <c r="D45" s="13" t="n"/>
-      <c r="E45" s="13" t="n"/>
-      <c r="F45" s="13" t="n"/>
+      <c r="B45" s="14" t="n"/>
+      <c r="C45" s="14" t="n"/>
+      <c r="D45" s="14" t="n"/>
+      <c r="E45" s="14" t="n"/>
+      <c r="F45" s="14" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="13" t="n"/>
-      <c r="C46" s="13" t="n"/>
-      <c r="D46" s="13" t="n"/>
-      <c r="E46" s="13" t="n"/>
-      <c r="F46" s="13" t="n"/>
+      <c r="B46" s="14" t="n"/>
+      <c r="C46" s="14" t="n"/>
+      <c r="D46" s="14" t="n"/>
+      <c r="E46" s="14" t="n"/>
+      <c r="F46" s="14" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="13" t="n"/>
-      <c r="C47" s="13" t="n"/>
-      <c r="D47" s="13" t="n"/>
-      <c r="E47" s="13" t="n"/>
-      <c r="F47" s="13" t="n"/>
+      <c r="B47" s="14" t="n"/>
+      <c r="C47" s="14" t="n"/>
+      <c r="D47" s="14" t="n"/>
+      <c r="E47" s="14" t="n"/>
+      <c r="F47" s="14" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="13" t="n"/>
-      <c r="C48" s="13" t="n"/>
-      <c r="D48" s="13" t="n"/>
-      <c r="E48" s="13" t="n"/>
-      <c r="F48" s="13" t="n"/>
+      <c r="B48" s="14" t="n"/>
+      <c r="C48" s="14" t="n"/>
+      <c r="D48" s="14" t="n"/>
+      <c r="E48" s="14" t="n"/>
+      <c r="F48" s="14" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -10563,246 +11141,246 @@
       <c r="I13" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>TRENDS &amp; BREAKDOWNS</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>[ P&amp;L Trend (Chart)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="13" t="n"/>
-      <c r="H17" s="13" t="n"/>
-      <c r="I17" s="13" t="n"/>
-      <c r="J17" s="13" t="n"/>
-      <c r="K17" s="13" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="14" t="n"/>
+      <c r="I17" s="14" t="n"/>
+      <c r="J17" s="14" t="n"/>
+      <c r="K17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="13" t="n"/>
-      <c r="H18" s="13" t="n"/>
-      <c r="I18" s="13" t="n"/>
-      <c r="J18" s="13" t="n"/>
-      <c r="K18" s="13" t="n"/>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="14" t="n"/>
+      <c r="I18" s="14" t="n"/>
+      <c r="J18" s="14" t="n"/>
+      <c r="K18" s="14" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="13" t="n"/>
-      <c r="H19" s="13" t="n"/>
-      <c r="I19" s="13" t="n"/>
-      <c r="J19" s="13" t="n"/>
-      <c r="K19" s="13" t="n"/>
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="14" t="n"/>
+      <c r="E19" s="14" t="n"/>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="14" t="n"/>
+      <c r="H19" s="14" t="n"/>
+      <c r="I19" s="14" t="n"/>
+      <c r="J19" s="14" t="n"/>
+      <c r="K19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="13" t="n"/>
-      <c r="H20" s="13" t="n"/>
-      <c r="I20" s="13" t="n"/>
-      <c r="J20" s="13" t="n"/>
-      <c r="K20" s="13" t="n"/>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="14" t="n"/>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="14" t="n"/>
+      <c r="H20" s="14" t="n"/>
+      <c r="I20" s="14" t="n"/>
+      <c r="J20" s="14" t="n"/>
+      <c r="K20" s="14" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="13" t="n"/>
-      <c r="H21" s="13" t="n"/>
-      <c r="I21" s="13" t="n"/>
-      <c r="J21" s="13" t="n"/>
-      <c r="K21" s="13" t="n"/>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="14" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="14" t="n"/>
+      <c r="H21" s="14" t="n"/>
+      <c r="I21" s="14" t="n"/>
+      <c r="J21" s="14" t="n"/>
+      <c r="K21" s="14" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="13" t="n"/>
-      <c r="H22" s="13" t="n"/>
-      <c r="I22" s="13" t="n"/>
-      <c r="J22" s="13" t="n"/>
-      <c r="K22" s="13" t="n"/>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="14" t="n"/>
+      <c r="I22" s="14" t="n"/>
+      <c r="J22" s="14" t="n"/>
+      <c r="K22" s="14" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="13" t="n"/>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="13" t="n"/>
-      <c r="J23" s="13" t="n"/>
-      <c r="K23" s="13" t="n"/>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="14" t="n"/>
+      <c r="I23" s="14" t="n"/>
+      <c r="J23" s="14" t="n"/>
+      <c r="K23" s="14" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="13" t="n"/>
-      <c r="H24" s="13" t="n"/>
-      <c r="I24" s="13" t="n"/>
-      <c r="J24" s="13" t="n"/>
-      <c r="K24" s="13" t="n"/>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="14" t="n"/>
+      <c r="I24" s="14" t="n"/>
+      <c r="J24" s="14" t="n"/>
+      <c r="K24" s="14" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>DETAIL (PIVOTTABLES)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>[ P&amp;L Statement (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="C28" s="13" t="n"/>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="13" t="inlineStr">
         <is>
           <t>[ Cash Flow Statement (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="H28" s="13" t="n"/>
-      <c r="I28" s="13" t="n"/>
-      <c r="J28" s="13" t="n"/>
-      <c r="K28" s="13" t="n"/>
+      <c r="H28" s="14" t="n"/>
+      <c r="I28" s="14" t="n"/>
+      <c r="J28" s="14" t="n"/>
+      <c r="K28" s="14" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="13" t="n"/>
-      <c r="H29" s="13" t="n"/>
-      <c r="I29" s="13" t="n"/>
-      <c r="J29" s="13" t="n"/>
-      <c r="K29" s="13" t="n"/>
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="14" t="n"/>
+      <c r="H29" s="14" t="n"/>
+      <c r="I29" s="14" t="n"/>
+      <c r="J29" s="14" t="n"/>
+      <c r="K29" s="14" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="13" t="n"/>
-      <c r="H30" s="13" t="n"/>
-      <c r="I30" s="13" t="n"/>
-      <c r="J30" s="13" t="n"/>
-      <c r="K30" s="13" t="n"/>
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="14" t="n"/>
+      <c r="I30" s="14" t="n"/>
+      <c r="J30" s="14" t="n"/>
+      <c r="K30" s="14" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="13" t="n"/>
-      <c r="C31" s="13" t="n"/>
-      <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
-      <c r="G31" s="13" t="n"/>
-      <c r="H31" s="13" t="n"/>
-      <c r="I31" s="13" t="n"/>
-      <c r="J31" s="13" t="n"/>
-      <c r="K31" s="13" t="n"/>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="14" t="n"/>
+      <c r="I31" s="14" t="n"/>
+      <c r="J31" s="14" t="n"/>
+      <c r="K31" s="14" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="13" t="n"/>
-      <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="13" t="n"/>
-      <c r="H32" s="13" t="n"/>
-      <c r="I32" s="13" t="n"/>
-      <c r="J32" s="13" t="n"/>
-      <c r="K32" s="13" t="n"/>
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="14" t="n"/>
+      <c r="H32" s="14" t="n"/>
+      <c r="I32" s="14" t="n"/>
+      <c r="J32" s="14" t="n"/>
+      <c r="K32" s="14" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="13" t="n"/>
-      <c r="H33" s="13" t="n"/>
-      <c r="I33" s="13" t="n"/>
-      <c r="J33" s="13" t="n"/>
-      <c r="K33" s="13" t="n"/>
+      <c r="B33" s="14" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="14" t="n"/>
+      <c r="E33" s="14" t="n"/>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="14" t="n"/>
+      <c r="H33" s="14" t="n"/>
+      <c r="I33" s="14" t="n"/>
+      <c r="J33" s="14" t="n"/>
+      <c r="K33" s="14" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="13" t="n"/>
-      <c r="C34" s="13" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="13" t="n"/>
-      <c r="H34" s="13" t="n"/>
-      <c r="I34" s="13" t="n"/>
-      <c r="J34" s="13" t="n"/>
-      <c r="K34" s="13" t="n"/>
+      <c r="B34" s="14" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="14" t="n"/>
+      <c r="E34" s="14" t="n"/>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="14" t="n"/>
+      <c r="H34" s="14" t="n"/>
+      <c r="I34" s="14" t="n"/>
+      <c r="J34" s="14" t="n"/>
+      <c r="K34" s="14" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="13" t="n"/>
-      <c r="C35" s="13" t="n"/>
-      <c r="D35" s="13" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="13" t="n"/>
-      <c r="H35" s="13" t="n"/>
-      <c r="I35" s="13" t="n"/>
-      <c r="J35" s="13" t="n"/>
-      <c r="K35" s="13" t="n"/>
+      <c r="B35" s="14" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="14" t="n"/>
+      <c r="F35" s="14" t="n"/>
+      <c r="G35" s="14" t="n"/>
+      <c r="H35" s="14" t="n"/>
+      <c r="I35" s="14" t="n"/>
+      <c r="J35" s="14" t="n"/>
+      <c r="K35" s="14" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="13" t="n"/>
-      <c r="D36" s="13" t="n"/>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="13" t="n"/>
-      <c r="H36" s="13" t="n"/>
-      <c r="I36" s="13" t="n"/>
-      <c r="J36" s="13" t="n"/>
-      <c r="K36" s="13" t="n"/>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="14" t="n"/>
+      <c r="F36" s="14" t="n"/>
+      <c r="G36" s="14" t="n"/>
+      <c r="H36" s="14" t="n"/>
+      <c r="I36" s="14" t="n"/>
+      <c r="J36" s="14" t="n"/>
+      <c r="K36" s="14" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="13" t="n"/>
-      <c r="C37" s="13" t="n"/>
-      <c r="D37" s="13" t="n"/>
-      <c r="E37" s="13" t="n"/>
-      <c r="F37" s="13" t="n"/>
-      <c r="G37" s="13" t="n"/>
-      <c r="H37" s="13" t="n"/>
-      <c r="I37" s="13" t="n"/>
-      <c r="J37" s="13" t="n"/>
-      <c r="K37" s="13" t="n"/>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="14" t="n"/>
+      <c r="G37" s="14" t="n"/>
+      <c r="H37" s="14" t="n"/>
+      <c r="I37" s="14" t="n"/>
+      <c r="J37" s="14" t="n"/>
+      <c r="K37" s="14" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -11001,246 +11579,246 @@
       <c r="I13" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>TRENDS &amp; BREAKDOWNS</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>[ Margin Trend (Chart)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="13" t="n"/>
-      <c r="H17" s="13" t="n"/>
-      <c r="I17" s="13" t="n"/>
-      <c r="J17" s="13" t="n"/>
-      <c r="K17" s="13" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="14" t="n"/>
+      <c r="I17" s="14" t="n"/>
+      <c r="J17" s="14" t="n"/>
+      <c r="K17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="13" t="n"/>
-      <c r="H18" s="13" t="n"/>
-      <c r="I18" s="13" t="n"/>
-      <c r="J18" s="13" t="n"/>
-      <c r="K18" s="13" t="n"/>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="14" t="n"/>
+      <c r="I18" s="14" t="n"/>
+      <c r="J18" s="14" t="n"/>
+      <c r="K18" s="14" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="13" t="n"/>
-      <c r="H19" s="13" t="n"/>
-      <c r="I19" s="13" t="n"/>
-      <c r="J19" s="13" t="n"/>
-      <c r="K19" s="13" t="n"/>
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="14" t="n"/>
+      <c r="E19" s="14" t="n"/>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="14" t="n"/>
+      <c r="H19" s="14" t="n"/>
+      <c r="I19" s="14" t="n"/>
+      <c r="J19" s="14" t="n"/>
+      <c r="K19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="13" t="n"/>
-      <c r="H20" s="13" t="n"/>
-      <c r="I20" s="13" t="n"/>
-      <c r="J20" s="13" t="n"/>
-      <c r="K20" s="13" t="n"/>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="14" t="n"/>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="14" t="n"/>
+      <c r="H20" s="14" t="n"/>
+      <c r="I20" s="14" t="n"/>
+      <c r="J20" s="14" t="n"/>
+      <c r="K20" s="14" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="13" t="n"/>
-      <c r="H21" s="13" t="n"/>
-      <c r="I21" s="13" t="n"/>
-      <c r="J21" s="13" t="n"/>
-      <c r="K21" s="13" t="n"/>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="14" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="14" t="n"/>
+      <c r="H21" s="14" t="n"/>
+      <c r="I21" s="14" t="n"/>
+      <c r="J21" s="14" t="n"/>
+      <c r="K21" s="14" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="13" t="n"/>
-      <c r="H22" s="13" t="n"/>
-      <c r="I22" s="13" t="n"/>
-      <c r="J22" s="13" t="n"/>
-      <c r="K22" s="13" t="n"/>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="14" t="n"/>
+      <c r="I22" s="14" t="n"/>
+      <c r="J22" s="14" t="n"/>
+      <c r="K22" s="14" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="13" t="n"/>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="13" t="n"/>
-      <c r="J23" s="13" t="n"/>
-      <c r="K23" s="13" t="n"/>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="14" t="n"/>
+      <c r="I23" s="14" t="n"/>
+      <c r="J23" s="14" t="n"/>
+      <c r="K23" s="14" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="13" t="n"/>
-      <c r="H24" s="13" t="n"/>
-      <c r="I24" s="13" t="n"/>
-      <c r="J24" s="13" t="n"/>
-      <c r="K24" s="13" t="n"/>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="14" t="n"/>
+      <c r="I24" s="14" t="n"/>
+      <c r="J24" s="14" t="n"/>
+      <c r="K24" s="14" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>DETAIL (PIVOTTABLES)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>[ Margin by Product (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="C28" s="13" t="n"/>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="13" t="inlineStr">
         <is>
           <t>[ Margin by Collection (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
         </is>
       </c>
-      <c r="H28" s="13" t="n"/>
-      <c r="I28" s="13" t="n"/>
-      <c r="J28" s="13" t="n"/>
-      <c r="K28" s="13" t="n"/>
+      <c r="H28" s="14" t="n"/>
+      <c r="I28" s="14" t="n"/>
+      <c r="J28" s="14" t="n"/>
+      <c r="K28" s="14" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="13" t="n"/>
-      <c r="H29" s="13" t="n"/>
-      <c r="I29" s="13" t="n"/>
-      <c r="J29" s="13" t="n"/>
-      <c r="K29" s="13" t="n"/>
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="14" t="n"/>
+      <c r="H29" s="14" t="n"/>
+      <c r="I29" s="14" t="n"/>
+      <c r="J29" s="14" t="n"/>
+      <c r="K29" s="14" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="13" t="n"/>
-      <c r="H30" s="13" t="n"/>
-      <c r="I30" s="13" t="n"/>
-      <c r="J30" s="13" t="n"/>
-      <c r="K30" s="13" t="n"/>
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="14" t="n"/>
+      <c r="I30" s="14" t="n"/>
+      <c r="J30" s="14" t="n"/>
+      <c r="K30" s="14" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="13" t="n"/>
-      <c r="C31" s="13" t="n"/>
-      <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
-      <c r="G31" s="13" t="n"/>
-      <c r="H31" s="13" t="n"/>
-      <c r="I31" s="13" t="n"/>
-      <c r="J31" s="13" t="n"/>
-      <c r="K31" s="13" t="n"/>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="14" t="n"/>
+      <c r="I31" s="14" t="n"/>
+      <c r="J31" s="14" t="n"/>
+      <c r="K31" s="14" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="13" t="n"/>
-      <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="13" t="n"/>
-      <c r="H32" s="13" t="n"/>
-      <c r="I32" s="13" t="n"/>
-      <c r="J32" s="13" t="n"/>
-      <c r="K32" s="13" t="n"/>
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="14" t="n"/>
+      <c r="H32" s="14" t="n"/>
+      <c r="I32" s="14" t="n"/>
+      <c r="J32" s="14" t="n"/>
+      <c r="K32" s="14" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="13" t="n"/>
-      <c r="H33" s="13" t="n"/>
-      <c r="I33" s="13" t="n"/>
-      <c r="J33" s="13" t="n"/>
-      <c r="K33" s="13" t="n"/>
+      <c r="B33" s="14" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="14" t="n"/>
+      <c r="E33" s="14" t="n"/>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="14" t="n"/>
+      <c r="H33" s="14" t="n"/>
+      <c r="I33" s="14" t="n"/>
+      <c r="J33" s="14" t="n"/>
+      <c r="K33" s="14" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="13" t="n"/>
-      <c r="C34" s="13" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="13" t="n"/>
-      <c r="H34" s="13" t="n"/>
-      <c r="I34" s="13" t="n"/>
-      <c r="J34" s="13" t="n"/>
-      <c r="K34" s="13" t="n"/>
+      <c r="B34" s="14" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="14" t="n"/>
+      <c r="E34" s="14" t="n"/>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="14" t="n"/>
+      <c r="H34" s="14" t="n"/>
+      <c r="I34" s="14" t="n"/>
+      <c r="J34" s="14" t="n"/>
+      <c r="K34" s="14" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="13" t="n"/>
-      <c r="C35" s="13" t="n"/>
-      <c r="D35" s="13" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="13" t="n"/>
-      <c r="H35" s="13" t="n"/>
-      <c r="I35" s="13" t="n"/>
-      <c r="J35" s="13" t="n"/>
-      <c r="K35" s="13" t="n"/>
+      <c r="B35" s="14" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="14" t="n"/>
+      <c r="F35" s="14" t="n"/>
+      <c r="G35" s="14" t="n"/>
+      <c r="H35" s="14" t="n"/>
+      <c r="I35" s="14" t="n"/>
+      <c r="J35" s="14" t="n"/>
+      <c r="K35" s="14" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="13" t="n"/>
-      <c r="D36" s="13" t="n"/>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="13" t="n"/>
-      <c r="H36" s="13" t="n"/>
-      <c r="I36" s="13" t="n"/>
-      <c r="J36" s="13" t="n"/>
-      <c r="K36" s="13" t="n"/>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="14" t="n"/>
+      <c r="F36" s="14" t="n"/>
+      <c r="G36" s="14" t="n"/>
+      <c r="H36" s="14" t="n"/>
+      <c r="I36" s="14" t="n"/>
+      <c r="J36" s="14" t="n"/>
+      <c r="K36" s="14" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="13" t="n"/>
-      <c r="C37" s="13" t="n"/>
-      <c r="D37" s="13" t="n"/>
-      <c r="E37" s="13" t="n"/>
-      <c r="F37" s="13" t="n"/>
-      <c r="G37" s="13" t="n"/>
-      <c r="H37" s="13" t="n"/>
-      <c r="I37" s="13" t="n"/>
-      <c r="J37" s="13" t="n"/>
-      <c r="K37" s="13" t="n"/>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="14" t="n"/>
+      <c r="G37" s="14" t="n"/>
+      <c r="H37" s="14" t="n"/>
+      <c r="I37" s="14" t="n"/>
+      <c r="J37" s="14" t="n"/>
+      <c r="K37" s="14" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>

--- a/passress-mis/PASSRESS_MIS.xlsx
+++ b/passress-mis/PASSRESS_MIS.xlsx
@@ -38,13 +38,19 @@
     <sheet name="DIM_Location" sheetId="29" state="hidden" r:id="rId29"/>
     <sheet name="DIM_Collection" sheetId="30" state="hidden" r:id="rId30"/>
     <sheet name="DIM_Parameters" sheetId="31" state="hidden" r:id="rId31"/>
-    <sheet name="FACT_OrderLines" sheetId="32" state="hidden" r:id="rId32"/>
-    <sheet name="FACT_Refunds" sheetId="33" state="hidden" r:id="rId33"/>
-    <sheet name="FACT_InventoryMovements" sheetId="34" state="hidden" r:id="rId34"/>
-    <sheet name="FACT_Payments" sheetId="35" state="hidden" r:id="rId35"/>
-    <sheet name="FACT_ManualExpenses" sheetId="36" state="hidden" r:id="rId36"/>
-    <sheet name="LOG_RefreshHistory" sheetId="37" state="hidden" r:id="rId37"/>
-    <sheet name="LOG_DataQuality" sheetId="38" state="hidden" r:id="rId38"/>
+    <sheet name="DIM_Supplier" sheetId="32" state="hidden" r:id="rId32"/>
+    <sheet name="DIM_ProductCostHistory" sheetId="33" state="hidden" r:id="rId33"/>
+    <sheet name="FACT_OrderLines" sheetId="34" state="hidden" r:id="rId34"/>
+    <sheet name="FACT_Refunds" sheetId="35" state="hidden" r:id="rId35"/>
+    <sheet name="FACT_InventoryMovements" sheetId="36" state="hidden" r:id="rId36"/>
+    <sheet name="FACT_Payments" sheetId="37" state="hidden" r:id="rId37"/>
+    <sheet name="FACT_ManualExpenses" sheetId="38" state="hidden" r:id="rId38"/>
+    <sheet name="FACT_CapitalTransactions" sheetId="39" state="hidden" r:id="rId39"/>
+    <sheet name="FACT_PurchaseOrderHeader" sheetId="40" state="hidden" r:id="rId40"/>
+    <sheet name="FACT_PurchaseOrderLines" sheetId="41" state="hidden" r:id="rId41"/>
+    <sheet name="FACT_GoodsReceipt" sheetId="42" state="hidden" r:id="rId42"/>
+    <sheet name="LOG_RefreshHistory" sheetId="43" state="hidden" r:id="rId43"/>
+    <sheet name="LOG_DataQuality" sheetId="44" state="hidden" r:id="rId44"/>
   </sheets>
   <definedNames>
     <definedName name="SetCompanyName">'15_Settings'!$C$13</definedName>
@@ -58,6 +64,21 @@
     <definedName name="SetLookbackDaysIncrementalRefresh">'15_Settings'!$C$25</definedName>
     <definedName name="SetHistoricalBackfillStartDate">'15_Settings'!$C$26</definedName>
     <definedName name="SetMaxPagesPerRefreshSafetyCap">'15_Settings'!$C$27</definedName>
+    <definedName name="LookupExpenseCategory">=tbl_LookupExpenseCategory[Expense Category]</definedName>
+    <definedName name="LookupExpenseSubcategory">=tbl_LookupExpenseSubcategory[Expense Subcategory]</definedName>
+    <definedName name="LookupCostCenter">=tbl_LookupCostCenter[Cost Center]</definedName>
+    <definedName name="LookupPaymentMethod">=tbl_LookupPaymentMethod[Payment Method]</definedName>
+    <definedName name="LookupCurrency">=tbl_LookupCurrency[Currency]</definedName>
+    <definedName name="LookupSupplierType">=tbl_LookupSupplierType[Supplier Type]</definedName>
+    <definedName name="LookupSupplierStatus">=tbl_LookupSupplierStatus[Supplier Status]</definedName>
+    <definedName name="LookupCapitalTransactionType">=tbl_LookupCapitalTransactionType[Capital Transaction Type]</definedName>
+    <definedName name="LookupPOStatus">=tbl_LookupPOStatus[PO Status]</definedName>
+    <definedName name="LookupWarehouse">=tbl_LookupWarehouse[Warehouse]</definedName>
+    <definedName name="LookupOwner">=tbl_LookupOwner[Owner]</definedName>
+    <definedName name="SupplierNameList">=tbl_SupplierMaster[Supplier Name]</definedName>
+    <definedName name="POHeaderList">=tbl_POHeader[PO Number]</definedName>
+    <definedName name="SKUList">=tbl_RAW_Variants[SKU]</definedName>
+    <definedName name="CollectionTitleList">=tbl_RAW_Collections[Title]</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -65,8 +86,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="19">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -138,6 +161,12 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
@@ -149,13 +178,13 @@
     </font>
     <font>
       <name val="Segoe UI"/>
-      <i val="1"/>
-      <color rgb="00C55A11"/>
+      <color rgb="007F7F7F"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Segoe UI"/>
-      <color rgb="007F7F7F"/>
+      <i val="1"/>
+      <color rgb="00C55A11"/>
       <sz val="9"/>
     </font>
     <font>
@@ -166,6 +195,11 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
+      <color rgb="00C55A11"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
       <color rgb="00C55A11"/>
       <sz val="9"/>
     </font>
@@ -281,7 +315,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -315,31 +349,38 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
@@ -419,23 +460,219 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tbl_ManualExpenses" displayName="tbl_ManualExpenses" ref="B17:H18" headerRowCount="1">
-  <autoFilter ref="B17:H18"/>
-  <tableColumns count="7">
-    <tableColumn id="2" name="Date"/>
-    <tableColumn id="3" name="Category"/>
-    <tableColumn id="4" name="Cost Center"/>
-    <tableColumn id="5" name="Description"/>
-    <tableColumn id="6" name="Amount (EGP)"/>
-    <tableColumn id="7" name="Payment Method"/>
-    <tableColumn id="8" name="Entered By"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tbl_ProductCostMaster" displayName="tbl_ProductCostMaster" ref="B44:S45" headerRowCount="1">
+  <autoFilter ref="B44:S45"/>
+  <tableColumns count="18">
+    <tableColumn id="2" name="Cost ID"/>
+    <tableColumn id="3" name="SKU"/>
+    <tableColumn id="4" name="Product Name"/>
+    <tableColumn id="5" name="Variant"/>
+    <tableColumn id="6" name="Collection"/>
+    <tableColumn id="7" name="Fabric Cost"/>
+    <tableColumn id="8" name="Accessories Cost"/>
+    <tableColumn id="9" name="Manufacturing Cost"/>
+    <tableColumn id="10" name="Packaging Cost"/>
+    <tableColumn id="11" name="Shipping Cost"/>
+    <tableColumn id="12" name="Other Cost"/>
+    <tableColumn id="13" name="Total Landed Cost"/>
+    <tableColumn id="14" name="Selling Price"/>
+    <tableColumn id="15" name="Expected Gross Margin %"/>
+    <tableColumn id="16" name="Effective From Date"/>
+    <tableColumn id="17" name="Effective To Date"/>
+    <tableColumn id="18" name="Active Flag"/>
+    <tableColumn id="19" name="Overlap Warning"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="tbl_RAW_OrderLines" displayName="tbl_RAW_OrderLines" ref="B11:K12" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="tbl_ChartOfAccounts" displayName="tbl_ChartOfAccounts" ref="B31:F32" headerRowCount="1">
+  <autoFilter ref="B31:F32"/>
+  <tableColumns count="5">
+    <tableColumn id="2" name="Account Code"/>
+    <tableColumn id="3" name="Account Name"/>
+    <tableColumn id="4" name="Statement"/>
+    <tableColumn id="5" name="P&amp;L / BS Line"/>
+    <tableColumn id="6" name="Source"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="tbl_VersionLog" displayName="tbl_VersionLog" ref="B36:E40" headerRowCount="1">
+  <autoFilter ref="B36:E40"/>
+  <tableColumns count="4">
+    <tableColumn id="2" name="Version"/>
+    <tableColumn id="3" name="Date"/>
+    <tableColumn id="4" name="Phase"/>
+    <tableColumn id="5" name="Summary"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="tbl_LookupExpenseCategory" displayName="tbl_LookupExpenseCategory" ref="B44:B54" headerRowCount="1">
+  <autoFilter ref="B44:B54"/>
+  <tableColumns count="1">
+    <tableColumn id="2" name="Expense Category"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tbl_LookupExpenseSubcategory" displayName="tbl_LookupExpenseSubcategory" ref="B56:B68" headerRowCount="1">
+  <autoFilter ref="B56:B68"/>
+  <tableColumns count="1">
+    <tableColumn id="2" name="Expense Subcategory"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="tbl_LookupCostCenter" displayName="tbl_LookupCostCenter" ref="B70:B75" headerRowCount="1">
+  <autoFilter ref="B70:B75"/>
+  <tableColumns count="1">
+    <tableColumn id="2" name="Cost Center"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="tbl_LookupPaymentMethod" displayName="tbl_LookupPaymentMethod" ref="B77:B83" headerRowCount="1">
+  <autoFilter ref="B77:B83"/>
+  <tableColumns count="1">
+    <tableColumn id="2" name="Payment Method"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="tbl_LookupCurrency" displayName="tbl_LookupCurrency" ref="B85:B89" headerRowCount="1">
+  <autoFilter ref="B85:B89"/>
+  <tableColumns count="1">
+    <tableColumn id="2" name="Currency"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="tbl_LookupSupplierType" displayName="tbl_LookupSupplierType" ref="B91:B99" headerRowCount="1">
+  <autoFilter ref="B91:B99"/>
+  <tableColumns count="1">
+    <tableColumn id="2" name="Supplier Type"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="tbl_LookupSupplierStatus" displayName="tbl_LookupSupplierStatus" ref="B101:B104" headerRowCount="1">
+  <autoFilter ref="B101:B104"/>
+  <tableColumns count="1">
+    <tableColumn id="2" name="Supplier Status"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tbl_LookupCapitalTransactionType" displayName="tbl_LookupCapitalTransactionType" ref="B106:B108" headerRowCount="1">
+  <autoFilter ref="B106:B108"/>
+  <tableColumns count="1">
+    <tableColumn id="2" name="Capital Transaction Type"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tbl_ManualExpenses" displayName="tbl_ManualExpenses" ref="B17:R18" headerRowCount="1">
+  <autoFilter ref="B17:R18"/>
+  <tableColumns count="17">
+    <tableColumn id="2" name="Expense ID"/>
+    <tableColumn id="3" name="Expense Date"/>
+    <tableColumn id="4" name="Expense Category"/>
+    <tableColumn id="5" name="Expense Subcategory"/>
+    <tableColumn id="6" name="Supplier"/>
+    <tableColumn id="7" name="Amount"/>
+    <tableColumn id="8" name="Currency"/>
+    <tableColumn id="9" name="Payment Method"/>
+    <tableColumn id="10" name="Related Collection"/>
+    <tableColumn id="11" name="Related SKU"/>
+    <tableColumn id="12" name="Cost Center"/>
+    <tableColumn id="13" name="Notes"/>
+    <tableColumn id="14" name="Invoice Number"/>
+    <tableColumn id="15" name="File Name"/>
+    <tableColumn id="16" name="File Path"/>
+    <tableColumn id="17" name="Cloud Link"/>
+    <tableColumn id="18" name="Possible Duplicate"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="tbl_LookupPOStatus" displayName="tbl_LookupPOStatus" ref="B110:B117" headerRowCount="1">
+  <autoFilter ref="B110:B117"/>
+  <tableColumns count="1">
+    <tableColumn id="2" name="PO Status"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="tbl_LookupWarehouse" displayName="tbl_LookupWarehouse" ref="B119:B122" headerRowCount="1">
+  <autoFilter ref="B119:B122"/>
+  <tableColumns count="1">
+    <tableColumn id="2" name="Warehouse"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="tbl_LookupOwner" displayName="tbl_LookupOwner" ref="B124:B125" headerRowCount="1">
+  <autoFilter ref="B124:B125"/>
+  <tableColumns count="1">
+    <tableColumn id="2" name="Owner"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="tbl_RAW_Orders" displayName="tbl_RAW_Orders" ref="B11:N12" headerRowCount="1">
+  <autoFilter ref="B11:N12"/>
+  <tableColumns count="13">
+    <tableColumn id="2" name="OrderID"/>
+    <tableColumn id="3" name="OrderNumber"/>
+    <tableColumn id="4" name="CreatedAt"/>
+    <tableColumn id="5" name="UpdatedAt"/>
+    <tableColumn id="6" name="FinancialStatus"/>
+    <tableColumn id="7" name="FulfillmentStatus"/>
+    <tableColumn id="8" name="Currency"/>
+    <tableColumn id="9" name="TotalPrice"/>
+    <tableColumn id="10" name="SubtotalPrice"/>
+    <tableColumn id="11" name="TotalDiscounts"/>
+    <tableColumn id="12" name="TotalTax"/>
+    <tableColumn id="13" name="CustomerID"/>
+    <tableColumn id="14" name="LocationID"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="tbl_RAW_OrderLines" displayName="tbl_RAW_OrderLines" ref="B11:K12" headerRowCount="1">
   <autoFilter ref="B11:K12"/>
   <tableColumns count="10">
     <tableColumn id="2" name="LineItemID"/>
@@ -453,8 +690,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="tbl_RAW_Transactions" displayName="tbl_RAW_Transactions" ref="B11:K12" headerRowCount="1">
+<file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="tbl_RAW_Transactions" displayName="tbl_RAW_Transactions" ref="B11:K12" headerRowCount="1">
   <autoFilter ref="B11:K12"/>
   <tableColumns count="10">
     <tableColumn id="2" name="TransactionID"/>
@@ -472,8 +709,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="tbl_RAW_Refunds" displayName="tbl_RAW_Refunds" ref="B11:K12" headerRowCount="1">
+<file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="tbl_RAW_Refunds" displayName="tbl_RAW_Refunds" ref="B11:K12" headerRowCount="1">
   <autoFilter ref="B11:K12"/>
   <tableColumns count="10">
     <tableColumn id="2" name="RefundLineItemID"/>
@@ -491,8 +728,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tbl_RAW_Products" displayName="tbl_RAW_Products" ref="B11:I12" headerRowCount="1">
+<file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="tbl_RAW_Products" displayName="tbl_RAW_Products" ref="B11:I12" headerRowCount="1">
   <autoFilter ref="B11:I12"/>
   <tableColumns count="8">
     <tableColumn id="2" name="ProductID"/>
@@ -508,8 +745,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="tbl_RAW_Variants" displayName="tbl_RAW_Variants" ref="B11:K12" headerRowCount="1">
+<file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="tbl_RAW_Variants" displayName="tbl_RAW_Variants" ref="B11:K12" headerRowCount="1">
   <autoFilter ref="B11:K12"/>
   <tableColumns count="10">
     <tableColumn id="2" name="VariantID"/>
@@ -527,8 +764,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="tbl_RAW_InventoryLevels" displayName="tbl_RAW_InventoryLevels" ref="B11:F12" headerRowCount="1">
+<file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="29" name="tbl_RAW_InventoryLevels" displayName="tbl_RAW_InventoryLevels" ref="B11:F12" headerRowCount="1">
   <autoFilter ref="B11:F12"/>
   <tableColumns count="5">
     <tableColumn id="2" name="InventoryItemID"/>
@@ -541,8 +778,25 @@
 </table>
 </file>
 
-<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="tbl_RAW_Customers" displayName="tbl_RAW_Customers" ref="B11:J12" headerRowCount="1">
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tbl_CapitalTransactions" displayName="tbl_CapitalTransactions" ref="B17:I18" headerRowCount="1">
+  <autoFilter ref="B17:I18"/>
+  <tableColumns count="8">
+    <tableColumn id="2" name="Capital ID"/>
+    <tableColumn id="3" name="Date"/>
+    <tableColumn id="4" name="Owner"/>
+    <tableColumn id="5" name="Transaction Type"/>
+    <tableColumn id="6" name="Amount"/>
+    <tableColumn id="7" name="Notes"/>
+    <tableColumn id="8" name="Entered By"/>
+    <tableColumn id="9" name="Possible Duplicate"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="30" name="tbl_RAW_Customers" displayName="tbl_RAW_Customers" ref="B11:J12" headerRowCount="1">
   <autoFilter ref="B11:J12"/>
   <tableColumns count="9">
     <tableColumn id="2" name="CustomerID"/>
@@ -559,8 +813,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="tbl_RAW_Collections" displayName="tbl_RAW_Collections" ref="B11:D12" headerRowCount="1">
+<file path=xl/tables/table31.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="31" name="tbl_RAW_Collections" displayName="tbl_RAW_Collections" ref="B11:D12" headerRowCount="1">
   <autoFilter ref="B11:D12"/>
   <tableColumns count="3">
     <tableColumn id="2" name="CollectionID"/>
@@ -571,8 +825,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="tbl_RAW_Discounts" displayName="tbl_RAW_Discounts" ref="B11:M12" headerRowCount="1">
+<file path=xl/tables/table32.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="32" name="tbl_RAW_Discounts" displayName="tbl_RAW_Discounts" ref="B11:M12" headerRowCount="1">
   <autoFilter ref="B11:M12"/>
   <tableColumns count="12">
     <tableColumn id="2" name="DiscountNodeID"/>
@@ -592,8 +846,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tbl_DIM_Date" displayName="tbl_DIM_Date" ref="B11:L12" headerRowCount="1">
+<file path=xl/tables/table33.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="33" name="tbl_DIM_Date" displayName="tbl_DIM_Date" ref="B11:L12" headerRowCount="1">
   <autoFilter ref="B11:L12"/>
   <tableColumns count="11">
     <tableColumn id="2" name="DateKey"/>
@@ -612,22 +866,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tbl_CapitalTransactions" displayName="tbl_CapitalTransactions" ref="B17:F18" headerRowCount="1">
-  <autoFilter ref="B17:F18"/>
-  <tableColumns count="5">
-    <tableColumn id="2" name="Date"/>
-    <tableColumn id="3" name="Type (Contribution/Withdrawal)"/>
-    <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Amount (EGP)"/>
-    <tableColumn id="6" name="Entered By"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="tbl_DIM_Product" displayName="tbl_DIM_Product" ref="B11:J12" headerRowCount="1">
+<file path=xl/tables/table34.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="34" name="tbl_DIM_Product" displayName="tbl_DIM_Product" ref="B11:J12" headerRowCount="1">
   <autoFilter ref="B11:J12"/>
   <tableColumns count="9">
     <tableColumn id="2" name="ProductKey"/>
@@ -644,8 +884,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="tbl_DIM_Customer" displayName="tbl_DIM_Customer" ref="B11:H12" headerRowCount="1">
+<file path=xl/tables/table35.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="35" name="tbl_DIM_Customer" displayName="tbl_DIM_Customer" ref="B11:H12" headerRowCount="1">
   <autoFilter ref="B11:H12"/>
   <tableColumns count="7">
     <tableColumn id="2" name="CustomerKey"/>
@@ -660,8 +900,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="tbl_DIM_Location" displayName="tbl_DIM_Location" ref="B11:F12" headerRowCount="1">
+<file path=xl/tables/table36.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="36" name="tbl_DIM_Location" displayName="tbl_DIM_Location" ref="B11:F12" headerRowCount="1">
   <autoFilter ref="B11:F12"/>
   <tableColumns count="5">
     <tableColumn id="2" name="LocationKey"/>
@@ -674,8 +914,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="tbl_DIM_Collection" displayName="tbl_DIM_Collection" ref="B11:E12" headerRowCount="1">
+<file path=xl/tables/table37.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="37" name="tbl_DIM_Collection" displayName="tbl_DIM_Collection" ref="B11:E12" headerRowCount="1">
   <autoFilter ref="B11:E12"/>
   <tableColumns count="4">
     <tableColumn id="2" name="CollectionKey"/>
@@ -687,8 +927,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="tbl_DIM_Parameters" displayName="tbl_DIM_Parameters" ref="B11:C12" headerRowCount="1">
+<file path=xl/tables/table38.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="38" name="tbl_DIM_Parameters" displayName="tbl_DIM_Parameters" ref="B11:C12" headerRowCount="1">
   <autoFilter ref="B11:C12"/>
   <tableColumns count="2">
     <tableColumn id="2" name="ParameterName"/>
@@ -698,8 +938,60 @@
 </table>
 </file>
 
-<file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="tbl_FACT_OrderLines" displayName="tbl_FACT_OrderLines" ref="B11:O12" headerRowCount="1">
+<file path=xl/tables/table39.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="39" name="tbl_DIM_Supplier" displayName="tbl_DIM_Supplier" ref="B11:G12" headerRowCount="1">
+  <autoFilter ref="B11:G12"/>
+  <tableColumns count="6">
+    <tableColumn id="2" name="SupplierKey"/>
+    <tableColumn id="3" name="SupplierID"/>
+    <tableColumn id="4" name="SupplierName"/>
+    <tableColumn id="5" name="SupplierType"/>
+    <tableColumn id="6" name="Currency"/>
+    <tableColumn id="7" name="Status"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tbl_SupplierMaster" displayName="tbl_SupplierMaster" ref="B17:K18" headerRowCount="1">
+  <autoFilter ref="B17:K18"/>
+  <tableColumns count="10">
+    <tableColumn id="2" name="Supplier ID"/>
+    <tableColumn id="3" name="Supplier Name"/>
+    <tableColumn id="4" name="Supplier Type"/>
+    <tableColumn id="5" name="Contact Person"/>
+    <tableColumn id="6" name="Phone"/>
+    <tableColumn id="7" name="Email"/>
+    <tableColumn id="8" name="Currency"/>
+    <tableColumn id="9" name="Payment Terms"/>
+    <tableColumn id="10" name="Status"/>
+    <tableColumn id="11" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table40.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="40" name="tbl_DIM_ProductCostHistory" displayName="tbl_DIM_ProductCostHistory" ref="B11:J12" headerRowCount="1">
+  <autoFilter ref="B11:J12"/>
+  <tableColumns count="9">
+    <tableColumn id="2" name="CostKey"/>
+    <tableColumn id="3" name="SKU"/>
+    <tableColumn id="4" name="Collection"/>
+    <tableColumn id="5" name="TotalLandedCost"/>
+    <tableColumn id="6" name="SellingPrice"/>
+    <tableColumn id="7" name="ExpectedGrossMarginPct"/>
+    <tableColumn id="8" name="EffectiveFromDate"/>
+    <tableColumn id="9" name="EffectiveToDate"/>
+    <tableColumn id="10" name="ActiveFlag"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table41.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="41" name="tbl_FACT_OrderLines" displayName="tbl_FACT_OrderLines" ref="B11:O12" headerRowCount="1">
   <autoFilter ref="B11:O12"/>
   <tableColumns count="14">
     <tableColumn id="2" name="OrderLineKey"/>
@@ -721,8 +1013,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="tbl_FACT_Refunds" displayName="tbl_FACT_Refunds" ref="B11:F12" headerRowCount="1">
+<file path=xl/tables/table42.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="42" name="tbl_FACT_Refunds" displayName="tbl_FACT_Refunds" ref="B11:F12" headerRowCount="1">
   <autoFilter ref="B11:F12"/>
   <tableColumns count="5">
     <tableColumn id="2" name="RefundKey"/>
@@ -735,8 +1027,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="tbl_FACT_InventoryMovements" displayName="tbl_FACT_InventoryMovements" ref="B11:H12" headerRowCount="1">
+<file path=xl/tables/table43.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="43" name="tbl_FACT_InventoryMovements" displayName="tbl_FACT_InventoryMovements" ref="B11:H12" headerRowCount="1">
   <autoFilter ref="B11:H12"/>
   <tableColumns count="7">
     <tableColumn id="2" name="MovementKey"/>
@@ -751,8 +1043,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="tbl_FACT_Payments" displayName="tbl_FACT_Payments" ref="B11:H12" headerRowCount="1">
+<file path=xl/tables/table44.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="44" name="tbl_FACT_Payments" displayName="tbl_FACT_Payments" ref="B11:H12" headerRowCount="1">
   <autoFilter ref="B11:H12"/>
   <tableColumns count="7">
     <tableColumn id="2" name="PaymentKey"/>
@@ -767,40 +1059,105 @@
 </table>
 </file>
 
-<file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="29" name="tbl_FACT_ManualExpenses" displayName="tbl_FACT_ManualExpenses" ref="B11:I12" headerRowCount="1">
-  <autoFilter ref="B11:I12"/>
-  <tableColumns count="8">
+<file path=xl/tables/table45.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="45" name="tbl_FACT_ManualExpenses" displayName="tbl_FACT_ManualExpenses" ref="B11:M12" headerRowCount="1">
+  <autoFilter ref="B11:M12"/>
+  <tableColumns count="12">
     <tableColumn id="2" name="ExpenseKey"/>
-    <tableColumn id="3" name="Date"/>
-    <tableColumn id="4" name="Category"/>
-    <tableColumn id="5" name="CostCenter"/>
-    <tableColumn id="6" name="Description"/>
+    <tableColumn id="3" name="ExpenseDate"/>
+    <tableColumn id="4" name="ExpenseCategory"/>
+    <tableColumn id="5" name="ExpenseSubcategory"/>
+    <tableColumn id="6" name="SupplierID"/>
     <tableColumn id="7" name="Amount"/>
-    <tableColumn id="8" name="PaymentMethod"/>
-    <tableColumn id="9" name="EnteredBy"/>
+    <tableColumn id="8" name="Currency"/>
+    <tableColumn id="9" name="PaymentMethod"/>
+    <tableColumn id="10" name="RelatedCollection"/>
+    <tableColumn id="11" name="RelatedSKU"/>
+    <tableColumn id="12" name="CostCenter"/>
+    <tableColumn id="13" name="InvoiceNumber"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tbl_SupplierMaster" displayName="tbl_SupplierMaster" ref="B17:G18" headerRowCount="1">
-  <autoFilter ref="B17:G18"/>
-  <tableColumns count="6">
-    <tableColumn id="2" name="Supplier ID"/>
-    <tableColumn id="3" name="Supplier Name"/>
-    <tableColumn id="4" name="Contact"/>
-    <tableColumn id="5" name="Category"/>
-    <tableColumn id="6" name="Lead Time (Days)"/>
-    <tableColumn id="7" name="Status"/>
+<file path=xl/tables/table46.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="46" name="tbl_FACT_CapitalTransactions" displayName="tbl_FACT_CapitalTransactions" ref="B11:F12" headerRowCount="1">
+  <autoFilter ref="B11:F12"/>
+  <tableColumns count="5">
+    <tableColumn id="2" name="CapitalKey"/>
+    <tableColumn id="3" name="Date"/>
+    <tableColumn id="4" name="Owner"/>
+    <tableColumn id="5" name="TransactionType"/>
+    <tableColumn id="6" name="Amount"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="30" name="tbl_LOG_RefreshHistory" displayName="tbl_LOG_RefreshHistory" ref="B11:I12" headerRowCount="1">
+<file path=xl/tables/table47.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="47" name="tbl_FACT_PurchaseOrderHeader" displayName="tbl_FACT_PurchaseOrderHeader" ref="B11:G12" headerRowCount="1">
+  <autoFilter ref="B11:G12"/>
+  <tableColumns count="6">
+    <tableColumn id="2" name="PONumber"/>
+    <tableColumn id="3" name="SupplierID"/>
+    <tableColumn id="4" name="OrderDate"/>
+    <tableColumn id="5" name="ExpectedDeliveryDate"/>
+    <tableColumn id="6" name="Status"/>
+    <tableColumn id="7" name="Currency"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table48.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="48" name="tbl_FACT_PurchaseOrderLines" displayName="tbl_FACT_PurchaseOrderLines" ref="B11:F12" headerRowCount="1">
+  <autoFilter ref="B11:F12"/>
+  <tableColumns count="5">
+    <tableColumn id="2" name="PONumber"/>
+    <tableColumn id="3" name="SKU"/>
+    <tableColumn id="4" name="QuantityOrdered"/>
+    <tableColumn id="5" name="UnitCost"/>
+    <tableColumn id="6" name="TotalCost"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table49.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="49" name="tbl_FACT_GoodsReceipt" displayName="tbl_FACT_GoodsReceipt" ref="B11:I12" headerRowCount="1">
+  <autoFilter ref="B11:I12"/>
+  <tableColumns count="8">
+    <tableColumn id="2" name="PONumber"/>
+    <tableColumn id="3" name="SKU"/>
+    <tableColumn id="4" name="GoodsReceivedDate"/>
+    <tableColumn id="5" name="QuantityReceived"/>
+    <tableColumn id="6" name="RemainingQuantity"/>
+    <tableColumn id="7" name="ActualUnitCost"/>
+    <tableColumn id="8" name="VarianceFromPO"/>
+    <tableColumn id="9" name="Warehouse"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="tbl_POHeader" displayName="tbl_POHeader" ref="B22:H23" headerRowCount="1">
+  <autoFilter ref="B22:H23"/>
+  <tableColumns count="7">
+    <tableColumn id="2" name="PO Number"/>
+    <tableColumn id="3" name="Supplier"/>
+    <tableColumn id="4" name="Order Date"/>
+    <tableColumn id="5" name="Expected Delivery Date"/>
+    <tableColumn id="6" name="Status"/>
+    <tableColumn id="7" name="Currency"/>
+    <tableColumn id="8" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table50.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="50" name="tbl_LOG_RefreshHistory" displayName="tbl_LOG_RefreshHistory" ref="B11:I12" headerRowCount="1">
   <autoFilter ref="B11:I12"/>
   <tableColumns count="8">
     <tableColumn id="2" name="RefreshID"/>
@@ -816,8 +1173,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table31.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="31" name="tbl_LOG_DataQuality" displayName="tbl_LOG_DataQuality" ref="B11:G12" headerRowCount="1">
+<file path=xl/tables/table51.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="51" name="tbl_LOG_DataQuality" displayName="tbl_LOG_DataQuality" ref="B11:G12" headerRowCount="1">
   <autoFilter ref="B11:G12"/>
   <tableColumns count="6">
     <tableColumn id="2" name="CheckID"/>
@@ -831,23 +1188,40 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tbl_PurchaseOrders" displayName="tbl_PurchaseOrders" ref="B22:G23" headerRowCount="1">
-  <autoFilter ref="B22:G23"/>
-  <tableColumns count="6">
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="tbl_POLines" displayName="tbl_POLines" ref="B27:F28" headerRowCount="1">
+  <autoFilter ref="B27:F28"/>
+  <tableColumns count="5">
     <tableColumn id="2" name="PO Number"/>
-    <tableColumn id="3" name="Supplier ID"/>
-    <tableColumn id="4" name="Date"/>
-    <tableColumn id="5" name="Amount (EGP)"/>
-    <tableColumn id="6" name="Status"/>
-    <tableColumn id="7" name="Expected Delivery"/>
+    <tableColumn id="3" name="SKU"/>
+    <tableColumn id="4" name="Quantity Ordered"/>
+    <tableColumn id="5" name="Unit Cost"/>
+    <tableColumn id="6" name="Total Cost"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="tbl_ValidationRules" displayName="tbl_ValidationRules" ref="B17:E18" headerRowCount="1">
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tbl_GoodsReceipt" displayName="tbl_GoodsReceipt" ref="B32:J33" headerRowCount="1">
+  <autoFilter ref="B32:J33"/>
+  <tableColumns count="9">
+    <tableColumn id="2" name="PO Number"/>
+    <tableColumn id="3" name="SKU"/>
+    <tableColumn id="4" name="Goods Received Date"/>
+    <tableColumn id="5" name="Quantity Received"/>
+    <tableColumn id="6" name="Remaining Quantity"/>
+    <tableColumn id="7" name="Actual Unit Cost"/>
+    <tableColumn id="8" name="Variance from PO"/>
+    <tableColumn id="9" name="Warehouse"/>
+    <tableColumn id="10" name="Receiver"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tbl_ValidationRules" displayName="tbl_ValidationRules" ref="B17:E18" headerRowCount="1">
   <autoFilter ref="B17:E18"/>
   <tableColumns count="4">
     <tableColumn id="2" name="Rule ID"/>
@@ -859,63 +1233,14 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="tbl_RefreshStatusSummary" displayName="tbl_RefreshStatusSummary" ref="B22:E23" headerRowCount="1">
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="tbl_RefreshStatusSummary" displayName="tbl_RefreshStatusSummary" ref="B22:E23" headerRowCount="1">
   <autoFilter ref="B22:E23"/>
   <tableColumns count="4">
     <tableColumn id="2" name="Table"/>
     <tableColumn id="3" name="Last Refreshed"/>
     <tableColumn id="4" name="Row Count"/>
     <tableColumn id="5" name="Status"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tbl_ChartOfAccounts" displayName="tbl_ChartOfAccounts" ref="B31:F32" headerRowCount="1">
-  <autoFilter ref="B31:F32"/>
-  <tableColumns count="5">
-    <tableColumn id="2" name="Account Code"/>
-    <tableColumn id="3" name="Account Name"/>
-    <tableColumn id="4" name="Statement"/>
-    <tableColumn id="5" name="P&amp;L / BS Line"/>
-    <tableColumn id="6" name="Source"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tbl_VersionLog" displayName="tbl_VersionLog" ref="B36:E39" headerRowCount="1">
-  <autoFilter ref="B36:E39"/>
-  <tableColumns count="4">
-    <tableColumn id="2" name="Version"/>
-    <tableColumn id="3" name="Date"/>
-    <tableColumn id="4" name="Phase"/>
-    <tableColumn id="5" name="Summary"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="tbl_RAW_Orders" displayName="tbl_RAW_Orders" ref="B11:N12" headerRowCount="1">
-  <autoFilter ref="B11:N12"/>
-  <tableColumns count="13">
-    <tableColumn id="2" name="OrderID"/>
-    <tableColumn id="3" name="OrderNumber"/>
-    <tableColumn id="4" name="CreatedAt"/>
-    <tableColumn id="5" name="UpdatedAt"/>
-    <tableColumn id="6" name="FinancialStatus"/>
-    <tableColumn id="7" name="FulfillmentStatus"/>
-    <tableColumn id="8" name="Currency"/>
-    <tableColumn id="9" name="TotalPrice"/>
-    <tableColumn id="10" name="SubtotalPrice"/>
-    <tableColumn id="11" name="TotalDiscounts"/>
-    <tableColumn id="12" name="TotalTax"/>
-    <tableColumn id="13" name="CustomerID"/>
-    <tableColumn id="14" name="LocationID"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1588,17 +1913,27 @@
     <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1630,7 +1965,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Operating expense tracking — the manual-entry source for costs that do not come from Shopify (rent, salaries, ad spend, shipping, etc.).</t>
+          <t>Complete operating-expense entry module — the manual-entry source for costs that do not come from Shopify (rent, salaries, ad spend, shipping, etc.), with category/subcategory lookups, optional SKU/Collection attribution, cost-center tagging, document references, and duplicate detection.</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1977,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>None — this sheet is the input. Category list validated against 15_Settings Chart of Accounts.</t>
+          <t>15_Settings lookup tables (Expense Category, Expense Subcategory, Payment Method, Currency, Cost Center), tbl_SupplierMaster (12_Suppliers), RAW_Variants / RAW_Collections (live Shopify SKUs/collections).</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1989,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>FACT_ManualExpenses (Data Model fact table).</t>
+          <t>FACT_ManualExpenses (Data Model-ready hidden mirror).</t>
         </is>
       </c>
     </row>
@@ -1666,7 +2001,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Feeds the Data Model as its own fact table, kept structurally separate from Shopify-sourced facts so system-of-record vs. hand-entered data is always distinguishable. Categories map to 15_Settings!ChartOfAccounts.</t>
+          <t>Feeds the Data Model as its own fact table, kept structurally separate from Shopify-sourced facts so system-of-record vs. hand-entered data is always distinguishable. Related SKU/Collection dropdowns pull from the live Shopify RAW_ tables, not a separate manual list, so an expense can be tied to real product/collection data. Category list is fully configurable on 15_Settings — nothing is hardcoded.</t>
         </is>
       </c>
     </row>
@@ -1678,7 +2013,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>This IS the source — no external system. Manual entry only.</t>
+          <t>This IS the source — no external system. Document Management: Invoice Number/File Name/File Path/Cloud Link are references only — see passress-mis/PHASE3_DOCUMENTATION.md; a future phase may connect Cloud Link directly to OneDrive/SharePoint.</t>
         </is>
       </c>
     </row>
@@ -1749,102 +2084,210 @@
     <row r="16">
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>MANUAL EXPENSE ENTRY  (green cells = type here)</t>
+          <t>MANUAL EXPENSE ENTRY  (green cells = type here — Expense ID and Possible Duplicate are automatic)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Expense ID</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>Expense Date</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>Expense Category</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>Expense Subcategory</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="H17" s="17" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="I17" s="17" t="inlineStr">
+        <is>
+          <t>Payment Method</t>
+        </is>
+      </c>
+      <c r="J17" s="17" t="inlineStr">
+        <is>
+          <t>Related Collection</t>
+        </is>
+      </c>
+      <c r="K17" s="17" t="inlineStr">
+        <is>
+          <t>Related SKU</t>
+        </is>
+      </c>
+      <c r="L17" s="17" t="inlineStr">
         <is>
           <t>Cost Center</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>Amount (EGP)</t>
-        </is>
-      </c>
-      <c r="G17" s="15" t="inlineStr">
-        <is>
-          <t>Payment Method</t>
-        </is>
-      </c>
-      <c r="H17" s="15" t="inlineStr">
-        <is>
-          <t>Entered By</t>
+      <c r="M17" s="17" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="N17" s="17" t="inlineStr">
+        <is>
+          <t>Invoice Number</t>
+        </is>
+      </c>
+      <c r="O17" s="17" t="inlineStr">
+        <is>
+          <t>File Name</t>
+        </is>
+      </c>
+      <c r="P17" s="17" t="inlineStr">
+        <is>
+          <t>File Path</t>
+        </is>
+      </c>
+      <c r="Q17" s="17" t="inlineStr">
+        <is>
+          <t>Cloud Link</t>
+        </is>
+      </c>
+      <c r="R17" s="17" t="inlineStr">
+        <is>
+          <t>Possible Duplicate</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="18">
+        <f>"EXP-"&amp;TEXT(ROW()-17,"00000")</f>
+        <v/>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
         <is>
           <t>Rent</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="n"/>
+      <c r="G18" s="19" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H18" s="19" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="I18" s="19" t="inlineStr">
+        <is>
+          <t>Bank Transfer</t>
+        </is>
+      </c>
+      <c r="J18" s="19" t="n"/>
+      <c r="K18" s="19" t="n"/>
+      <c r="L18" s="19" t="inlineStr">
         <is>
           <t>Head Office</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="M18" s="19" t="inlineStr">
         <is>
           <t>EXAMPLE — January office rent</t>
         </is>
       </c>
-      <c r="F18" s="16" t="n">
-        <v>15000</v>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>Bank Transfer</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
+      <c r="N18" s="19" t="inlineStr">
+        <is>
+          <t>INV-2026-0001</t>
+        </is>
+      </c>
+      <c r="O18" s="19" t="inlineStr">
+        <is>
+          <t>jan-rent.pdf</t>
+        </is>
+      </c>
+      <c r="P18" s="19" t="inlineStr">
+        <is>
+          <t>/Finance/2026/Rent/</t>
+        </is>
+      </c>
+      <c r="Q18" s="19" t="n"/>
+      <c r="R18" s="18">
+        <f>IF(COUNTIFS(tbl_ManualExpenses[Expense Date],[@[Expense Date]],tbl_ManualExpenses[Supplier],[@Supplier],tbl_ManualExpenses[Amount],[@Amount])&gt;1,"Possible Duplicate","")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
   <mergeCells count="16">
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B8:R8"/>
+    <mergeCell ref="A3:R3"/>
+    <mergeCell ref="B4:R4"/>
     <mergeCell ref="B12:C13"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H12:I13"/>
     <mergeCell ref="F12:G13"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="H12:I13"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A2:R2"/>
     <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B7:R7"/>
+    <mergeCell ref="B6:R6"/>
     <mergeCell ref="D12:E13"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="B5:R5"/>
   </mergeCells>
+  <dataValidations count="8">
+    <dataValidation sqref="D18:D501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the Expense Category list — free text isn't accepted here." promptTitle="Expense Category" prompt="Choose from the Expense Category list on 15_Settings." type="list" errorStyle="stop">
+      <formula1>=LookupExpenseCategory</formula1>
+    </dataValidation>
+    <dataValidation sqref="E18:E501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the Expense Subcategory list — free text isn't accepted here." promptTitle="Expense Subcategory" prompt="Choose from the Expense Subcategory list on 15_Settings." type="list" errorStyle="stop">
+      <formula1>=LookupExpenseSubcategory</formula1>
+    </dataValidation>
+    <dataValidation sqref="F18:F501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the Supplier list — free text isn't accepted here." promptTitle="Supplier" prompt="Choose from Supplier Master (12_Suppliers). Leave blank if this expense has no supplier." type="list" errorStyle="stop">
+      <formula1>=SupplierNameList</formula1>
+    </dataValidation>
+    <dataValidation sqref="H18:H501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the Currency list — free text isn't accepted here." promptTitle="Currency" prompt="Choose from the Currency list on 15_Settings." type="list" errorStyle="stop">
+      <formula1>=LookupCurrency</formula1>
+    </dataValidation>
+    <dataValidation sqref="I18:I501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the Payment Method list — free text isn't accepted here." promptTitle="Payment Method" prompt="Choose from the Payment Method list on 15_Settings." type="list" errorStyle="stop">
+      <formula1>=LookupPaymentMethod</formula1>
+    </dataValidation>
+    <dataValidation sqref="J18:J501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the Related Collection (optional) list — free text isn't accepted here." promptTitle="Related Collection (optional)" prompt="Choose a live Shopify collection, or leave blank." type="list" errorStyle="stop">
+      <formula1>=CollectionTitleList</formula1>
+    </dataValidation>
+    <dataValidation sqref="K18:K501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the Related SKU (optional) list — free text isn't accepted here." promptTitle="Related SKU (optional)" prompt="Choose a live Shopify SKU, or leave blank." type="list" errorStyle="stop">
+      <formula1>=SKUList</formula1>
+    </dataValidation>
+    <dataValidation sqref="L18:L501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the Cost Center list — free text isn't accepted here." promptTitle="Cost Center" prompt="Choose from the Cost Center list on 15_Settings." type="list" errorStyle="stop">
+      <formula1>=LookupCostCenter</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1863,11 +2306,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1911,7 +2357,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>None — this sheet is the input.</t>
+          <t>15_Settings lookup tables (Owner, Capital Transaction Type).</t>
         </is>
       </c>
     </row>
@@ -1923,7 +2369,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>FACT_ManualExpenses-style capital ledger (own table) feeding the Data Model owner-equity measures.</t>
+          <t>FACT_CapitalTransactions (Data Model-ready hidden mirror).</t>
         </is>
       </c>
     </row>
@@ -1935,7 +2381,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>The only source that grows/shrinks Capital Invested and Owner Equity on the dashboards.</t>
+          <t>The only source that grows/shrinks Capital Invested and Owner Equity in future financial calculations. Owner and Transaction Type are both configurable lookups on 15_Settings, not hardcoded.</t>
         </is>
       </c>
     </row>
@@ -2018,82 +2464,118 @@
     <row r="16">
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>CAPITAL TRANSACTIONS  (green cells = type here)</t>
+          <t>CAPITAL TRANSACTIONS  (green cells = type here — Capital ID and Possible Duplicate are automatic)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Capital ID</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>Type (Contribution/Withdrawal)</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="inlineStr">
-        <is>
-          <t>Amount (EGP)</t>
-        </is>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>Transaction Type</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="H17" s="17" t="inlineStr">
         <is>
           <t>Entered By</t>
         </is>
       </c>
+      <c r="I17" s="17" t="inlineStr">
+        <is>
+          <t>Possible Duplicate</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="18">
+        <f>"CAP-"&amp;TEXT(ROW()-17,"00000")</f>
+        <v/>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Contribution</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>Capital Contribution</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G18" s="19" t="inlineStr">
         <is>
           <t>EXAMPLE — founder capital injection</t>
         </is>
       </c>
-      <c r="E18" s="16" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="H18" s="19" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
+      </c>
+      <c r="I18" s="18">
+        <f>IF(COUNTIFS(tbl_CapitalTransactions[Date],[@Date],tbl_CapitalTransactions[Owner],[@Owner],tbl_CapitalTransactions[Amount],[@Amount])&gt;1,"Possible Duplicate","")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
   <mergeCells count="16">
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="A2:F2"/>
     <mergeCell ref="B12:C13"/>
     <mergeCell ref="F11:G11"/>
-    <mergeCell ref="B7:F7"/>
     <mergeCell ref="H11:I11"/>
-    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="H12:I13"/>
     <mergeCell ref="F12:G13"/>
+    <mergeCell ref="B7:I7"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="H12:I13"/>
+    <mergeCell ref="B6:I6"/>
     <mergeCell ref="D11:E11"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B5:F5"/>
     <mergeCell ref="D12:E13"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B4:I4"/>
   </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="D18:D501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the Owner list — free text isn't accepted here." promptTitle="Owner" prompt="Choose from the Owner list on 15_Settings." type="list" errorStyle="stop">
+      <formula1>=LookupOwner</formula1>
+    </dataValidation>
+    <dataValidation sqref="E18:E501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the Transaction Type list — free text isn't accepted here." promptTitle="Transaction Type" prompt="Capital Contribution or Capital Withdrawal — from the list on 15_Settings." type="list" errorStyle="stop">
+      <formula1>=LookupCapitalTransactionType</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2108,16 +2590,19 @@
     <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -2149,7 +2634,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Supplier master data and purchase order tracking.</t>
+          <t>Supplier master data and the complete purchasing engine: Purchase Order Header, Purchase Order Lines, and Goods Receipt, with a Draft-through-Closed status workflow.</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2646,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>None — this sheet is the input.</t>
+          <t>15_Settings lookup tables (Supplier Type, Supplier Status, Currency, PO Status, Warehouse), RAW_Variants (live Shopify SKUs).</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2658,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Supplier master table, Purchase Order log — future Data Model facts (FACT_Purchases).</t>
+          <t>DIM_Supplier, FACT_PurchaseOrderHeader, FACT_PurchaseOrderLines, FACT_GoodsReceipt (Data Model-ready hidden mirrors).</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2670,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Purchase Order log will link to DIM_Product once SKU-level purchasing is tracked (Phase 3+).</t>
+          <t>PO Lines and Goods Receipt both key on PO Number (from PO Header) and SKU (from the live Shopify variant list), not a separate manual product list. Goods Receipt's Remaining Quantity and Variance from PO are computed by looking up PO Lines for the same PO Number + SKU.</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2682,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>This IS the source today. Candidate for supplier-portal or accounting-system integration later (see Future Integrations).</t>
+          <t>This IS the source today. Candidate for supplier-portal or accounting-system integration later (see Future Integrations in the Phase 0 architecture).</t>
         </is>
       </c>
     </row>
@@ -2212,19 +2697,19 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>PURCHASES YTD</t>
+          <t>OPEN POS</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>AVG LEAD TIME</t>
+          <t>PURCHASES YTD</t>
         </is>
       </c>
       <c r="G11" s="7" t="n"/>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>OUTSTANDING PAYABLES</t>
+          <t>OUTSTANDING RECEIPTS</t>
         </is>
       </c>
       <c r="I11" s="7" t="n"/>
@@ -2268,165 +2753,377 @@
     <row r="16">
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>SUPPLIER MASTER  (green cells = type here)</t>
+          <t>SUPPLIER MASTER  (green cells = type here — Supplier ID is automatic)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Supplier ID</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>Supplier Name</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>Lead Time (Days)</t>
-        </is>
-      </c>
-      <c r="G17" s="15" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>Supplier Type</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>Contact Person</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H17" s="17" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="I17" s="17" t="inlineStr">
+        <is>
+          <t>Payment Terms</t>
+        </is>
+      </c>
+      <c r="J17" s="17" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
+      <c r="K17" s="17" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>SUP-001</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="B18" s="18">
+        <f>"SUP-"&amp;TEXT(ROW()-17,"00000")</f>
+        <v/>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>EXAMPLE — ABC Textiles</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>Fabric</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>Mona Ahmed</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr">
+        <is>
+          <t>+20 100 000 0000</t>
+        </is>
+      </c>
+      <c r="G18" s="19" t="inlineStr">
         <is>
           <t>contact@example.com</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>Fabric</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="H18" s="19" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="I18" s="19" t="inlineStr">
+        <is>
+          <t>Net 30</t>
+        </is>
+      </c>
+      <c r="J18" s="19" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
+      <c r="K18" s="19" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>PURCHASE ORDER LOG  (green cells = type here)</t>
+          <t>PURCHASE ORDER HEADER  (green cells = type here — PO Number is automatic)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>PO Number</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>Supplier ID</t>
-        </is>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>Amount (EGP)</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>Order Date</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>Expected Delivery Date</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G22" s="15" t="inlineStr">
-        <is>
-          <t>Expected Delivery</t>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="H22" s="17" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>PO-2026-001</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>SUP-001</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="B23" s="18">
+        <f>"PO-"&amp;TEXT(ROW()-22,"00000")</f>
+        <v/>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>EXAMPLE — ABC Textiles</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="inlineStr">
         <is>
           <t>2026-01-10</t>
         </is>
       </c>
-      <c r="E23" s="16" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>Ordered</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="E23" s="19" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
+      <c r="F23" s="19" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="G23" s="19" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="H23" s="19" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>PURCHASE ORDER LINES  (green cells = type here — Total Cost is automatic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>PO Number</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>Quantity Ordered</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="19" t="n"/>
+      <c r="C28" s="19" t="n"/>
+      <c r="D28" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="E28" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="F28" s="18">
+        <f>[@[Quantity Ordered]]*[@[Unit Cost]]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>GOODS RECEIPT  (green cells = type here — Remaining Quantity and Variance from PO are automatic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>PO Number</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>Goods Received Date</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>Quantity Received</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>Remaining Quantity</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>Actual Unit Cost</t>
+        </is>
+      </c>
+      <c r="H32" s="17" t="inlineStr">
+        <is>
+          <t>Variance from PO</t>
+        </is>
+      </c>
+      <c r="I32" s="17" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="J32" s="17" t="inlineStr">
+        <is>
+          <t>Receiver</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="19" t="n"/>
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F33" s="18">
+        <f>SUMIFS(tbl_POLines[Quantity Ordered],tbl_POLines[PO Number],[@[PO Number]],tbl_POLines[SKU],[@SKU])-SUMIFS(tbl_GoodsReceipt[Quantity Received],tbl_GoodsReceipt[PO Number],[@[PO Number]],tbl_GoodsReceipt[SKU],[@SKU])</f>
+        <v/>
+      </c>
+      <c r="G33" s="19" t="n">
+        <v>122</v>
+      </c>
+      <c r="H33" s="18">
+        <f>[@[Actual Unit Cost]]-SUMIFS(tbl_POLines[Unit Cost],tbl_POLines[PO Number],[@[PO Number]],tbl_POLines[SKU],[@SKU])</f>
+        <v/>
+      </c>
+      <c r="I33" s="19" t="inlineStr">
+        <is>
+          <t>Main Warehouse</t>
+        </is>
+      </c>
+      <c r="J33" s="19" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
   <mergeCells count="16">
+    <mergeCell ref="B7:J7"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="B12:C13"/>
     <mergeCell ref="F11:G11"/>
+    <mergeCell ref="B5:J5"/>
     <mergeCell ref="H11:I11"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="F12:G13"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="H12:I13"/>
-    <mergeCell ref="F12:G13"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A3:G3"/>
     <mergeCell ref="D11:E11"/>
+    <mergeCell ref="A3:J3"/>
     <mergeCell ref="D12:E13"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B8:J8"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="B6:J6"/>
   </mergeCells>
+  <dataValidations count="11">
+    <dataValidation sqref="D18:D501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the Supplier Type list — free text isn't accepted here." promptTitle="Supplier Type" prompt="Choose from the Supplier Type list on 15_Settings." type="list" errorStyle="stop">
+      <formula1>=LookupSupplierType</formula1>
+    </dataValidation>
+    <dataValidation sqref="H18:H501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the Currency list — free text isn't accepted here." promptTitle="Currency" prompt="Choose from the Currency list on 15_Settings." type="list" errorStyle="stop">
+      <formula1>=LookupCurrency</formula1>
+    </dataValidation>
+    <dataValidation sqref="J18:J501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the Status list — free text isn't accepted here." promptTitle="Status" prompt="Choose from the Supplier Status list on 15_Settings." type="list" errorStyle="stop">
+      <formula1>=LookupSupplierStatus</formula1>
+    </dataValidation>
+    <dataValidation sqref="C23:C501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the Supplier list — free text isn't accepted here." promptTitle="Supplier" prompt="Choose from Supplier Master (this sheet, above)." type="list" errorStyle="stop">
+      <formula1>=SupplierNameList</formula1>
+    </dataValidation>
+    <dataValidation sqref="F23:F501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the Status list — free text isn't accepted here." promptTitle="Status" prompt="Draft → Approved → Sent → Partially Received → Received → Closed, or Cancelled at any point." type="list" errorStyle="stop">
+      <formula1>=LookupPOStatus</formula1>
+    </dataValidation>
+    <dataValidation sqref="G23:G501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the Currency list — free text isn't accepted here." promptTitle="Currency" prompt="Choose from the Currency list on 15_Settings." type="list" errorStyle="stop">
+      <formula1>=LookupCurrency</formula1>
+    </dataValidation>
+    <dataValidation sqref="B28:B501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the PO Number list — free text isn't accepted here." promptTitle="PO Number" prompt="Choose an existing PO Number from Purchase Order Header, above." type="list" errorStyle="stop">
+      <formula1>=POHeaderList</formula1>
+    </dataValidation>
+    <dataValidation sqref="C28:C501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the SKU list — free text isn't accepted here." promptTitle="SKU" prompt="Choose a live Shopify SKU." type="list" errorStyle="stop">
+      <formula1>=SKUList</formula1>
+    </dataValidation>
+    <dataValidation sqref="B33:B501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the PO Number list — free text isn't accepted here." promptTitle="PO Number" prompt="Choose an existing PO Number from Purchase Order Header, above." type="list" errorStyle="stop">
+      <formula1>=POHeaderList</formula1>
+    </dataValidation>
+    <dataValidation sqref="C33:C501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the SKU list — free text isn't accepted here." promptTitle="SKU" prompt="Choose a live Shopify SKU." type="list" errorStyle="stop">
+      <formula1>=SKUList</formula1>
+    </dataValidation>
+    <dataValidation sqref="I33:I501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the Warehouse list — free text isn't accepted here." promptTitle="Warehouse" prompt="Choose from the Warehouse list on 15_Settings." type="list" errorStyle="stop">
+      <formula1>=LookupWarehouse</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="2">
+  <tableParts count="4">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2610,7 +3307,7 @@
     <row r="17">
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>[ Discount Trend (Chart)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Discount Trend (Chart)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="C17" s="14" t="n"/>
@@ -2717,7 +3414,7 @@
     <row r="28">
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>[ Campaign Performance (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Campaign Performance (PivotTable)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="C28" s="14" t="n"/>
@@ -2726,7 +3423,7 @@
       <c r="F28" s="14" t="n"/>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>[ Discount Code Usage (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Discount Code Usage (PivotTable)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="H28" s="14" t="n"/>
@@ -3039,44 +3736,44 @@
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>Rule ID</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>Check Name</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>Applies To</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>Threshold</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>DQ-001</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>No orders older than lookback window missing</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>RAW_Orders</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>0 gaps</t>
         </is>
@@ -3090,32 +3787,32 @@
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>Table</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>Last Refreshed</t>
         </is>
       </c>
-      <c r="D22" s="19" t="inlineStr">
+      <c r="D22" s="24" t="inlineStr">
         <is>
           <t>Row Count</t>
         </is>
       </c>
-      <c r="E22" s="19" t="inlineStr">
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="20" t="n"/>
-      <c r="C23" s="20" t="n"/>
-      <c r="D23" s="20" t="n"/>
-      <c r="E23" s="20" t="n"/>
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -3152,11 +3849,11 @@
     <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
   </cols>
@@ -3252,119 +3949,119 @@
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>Company Name</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>Passress</t>
         </is>
       </c>
-      <c r="D13" s="24" t="inlineStr">
+      <c r="D13" s="28" t="inlineStr">
         <is>
           <t>Legal/trading name shown across dashboards.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Base Currency</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D14" s="28" t="inlineStr">
         <is>
           <t>Currency all imported Shopify data is stored in.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>Reporting Currency</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
       </c>
-      <c r="D15" s="24" t="inlineStr">
+      <c r="D15" s="28" t="inlineStr">
         <is>
           <t>Currency used for dashboard display. Phase 1: same as base.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>Fiscal Year Start Month</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>January</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D16" s="28" t="inlineStr">
         <is>
           <t>First month of fiscal year, used for YTD/FY calculations.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>Default VAT Rate</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D17" s="28" t="inlineStr">
         <is>
           <t>Egypt standard VAT — used for tax reconciliation.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>Target Gross Margin %</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D18" s="28" t="inlineStr">
         <is>
           <t>Benchmark used for profitability flags (Phase 3).</t>
         </is>
@@ -3378,102 +4075,102 @@
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="25" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D22" s="25" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>Shopify Store Domain</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="27" t="inlineStr">
         <is>
           <t>your-store.myshopify.com</t>
         </is>
       </c>
-      <c r="D23" s="24" t="inlineStr">
+      <c r="D23" s="28" t="inlineStr">
         <is>
           <t>Set this to your real *.myshopify.com domain to go live. The access token itself is never stored in this workbook — see power-query/README.md.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>Shopify API Version</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="27" t="inlineStr">
         <is>
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D24" s="24" t="inlineStr">
+      <c r="D24" s="28" t="inlineStr">
         <is>
           <t>Admin GraphQL API version pinned for Power Query — reviewed twice a year.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>Lookback Days (Incremental Refresh)</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C25" s="27" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D25" s="24" t="inlineStr">
+      <c r="D25" s="28" t="inlineStr">
         <is>
           <t>Rolling re-check window: days of history re-pulled on every refresh so late-updated records are never missed.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>Historical Backfill Start Date</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C26" s="27" t="inlineStr">
         <is>
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="D26" s="24" t="inlineStr">
+      <c r="D26" s="28" t="inlineStr">
         <is>
           <t>Earliest date fetched on a first-ever run (empty staging table). Ignored once a table has data — Lookback Days takes over.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>Max Pages Per Refresh (Safety Cap)</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C27" s="27" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="D27" s="24" t="inlineStr">
+      <c r="D27" s="28" t="inlineStr">
         <is>
           <t>Hard stop on pagination per query per refresh (500 pages x 250 records ≈ 125,000 rows), so a misconfigured filter can't run away.</t>
         </is>
@@ -3487,54 +4184,54 @@
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>Account Code</t>
         </is>
       </c>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="D31" s="22" t="inlineStr">
         <is>
           <t>Statement</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>P&amp;L / BS Line</t>
         </is>
       </c>
-      <c r="F31" s="17" t="inlineStr">
+      <c r="F31" s="22" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="18" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>4000</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>EXAMPLE — Net Sales</t>
         </is>
       </c>
-      <c r="D32" s="18" t="inlineStr">
+      <c r="D32" s="23" t="inlineStr">
         <is>
           <t>P&amp;L</t>
         </is>
       </c>
-      <c r="E32" s="18" t="inlineStr">
+      <c r="E32" s="23" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="F32" s="18" t="inlineStr">
+      <c r="F32" s="23" t="inlineStr">
         <is>
           <t>FACT_OrderLines</t>
         </is>
@@ -3548,90 +4245,623 @@
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="19" t="inlineStr">
+      <c r="B36" s="24" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="C36" s="19" t="inlineStr">
+      <c r="C36" s="24" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D36" s="19" t="inlineStr">
+      <c r="D36" s="24" t="inlineStr">
         <is>
           <t>Phase</t>
         </is>
       </c>
-      <c r="E36" s="19" t="inlineStr">
+      <c r="E36" s="24" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="20" t="inlineStr">
+      <c r="B37" s="18" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="C37" s="20" t="inlineStr">
+      <c r="C37" s="18" t="inlineStr">
         <is>
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="D37" s="20" t="inlineStr">
+      <c r="D37" s="18" t="inlineStr">
         <is>
           <t>Phase 1 — Workbook Foundation</t>
         </is>
       </c>
-      <c r="E37" s="20" t="inlineStr">
+      <c r="E37" s="18" t="inlineStr">
         <is>
           <t>Structure, tables, named ranges, documentation. No live data, no calculations.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="20" t="inlineStr">
+      <c r="B38" s="18" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="C38" s="20" t="inlineStr">
+      <c r="C38" s="18" t="inlineStr">
         <is>
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="D38" s="20" t="inlineStr">
+      <c r="D38" s="18" t="inlineStr">
         <is>
           <t>Phase 1 Finalization</t>
         </is>
       </c>
-      <c r="E38" s="20" t="inlineStr">
+      <c r="E38" s="18" t="inlineStr">
         <is>
           <t>01_Home's Workbook Version / Phase Completed KPI cards now read this table's last row live via formula — every future phase appends a row here and Home updates automatically.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="20" t="inlineStr">
+      <c r="B39" s="18" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="C39" s="20" t="inlineStr">
+      <c r="C39" s="18" t="inlineStr">
         <is>
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="D39" s="20" t="inlineStr">
+      <c r="D39" s="18" t="inlineStr">
         <is>
           <t>Phase 2 — Shopify GraphQL Ingestion Layer</t>
         </is>
       </c>
-      <c r="E39" s="20" t="inlineStr">
+      <c r="E39" s="18" t="inlineStr">
         <is>
           <t>Complete Power Query M layer: authentication (Extension.CurrentCredential, no hardcoded tokens), automatic cursor pagination, incremental refresh, HTTP/GraphQL error handling with backoff. Covers Products, Variants, Orders, Order Lines, Customers, Collections, Inventory Levels, Transactions, Refunds, Discounts — read-only (GraphQL query operations only). Added RAW_Transactions and RAW_Discounts staging sheets; revised RAW_Refunds and RAW_InventoryLevels to match verified Shopify Admin API schema. See /passress-mis/power-query/README.md and DOCUMENTATION.md. No dashboards yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="inlineStr">
+        <is>
+          <t>Phase 3 — Business Master Data &amp; Manual-Entry Engine</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>Product Cost Master with historical/versioned costing (05_Products). Complete Manual Expenses module: category/subcategory lookups, duplicate-flag column, document references (10_Expenses). Capital module (11_Capital). Expanded Supplier Master + full Purchase Order engine — Header/Lines/Goods Receipt with a Draft-to-Closed status workflow (12_Suppliers). Every dropdown sourced from an editable lookup table on 15_Settings — no hardcoded values — with input prompts and stop-on-error messages. SKU/Collection dropdowns reference the live Shopify RAW_ tables, not a separate manual list. New hidden Data-Model-ready mirrors: DIM_Supplier, DIM_ProductCostHistory, FACT_CapitalTransactions, FACT_PurchaseOrderHeader, FACT_PurchaseOrderLines, FACT_GoodsReceipt. See /passress-mis/PHASE3_DOCUMENTATION.md. Still no dashboards, PivotTables, DAX, or financial statements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>MASTER DATA LOOKUP TABLES  (orange cells = configurable — edit freely, every dropdown in the workbook reads from here)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="B44" s="25" t="inlineStr">
+        <is>
+          <t>Expense Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="29" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="29" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="29" t="inlineStr">
+        <is>
+          <t>Salaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="29" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="29" t="inlineStr">
+        <is>
+          <t>Shipping &amp; Logistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="29" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="29" t="inlineStr">
+        <is>
+          <t>Software &amp; Subscriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="29" t="inlineStr">
+        <is>
+          <t>Professional Fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="29" t="inlineStr">
+        <is>
+          <t>Bank Charges</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="29" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="B56" s="25" t="inlineStr">
+        <is>
+          <t>Expense Subcategory</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="29" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="29" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="29" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="29" t="inlineStr">
+        <is>
+          <t>Online Ads</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="29" t="inlineStr">
+        <is>
+          <t>Influencer</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="29" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="29" t="inlineStr">
+        <is>
+          <t>Courier</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="29" t="inlineStr">
+        <is>
+          <t>Customs &amp; Duties</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="29" t="inlineStr">
+        <is>
+          <t>Software License</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="29" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="29" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="29" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="B70" s="25" t="inlineStr">
+        <is>
+          <t>Cost Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="29" t="inlineStr">
+        <is>
+          <t>Head Office</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="29" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="29" t="inlineStr">
+        <is>
+          <t>E-Commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="29" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="29" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="B77" s="25" t="inlineStr">
+        <is>
+          <t>Payment Method</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="29" t="inlineStr">
+        <is>
+          <t>Bank Transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="29" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="29" t="inlineStr">
+        <is>
+          <t>Credit Card</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="29" t="inlineStr">
+        <is>
+          <t>Instapay</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="29" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="29" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="16" customHeight="1">
+      <c r="B85" s="25" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="29" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="29" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="29" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="16" customHeight="1">
+      <c r="B91" s="25" t="inlineStr">
+        <is>
+          <t>Supplier Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="29" t="inlineStr">
+        <is>
+          <t>Fabric</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="29" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="29" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="29" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="29" t="inlineStr">
+        <is>
+          <t>Logistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="29" t="inlineStr">
+        <is>
+          <t>Marketing Agency</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="29" t="inlineStr">
+        <is>
+          <t>Software Vendor</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="29" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="16" customHeight="1">
+      <c r="B101" s="25" t="inlineStr">
+        <is>
+          <t>Supplier Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="29" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="29" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="29" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="16" customHeight="1">
+      <c r="B106" s="25" t="inlineStr">
+        <is>
+          <t>Capital Transaction Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="29" t="inlineStr">
+        <is>
+          <t>Capital Contribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="29" t="inlineStr">
+        <is>
+          <t>Capital Withdrawal</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="16" customHeight="1">
+      <c r="B110" s="25" t="inlineStr">
+        <is>
+          <t>PO Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="29" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="29" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="29" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="29" t="inlineStr">
+        <is>
+          <t>Partially Received</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="29" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="29" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="29" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="16" customHeight="1">
+      <c r="B119" s="25" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="29" t="inlineStr">
+        <is>
+          <t>Main Warehouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="29" t="inlineStr">
+        <is>
+          <t>Retail Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" s="29" t="inlineStr">
+        <is>
+          <t>Third-Party Logistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="16" customHeight="1">
+      <c r="B124" s="25" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" s="29" t="inlineStr">
+        <is>
+          <t>Founder</t>
         </is>
       </c>
     </row>
@@ -3648,9 +4878,20 @@
     <mergeCell ref="B6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="2">
+  <tableParts count="13">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3765,86 +5006,86 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>OrderID</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>OrderNumber</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>CreatedAt</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>UpdatedAt</t>
         </is>
       </c>
-      <c r="F11" s="25" t="inlineStr">
+      <c r="F11" s="30" t="inlineStr">
         <is>
           <t>FinancialStatus</t>
         </is>
       </c>
-      <c r="G11" s="25" t="inlineStr">
+      <c r="G11" s="30" t="inlineStr">
         <is>
           <t>FulfillmentStatus</t>
         </is>
       </c>
-      <c r="H11" s="25" t="inlineStr">
+      <c r="H11" s="30" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="I11" s="25" t="inlineStr">
+      <c r="I11" s="30" t="inlineStr">
         <is>
           <t>TotalPrice</t>
         </is>
       </c>
-      <c r="J11" s="25" t="inlineStr">
+      <c r="J11" s="30" t="inlineStr">
         <is>
           <t>SubtotalPrice</t>
         </is>
       </c>
-      <c r="K11" s="25" t="inlineStr">
+      <c r="K11" s="30" t="inlineStr">
         <is>
           <t>TotalDiscounts</t>
         </is>
       </c>
-      <c r="L11" s="25" t="inlineStr">
+      <c r="L11" s="30" t="inlineStr">
         <is>
           <t>TotalTax</t>
         </is>
       </c>
-      <c r="M11" s="25" t="inlineStr">
+      <c r="M11" s="30" t="inlineStr">
         <is>
           <t>CustomerID</t>
         </is>
       </c>
-      <c r="N11" s="25" t="inlineStr">
+      <c r="N11" s="30" t="inlineStr">
         <is>
           <t>LocationID</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="26" t="n"/>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="26" t="n"/>
-      <c r="G12" s="26" t="n"/>
-      <c r="H12" s="26" t="n"/>
-      <c r="I12" s="26" t="n"/>
-      <c r="J12" s="26" t="n"/>
-      <c r="K12" s="26" t="n"/>
-      <c r="L12" s="26" t="n"/>
-      <c r="M12" s="26" t="n"/>
-      <c r="N12" s="26" t="n"/>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="31" t="n"/>
+      <c r="E12" s="31" t="n"/>
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="31" t="n"/>
+      <c r="H12" s="31" t="n"/>
+      <c r="I12" s="31" t="n"/>
+      <c r="J12" s="31" t="n"/>
+      <c r="K12" s="31" t="n"/>
+      <c r="L12" s="31" t="n"/>
+      <c r="M12" s="31" t="n"/>
+      <c r="N12" s="31" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -3972,68 +5213,68 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>LineItemID</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>OrderID</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>ProductID</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>VariantID</t>
         </is>
       </c>
-      <c r="F11" s="25" t="inlineStr">
+      <c r="F11" s="30" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="G11" s="25" t="inlineStr">
+      <c r="G11" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="H11" s="25" t="inlineStr">
+      <c r="H11" s="30" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="I11" s="25" t="inlineStr">
+      <c r="I11" s="30" t="inlineStr">
         <is>
           <t>UnitPrice</t>
         </is>
       </c>
-      <c r="J11" s="25" t="inlineStr">
+      <c r="J11" s="30" t="inlineStr">
         <is>
           <t>DiscountAllocated</t>
         </is>
       </c>
-      <c r="K11" s="25" t="inlineStr">
+      <c r="K11" s="30" t="inlineStr">
         <is>
           <t>TaxAllocated</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="26" t="n"/>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="26" t="n"/>
-      <c r="G12" s="26" t="n"/>
-      <c r="H12" s="26" t="n"/>
-      <c r="I12" s="26" t="n"/>
-      <c r="J12" s="26" t="n"/>
-      <c r="K12" s="26" t="n"/>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="31" t="n"/>
+      <c r="E12" s="31" t="n"/>
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="31" t="n"/>
+      <c r="H12" s="31" t="n"/>
+      <c r="I12" s="31" t="n"/>
+      <c r="J12" s="31" t="n"/>
+      <c r="K12" s="31" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -4161,68 +5402,68 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>TransactionID</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>OrderID</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F11" s="25" t="inlineStr">
+      <c r="F11" s="30" t="inlineStr">
         <is>
           <t>Gateway</t>
         </is>
       </c>
-      <c r="G11" s="25" t="inlineStr">
+      <c r="G11" s="30" t="inlineStr">
         <is>
           <t>AmountShop</t>
         </is>
       </c>
-      <c r="H11" s="25" t="inlineStr">
+      <c r="H11" s="30" t="inlineStr">
         <is>
           <t>CurrencyShop</t>
         </is>
       </c>
-      <c r="I11" s="25" t="inlineStr">
+      <c r="I11" s="30" t="inlineStr">
         <is>
           <t>CreatedAt</t>
         </is>
       </c>
-      <c r="J11" s="25" t="inlineStr">
+      <c r="J11" s="30" t="inlineStr">
         <is>
           <t>ProcessedAt</t>
         </is>
       </c>
-      <c r="K11" s="25" t="inlineStr">
+      <c r="K11" s="30" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="26" t="n"/>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="26" t="n"/>
-      <c r="G12" s="26" t="n"/>
-      <c r="H12" s="26" t="n"/>
-      <c r="I12" s="26" t="n"/>
-      <c r="J12" s="26" t="n"/>
-      <c r="K12" s="26" t="n"/>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="31" t="n"/>
+      <c r="E12" s="31" t="n"/>
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="31" t="n"/>
+      <c r="H12" s="31" t="n"/>
+      <c r="I12" s="31" t="n"/>
+      <c r="J12" s="31" t="n"/>
+      <c r="K12" s="31" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -4350,68 +5591,68 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>RefundLineItemID</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>RefundID</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>OrderID</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>LineItemID</t>
         </is>
       </c>
-      <c r="F11" s="25" t="inlineStr">
+      <c r="F11" s="30" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="G11" s="25" t="inlineStr">
+      <c r="G11" s="30" t="inlineStr">
         <is>
           <t>SubtotalAmount</t>
         </is>
       </c>
-      <c r="H11" s="25" t="inlineStr">
+      <c r="H11" s="30" t="inlineStr">
         <is>
           <t>TaxAmount</t>
         </is>
       </c>
-      <c r="I11" s="25" t="inlineStr">
+      <c r="I11" s="30" t="inlineStr">
         <is>
           <t>RefundCreatedAt</t>
         </is>
       </c>
-      <c r="J11" s="25" t="inlineStr">
+      <c r="J11" s="30" t="inlineStr">
         <is>
           <t>RefundProcessedAt</t>
         </is>
       </c>
-      <c r="K11" s="25" t="inlineStr">
+      <c r="K11" s="30" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="26" t="n"/>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="26" t="n"/>
-      <c r="G12" s="26" t="n"/>
-      <c r="H12" s="26" t="n"/>
-      <c r="I12" s="26" t="n"/>
-      <c r="J12" s="26" t="n"/>
-      <c r="K12" s="26" t="n"/>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="31" t="n"/>
+      <c r="E12" s="31" t="n"/>
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="31" t="n"/>
+      <c r="H12" s="31" t="n"/>
+      <c r="I12" s="31" t="n"/>
+      <c r="J12" s="31" t="n"/>
+      <c r="K12" s="31" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -4639,7 +5880,7 @@
     <row r="17">
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>[ Revenue Trend (Chart)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Revenue Trend (Chart)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="C17" s="14" t="n"/>
@@ -4739,7 +5980,7 @@
     <row r="26">
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>[ Expense Breakdown (Chart)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Expense Breakdown (Chart)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="C26" s="14" t="n"/>
@@ -4846,7 +6087,7 @@
     <row r="37">
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>[ Financial Summary (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Financial Summary (PivotTable)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="C37" s="14" t="n"/>
@@ -5053,56 +6294,56 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>ProductID</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>ProductType</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="F11" s="25" t="inlineStr">
+      <c r="F11" s="30" t="inlineStr">
         <is>
           <t>CollectionIDs</t>
         </is>
       </c>
-      <c r="G11" s="25" t="inlineStr">
+      <c r="G11" s="30" t="inlineStr">
         <is>
           <t>CreatedAt</t>
         </is>
       </c>
-      <c r="H11" s="25" t="inlineStr">
+      <c r="H11" s="30" t="inlineStr">
         <is>
           <t>UpdatedAt</t>
         </is>
       </c>
-      <c r="I11" s="25" t="inlineStr">
+      <c r="I11" s="30" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="26" t="n"/>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="26" t="n"/>
-      <c r="G12" s="26" t="n"/>
-      <c r="H12" s="26" t="n"/>
-      <c r="I12" s="26" t="n"/>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="31" t="n"/>
+      <c r="E12" s="31" t="n"/>
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="31" t="n"/>
+      <c r="H12" s="31" t="n"/>
+      <c r="I12" s="31" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -5230,68 +6471,68 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>VariantID</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>ProductID</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="F11" s="25" t="inlineStr">
+      <c r="F11" s="30" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="G11" s="25" t="inlineStr">
+      <c r="G11" s="30" t="inlineStr">
         <is>
           <t>CompareAtPrice</t>
         </is>
       </c>
-      <c r="H11" s="25" t="inlineStr">
+      <c r="H11" s="30" t="inlineStr">
         <is>
           <t>InventoryItemID</t>
         </is>
       </c>
-      <c r="I11" s="25" t="inlineStr">
+      <c r="I11" s="30" t="inlineStr">
         <is>
           <t>UnitCost</t>
         </is>
       </c>
-      <c r="J11" s="25" t="inlineStr">
+      <c r="J11" s="30" t="inlineStr">
         <is>
           <t>CreatedAt</t>
         </is>
       </c>
-      <c r="K11" s="25" t="inlineStr">
+      <c r="K11" s="30" t="inlineStr">
         <is>
           <t>UpdatedAt</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="26" t="n"/>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="26" t="n"/>
-      <c r="G12" s="26" t="n"/>
-      <c r="H12" s="26" t="n"/>
-      <c r="I12" s="26" t="n"/>
-      <c r="J12" s="26" t="n"/>
-      <c r="K12" s="26" t="n"/>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="31" t="n"/>
+      <c r="E12" s="31" t="n"/>
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="31" t="n"/>
+      <c r="H12" s="31" t="n"/>
+      <c r="I12" s="31" t="n"/>
+      <c r="J12" s="31" t="n"/>
+      <c r="K12" s="31" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -5414,38 +6655,38 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>InventoryItemID</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>LocationID</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="F11" s="25" t="inlineStr">
+      <c r="F11" s="30" t="inlineStr">
         <is>
           <t>UpdatedAt</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="26" t="n"/>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="26" t="n"/>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="31" t="n"/>
+      <c r="E12" s="31" t="n"/>
+      <c r="F12" s="31" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -5572,62 +6813,62 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>CustomerID</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>FirstName</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>LastName</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="F11" s="25" t="inlineStr">
+      <c r="F11" s="30" t="inlineStr">
         <is>
           <t>CreatedAt</t>
         </is>
       </c>
-      <c r="G11" s="25" t="inlineStr">
+      <c r="G11" s="30" t="inlineStr">
         <is>
           <t>UpdatedAt</t>
         </is>
       </c>
-      <c r="H11" s="25" t="inlineStr">
+      <c r="H11" s="30" t="inlineStr">
         <is>
           <t>OrdersCount</t>
         </is>
       </c>
-      <c r="I11" s="25" t="inlineStr">
+      <c r="I11" s="30" t="inlineStr">
         <is>
           <t>TotalSpent</t>
         </is>
       </c>
-      <c r="J11" s="25" t="inlineStr">
+      <c r="J11" s="30" t="inlineStr">
         <is>
           <t>DefaultAddressCountry</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="26" t="n"/>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="26" t="n"/>
-      <c r="G12" s="26" t="n"/>
-      <c r="H12" s="26" t="n"/>
-      <c r="I12" s="26" t="n"/>
-      <c r="J12" s="26" t="n"/>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="31" t="n"/>
+      <c r="E12" s="31" t="n"/>
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="31" t="n"/>
+      <c r="H12" s="31" t="n"/>
+      <c r="I12" s="31" t="n"/>
+      <c r="J12" s="31" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -5748,26 +6989,26 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>CollectionID</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>Handle</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="26" t="n"/>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="26" t="n"/>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="31" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -5897,80 +7138,80 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>DiscountNodeID</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>Typename</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F11" s="25" t="inlineStr">
+      <c r="F11" s="30" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="G11" s="25" t="inlineStr">
+      <c r="G11" s="30" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="H11" s="25" t="inlineStr">
+      <c r="H11" s="30" t="inlineStr">
         <is>
           <t>StartsAt</t>
         </is>
       </c>
-      <c r="I11" s="25" t="inlineStr">
+      <c r="I11" s="30" t="inlineStr">
         <is>
           <t>EndsAt</t>
         </is>
       </c>
-      <c r="J11" s="25" t="inlineStr">
+      <c r="J11" s="30" t="inlineStr">
         <is>
           <t>UsageLimit</t>
         </is>
       </c>
-      <c r="K11" s="25" t="inlineStr">
+      <c r="K11" s="30" t="inlineStr">
         <is>
           <t>AsyncUsageCount</t>
         </is>
       </c>
-      <c r="L11" s="25" t="inlineStr">
+      <c r="L11" s="30" t="inlineStr">
         <is>
           <t>CreatedAt</t>
         </is>
       </c>
-      <c r="M11" s="25" t="inlineStr">
+      <c r="M11" s="30" t="inlineStr">
         <is>
           <t>UpdatedAt</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="26" t="n"/>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="26" t="n"/>
-      <c r="G12" s="26" t="n"/>
-      <c r="H12" s="26" t="n"/>
-      <c r="I12" s="26" t="n"/>
-      <c r="J12" s="26" t="n"/>
-      <c r="K12" s="26" t="n"/>
-      <c r="L12" s="26" t="n"/>
-      <c r="M12" s="26" t="n"/>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="31" t="n"/>
+      <c r="E12" s="31" t="n"/>
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="31" t="n"/>
+      <c r="H12" s="31" t="n"/>
+      <c r="I12" s="31" t="n"/>
+      <c r="J12" s="31" t="n"/>
+      <c r="K12" s="31" t="n"/>
+      <c r="L12" s="31" t="n"/>
+      <c r="M12" s="31" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -6099,74 +7340,74 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>DateKey</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>FiscalYear</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="24" t="inlineStr">
         <is>
           <t>Quarter</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="G11" s="24" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="H11" s="19" t="inlineStr">
+      <c r="H11" s="24" t="inlineStr">
         <is>
           <t>MonthName</t>
         </is>
       </c>
-      <c r="I11" s="19" t="inlineStr">
+      <c r="I11" s="24" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
       </c>
-      <c r="J11" s="19" t="inlineStr">
+      <c r="J11" s="24" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="K11" s="19" t="inlineStr">
+      <c r="K11" s="24" t="inlineStr">
         <is>
           <t>DayName</t>
         </is>
       </c>
-      <c r="L11" s="19" t="inlineStr">
+      <c r="L11" s="24" t="inlineStr">
         <is>
           <t>IsWeekend</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="20" t="n"/>
-      <c r="H12" s="20" t="n"/>
-      <c r="I12" s="20" t="n"/>
-      <c r="J12" s="20" t="n"/>
-      <c r="K12" s="20" t="n"/>
-      <c r="L12" s="20" t="n"/>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="n"/>
+      <c r="I12" s="18" t="n"/>
+      <c r="J12" s="18" t="n"/>
+      <c r="K12" s="18" t="n"/>
+      <c r="L12" s="18" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -6293,62 +7534,62 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>ProductKey</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>ProductID</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="24" t="inlineStr">
         <is>
           <t>ProductType</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="G11" s="24" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="H11" s="19" t="inlineStr">
+      <c r="H11" s="24" t="inlineStr">
         <is>
           <t>Collection</t>
         </is>
       </c>
-      <c r="I11" s="19" t="inlineStr">
+      <c r="I11" s="24" t="inlineStr">
         <is>
           <t>UnitCost</t>
         </is>
       </c>
-      <c r="J11" s="19" t="inlineStr">
+      <c r="J11" s="24" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="20" t="n"/>
-      <c r="H12" s="20" t="n"/>
-      <c r="I12" s="20" t="n"/>
-      <c r="J12" s="20" t="n"/>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="n"/>
+      <c r="I12" s="18" t="n"/>
+      <c r="J12" s="18" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -6473,50 +7714,50 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>CustomerKey</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>CustomerID</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="24" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="G11" s="24" t="inlineStr">
         <is>
           <t>FirstOrderDate</t>
         </is>
       </c>
-      <c r="H11" s="19" t="inlineStr">
+      <c r="H11" s="24" t="inlineStr">
         <is>
           <t>CustomerSegment</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="20" t="n"/>
-      <c r="H12" s="20" t="n"/>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -6639,38 +7880,38 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>LocationKey</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>LocationID</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>LocationName</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="24" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -6926,7 +8167,7 @@
     <row r="17">
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>[ Sales Trend (Chart)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Sales Trend (Chart)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="C17" s="14" t="n"/>
@@ -7026,7 +8267,7 @@
     <row r="26">
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>[ Sales by Collection (Chart)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Sales by Collection (Chart)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="C26" s="14" t="n"/>
@@ -7126,7 +8367,7 @@
     <row r="35">
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>[ Top Products (Chart)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Top Products (Chart)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="C35" s="14" t="n"/>
@@ -7226,7 +8467,7 @@
     <row r="44">
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>[ Geography (Chart)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Geography (Chart)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="C44" s="14" t="n"/>
@@ -7333,7 +8574,7 @@
     <row r="55">
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>[ Executive Summary (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Executive Summary (PivotTable)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="C55" s="14" t="n"/>
@@ -7542,32 +8783,32 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>CollectionKey</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>CollectionID</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>Handle</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -7687,20 +8928,20 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>ParameterName</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>ParameterValue</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -7722,6 +8963,349 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007F7F7F"/>
+    <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DIM_Supplier</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PASSRESS MIS   |   Home ▸ DIM_Supplier</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sheet Documentation  (use the  +  outline control at left to expand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Data Model-ready mirror of 12_Suppliers (Supplier Master table).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Input tables</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>12_Suppliers's master-data table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Output tables</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Related to FACT_ tables in the Data Model (one-to-many).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Relationships</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>SupplierID relates to FACT_PurchaseOrderHeader (one-to-many).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Future data source</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Load 12_Suppliers's table into this mirror — Phase 4 (Data Model wiring).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" hidden="1" outlineLevel="1"/>
+    <row r="10" ht="6" customHeight="1"/>
+    <row r="11" ht="18" customHeight="1">
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>SupplierKey</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>SupplierID</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>SupplierName</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>SupplierType</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
+  <mergeCells count="8">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B6:G6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007F7F7F"/>
+    <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DIM_ProductCostHistory</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PASSRESS MIS   |   Home ▸ DIM_ProductCostHistory</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sheet Documentation  (use the  +  outline control at left to expand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Data Model-ready mirror of 05_Products (Product Cost Master table), time-variant (Effective From/To + Active Flag preserved) so Phase 4 can join each order line to the cost that was active on the order's date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Input tables</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>05_Products's master-data table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Output tables</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Related to FACT_ tables in the Data Model (one-to-many).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Relationships</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>SKU relates to FACT_OrderLines; EffectiveFromDate/EffectiveToDate bound which cost row applies to a given order date (Phase 4 DAX).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Future data source</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Load 05_Products's table into this mirror — Phase 4 (Data Model wiring).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" hidden="1" outlineLevel="1"/>
+    <row r="10" ht="6" customHeight="1"/>
+    <row r="11" ht="18" customHeight="1">
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>CostKey</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>TotalLandedCost</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>SellingPrice</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>ExpectedGrossMarginPct</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>EffectiveFromDate</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>EffectiveToDate</t>
+        </is>
+      </c>
+      <c r="J11" s="24" t="inlineStr">
+        <is>
+          <t>ActiveFlag</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="n"/>
+      <c r="I12" s="18" t="n"/>
+      <c r="J12" s="18" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
+  <mergeCells count="8">
+    <mergeCell ref="B7:J7"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="B8:J8"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="B6:J6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>
@@ -7832,92 +9416,92 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>OrderLineKey</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>OrderID</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>DateKey</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>ProductKey</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="24" t="inlineStr">
         <is>
           <t>CustomerKey</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="G11" s="24" t="inlineStr">
         <is>
           <t>LocationKey</t>
         </is>
       </c>
-      <c r="H11" s="19" t="inlineStr">
+      <c r="H11" s="24" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="I11" s="19" t="inlineStr">
+      <c r="I11" s="24" t="inlineStr">
         <is>
           <t>UnitPrice</t>
         </is>
       </c>
-      <c r="J11" s="19" t="inlineStr">
+      <c r="J11" s="24" t="inlineStr">
         <is>
           <t>GrossAmount</t>
         </is>
       </c>
-      <c r="K11" s="19" t="inlineStr">
+      <c r="K11" s="24" t="inlineStr">
         <is>
           <t>DiscountAmount</t>
         </is>
       </c>
-      <c r="L11" s="19" t="inlineStr">
+      <c r="L11" s="24" t="inlineStr">
         <is>
           <t>TaxAmount</t>
         </is>
       </c>
-      <c r="M11" s="19" t="inlineStr">
+      <c r="M11" s="24" t="inlineStr">
         <is>
           <t>NetAmount</t>
         </is>
       </c>
-      <c r="N11" s="19" t="inlineStr">
+      <c r="N11" s="24" t="inlineStr">
         <is>
           <t>UnitCost</t>
         </is>
       </c>
-      <c r="O11" s="19" t="inlineStr">
+      <c r="O11" s="24" t="inlineStr">
         <is>
           <t>COGS</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="20" t="n"/>
-      <c r="H12" s="20" t="n"/>
-      <c r="I12" s="20" t="n"/>
-      <c r="J12" s="20" t="n"/>
-      <c r="K12" s="20" t="n"/>
-      <c r="L12" s="20" t="n"/>
-      <c r="M12" s="20" t="n"/>
-      <c r="N12" s="20" t="n"/>
-      <c r="O12" s="20" t="n"/>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="n"/>
+      <c r="I12" s="18" t="n"/>
+      <c r="J12" s="18" t="n"/>
+      <c r="K12" s="18" t="n"/>
+      <c r="L12" s="18" t="n"/>
+      <c r="M12" s="18" t="n"/>
+      <c r="N12" s="18" t="n"/>
+      <c r="O12" s="18" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -7938,7 +9522,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>
@@ -8040,38 +9624,38 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>RefundKey</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>OrderLineKey</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>DateKey</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="24" t="inlineStr">
         <is>
           <t>RefundAmount</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -8092,7 +9676,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>
@@ -8196,50 +9780,50 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>MovementKey</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>DateKey</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>ProductKey</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>LocationKey</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="24" t="inlineStr">
         <is>
           <t>MovementType</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="G11" s="24" t="inlineStr">
         <is>
           <t>QuantityChange</t>
         </is>
       </c>
-      <c r="H11" s="19" t="inlineStr">
+      <c r="H11" s="24" t="inlineStr">
         <is>
           <t>ResultingOnHand</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="20" t="n"/>
-      <c r="H12" s="20" t="n"/>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -8260,7 +9844,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>
@@ -8364,50 +9948,50 @@
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>PaymentKey</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>OrderID</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>DateKey</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>PaymentMethod</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="24" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="G11" s="24" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="H11" s="19" t="inlineStr">
+      <c r="H11" s="24" t="inlineStr">
         <is>
           <t>PresentmentAmount</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="20" t="n"/>
-      <c r="H12" s="20" t="n"/>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -8428,14 +10012,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>
     <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -8447,6 +10031,10 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -8478,7 +10066,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Manually entered operating-expense fact, kept structurally separate from Shopify-sourced facts. Mirrors the input table on 10_Expenses — this is the Data Model-ready version of it.</t>
+          <t>Manually entered fact, kept structurally separate from Shopify-sourced facts. Mirrors the input table(s) on 10_Expenses — this is the Data Model-ready version of it.</t>
         </is>
       </c>
     </row>
@@ -8490,7 +10078,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>10_Expenses manual entry table.</t>
+          <t>10_Expenses manual entry table(s).</t>
         </is>
       </c>
     </row>
@@ -8514,7 +10102,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Grain: one row per expense entry.</t>
+          <t>Grain matches its source table on the visible sheet, one-for-one.</t>
         </is>
       </c>
     </row>
@@ -8526,75 +10114,99 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>10_Expenses (already the source of truth — no external system).</t>
+          <t>10_Expenses (already the source of truth — no external system). Loaded into this mirror in Phase 4 (Data Model wiring).</t>
         </is>
       </c>
     </row>
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>ExpenseKey</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>ExpenseDate</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>ExpenseCategory</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>ExpenseSubcategory</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>SupplierID</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>PaymentMethod</t>
+        </is>
+      </c>
+      <c r="J11" s="17" t="inlineStr">
+        <is>
+          <t>RelatedCollection</t>
+        </is>
+      </c>
+      <c r="K11" s="17" t="inlineStr">
+        <is>
+          <t>RelatedSKU</t>
+        </is>
+      </c>
+      <c r="L11" s="17" t="inlineStr">
         <is>
           <t>CostCenter</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="G11" s="15" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="H11" s="15" t="inlineStr">
-        <is>
-          <t>PaymentMethod</t>
-        </is>
-      </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>EnteredBy</t>
+      <c r="M11" s="17" t="inlineStr">
+        <is>
+          <t>InvoiceNumber</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="27" t="n"/>
-      <c r="C12" s="27" t="n"/>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="27" t="n"/>
-      <c r="F12" s="27" t="n"/>
-      <c r="G12" s="27" t="n"/>
-      <c r="H12" s="27" t="n"/>
-      <c r="I12" s="27" t="n"/>
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="32" t="n"/>
+      <c r="E12" s="32" t="n"/>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="32" t="n"/>
+      <c r="H12" s="32" t="n"/>
+      <c r="I12" s="32" t="n"/>
+      <c r="J12" s="32" t="n"/>
+      <c r="K12" s="32" t="n"/>
+      <c r="L12" s="32" t="n"/>
+      <c r="M12" s="32" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
   <mergeCells count="8">
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B6:I6"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B6:M6"/>
+    <mergeCell ref="B7:M7"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="B5:M5"/>
+    <mergeCell ref="B8:M8"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="B4:M4"/>
+    <mergeCell ref="A2:M2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -8603,14 +10215,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00C55A11"/>
+    <tabColor rgb="00595959"/>
     <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -8619,22 +10231,19 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LOG_RefreshHistory</t>
+          <t>FACT_CapitalTransactions</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PASSRESS MIS   |   Home ▸ LOG_RefreshHistory</t>
+          <t>PASSRESS MIS   |   Home ▸ FACT_CapitalTransactions</t>
         </is>
       </c>
     </row>
@@ -8653,7 +10262,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Append-only log of every workbook refresh: what ran, how many rows moved, and how long it took.</t>
+          <t>Manually entered fact, kept structurally separate from Shopify-sourced facts. Mirrors the input table(s) on 11_Capital — this is the Data Model-ready version of it.</t>
         </is>
       </c>
     </row>
@@ -8665,7 +10274,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Written by the Power Query refresh process (Phase 2).</t>
+          <t>11_Capital manual entry table(s).</t>
         </is>
       </c>
     </row>
@@ -8677,7 +10286,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Displayed on 14_Data_Quality and summarized on 01_Home.</t>
+          <t>Referenced by DAX measures across 08_Finance, 09_Profitability, 02/03 dashboards.</t>
         </is>
       </c>
     </row>
@@ -8689,7 +10298,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>No Data Model relationship — a flat audit trail, queried directly by 14_Data_Quality.</t>
+          <t>Grain matches its source table on the visible sheet, one-for-one.</t>
         </is>
       </c>
     </row>
@@ -8701,236 +10310,57 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Populated automatically on every Refresh All — Phase 2.</t>
+          <t>11_Capital (already the source of truth — no external system). Loaded into this mirror in Phase 4 (Data Model wiring).</t>
         </is>
       </c>
     </row>
     <row r="9" hidden="1" outlineLevel="1"/>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>RefreshID</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>Timestamp</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>RowsLoaded</t>
-        </is>
-      </c>
-      <c r="F11" s="19" t="inlineStr">
-        <is>
-          <t>RowsUpdated</t>
-        </is>
-      </c>
-      <c r="G11" s="19" t="inlineStr">
-        <is>
-          <t>Errors</t>
-        </is>
-      </c>
-      <c r="H11" s="19" t="inlineStr">
-        <is>
-          <t>DurationSeconds</t>
-        </is>
-      </c>
-      <c r="I11" s="19" t="inlineStr">
-        <is>
-          <t>TriggeredBy</t>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>CapitalKey</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>TransactionType</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>Amount</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="20" t="n"/>
-      <c r="H12" s="20" t="n"/>
-      <c r="I12" s="20" t="n"/>
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="32" t="n"/>
+      <c r="E12" s="32" t="n"/>
+      <c r="F12" s="32" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
   <mergeCells count="8">
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B6:I6"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B4:I4"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00C55A11"/>
-    <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>LOG_DataQuality</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>PASSRESS MIS   |   Home ▸ LOG_DataQuality</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="14" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Sheet Documentation  (use the  +  outline control at left to expand)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" hidden="1" outlineLevel="1" ht="13" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Append-only log of validation-rule results, one row per check per refresh.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" hidden="1" outlineLevel="1" ht="13" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Input tables</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Written by the Power Query refresh process (Phase 2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" hidden="1" outlineLevel="1" ht="13" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Output tables</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Displayed on 14_Data_Quality and summarized on 01_Home.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" hidden="1" outlineLevel="1" ht="13" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Relationships</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>No Data Model relationship — a flat audit trail, queried directly by 14_Data_Quality.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" hidden="1" outlineLevel="1" ht="13" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Future data source</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Populated automatically on every Refresh All — Phase 2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" hidden="1" outlineLevel="1"/>
-    <row r="10" ht="6" customHeight="1"/>
-    <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>CheckID</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>Timestamp</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>CheckName</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>TableName</t>
-        </is>
-      </c>
-      <c r="F11" s="19" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="G11" s="19" t="inlineStr">
-        <is>
-          <t>Details</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="20" t="n"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
-  <mergeCells count="8">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="A3:F3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -9118,7 +10548,7 @@
     <row r="17">
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>[ Sales Trend (Chart)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Sales Trend (Chart)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="C17" s="14" t="n"/>
@@ -9225,7 +10655,7 @@
     <row r="28">
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>[ Sales by Date (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Sales by Date (PivotTable)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="C28" s="14" t="n"/>
@@ -9234,7 +10664,7 @@
       <c r="F28" s="14" t="n"/>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>[ Sales by Product (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Sales by Product (PivotTable)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="H28" s="14" t="n"/>
@@ -9353,7 +10783,7 @@
     <row r="39">
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>[ Sales by Collection (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Sales by Collection (PivotTable)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="C39" s="14" t="n"/>
@@ -9362,7 +10792,7 @@
       <c r="F39" s="14" t="n"/>
       <c r="G39" s="13" t="inlineStr">
         <is>
-          <t>[ Order List (Table)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Order List (Table)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="H39" s="14" t="n"/>
@@ -9507,6 +10937,832 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00595959"/>
+    <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FACT_PurchaseOrderHeader</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PASSRESS MIS   |   Home ▸ FACT_PurchaseOrderHeader</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sheet Documentation  (use the  +  outline control at left to expand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Manually entered fact, kept structurally separate from Shopify-sourced facts. Mirrors the input table(s) on 12_Suppliers (PO Header table) — this is the Data Model-ready version of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Input tables</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>12_Suppliers (PO Header table) manual entry table(s).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Output tables</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Referenced by DAX measures across 08_Finance, 09_Profitability, 02/03 dashboards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Relationships</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Grain matches its source table on the visible sheet, one-for-one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Future data source</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>12_Suppliers (PO Header table) (already the source of truth — no external system). Loaded into this mirror in Phase 4 (Data Model wiring).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" hidden="1" outlineLevel="1"/>
+    <row r="10" ht="6" customHeight="1"/>
+    <row r="11" ht="18" customHeight="1">
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>PONumber</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>SupplierID</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>OrderDate</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>ExpectedDeliveryDate</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="32" t="n"/>
+      <c r="E12" s="32" t="n"/>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="32" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
+  <mergeCells count="8">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B6:G6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00595959"/>
+    <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FACT_PurchaseOrderLines</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PASSRESS MIS   |   Home ▸ FACT_PurchaseOrderLines</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sheet Documentation  (use the  +  outline control at left to expand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Manually entered fact, kept structurally separate from Shopify-sourced facts. Mirrors the input table(s) on 12_Suppliers (PO Lines table) — this is the Data Model-ready version of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Input tables</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>12_Suppliers (PO Lines table) manual entry table(s).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Output tables</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Referenced by DAX measures across 08_Finance, 09_Profitability, 02/03 dashboards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Relationships</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Grain matches its source table on the visible sheet, one-for-one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Future data source</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>12_Suppliers (PO Lines table) (already the source of truth — no external system). Loaded into this mirror in Phase 4 (Data Model wiring).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" hidden="1" outlineLevel="1"/>
+    <row r="10" ht="6" customHeight="1"/>
+    <row r="11" ht="18" customHeight="1">
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>PONumber</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>QuantityOrdered</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>UnitCost</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>TotalCost</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="32" t="n"/>
+      <c r="E12" s="32" t="n"/>
+      <c r="F12" s="32" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
+  <mergeCells count="8">
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="A3:F3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00595959"/>
+    <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FACT_GoodsReceipt</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PASSRESS MIS   |   Home ▸ FACT_GoodsReceipt</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sheet Documentation  (use the  +  outline control at left to expand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Manually entered fact, kept structurally separate from Shopify-sourced facts. Mirrors the input table(s) on 12_Suppliers (Goods Receipt table) — this is the Data Model-ready version of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Input tables</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>12_Suppliers (Goods Receipt table) manual entry table(s).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Output tables</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Referenced by DAX measures across 08_Finance, 09_Profitability, 02/03 dashboards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Relationships</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Grain matches its source table on the visible sheet, one-for-one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Future data source</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>12_Suppliers (Goods Receipt table) (already the source of truth — no external system). Loaded into this mirror in Phase 4 (Data Model wiring).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" hidden="1" outlineLevel="1"/>
+    <row r="10" ht="6" customHeight="1"/>
+    <row r="11" ht="18" customHeight="1">
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>PONumber</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>GoodsReceivedDate</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>QuantityReceived</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>RemainingQuantity</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>ActualUnitCost</t>
+        </is>
+      </c>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t>VarianceFromPO</t>
+        </is>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="32" t="n"/>
+      <c r="E12" s="32" t="n"/>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="32" t="n"/>
+      <c r="H12" s="32" t="n"/>
+      <c r="I12" s="32" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
+  <mergeCells count="8">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B4:I4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C55A11"/>
+    <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>LOG_RefreshHistory</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PASSRESS MIS   |   Home ▸ LOG_RefreshHistory</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sheet Documentation  (use the  +  outline control at left to expand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Append-only log of every workbook refresh: what ran, how many rows moved, and how long it took.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Input tables</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Written by the Power Query refresh process (Phase 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Output tables</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Displayed on 14_Data_Quality and summarized on 01_Home.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Relationships</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>No Data Model relationship — a flat audit trail, queried directly by 14_Data_Quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Future data source</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Populated automatically on every Refresh All — Phase 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" hidden="1" outlineLevel="1"/>
+    <row r="10" ht="6" customHeight="1"/>
+    <row r="11" ht="18" customHeight="1">
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>RefreshID</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>RowsLoaded</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>RowsUpdated</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>Errors</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>DurationSeconds</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>TriggeredBy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="n"/>
+      <c r="I12" s="18" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
+  <mergeCells count="8">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B4:I4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C55A11"/>
+    <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>LOG_DataQuality</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PASSRESS MIS   |   Home ▸ LOG_DataQuality</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sheet Documentation  (use the  +  outline control at left to expand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Append-only log of validation-rule results, one row per check per refresh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Input tables</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Written by the Power Query refresh process (Phase 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Output tables</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Displayed on 14_Data_Quality and summarized on 01_Home.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Relationships</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>No Data Model relationship — a flat audit trail, queried directly by 14_Data_Quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" hidden="1" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Future data source</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Populated automatically on every Refresh All — Phase 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" hidden="1" outlineLevel="1"/>
+    <row r="10" ht="6" customHeight="1"/>
+    <row r="11" ht="18" customHeight="1">
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>CheckID</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>CheckName</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>TableName</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
+  <mergeCells count="8">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B6:G6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -9514,7 +11770,7 @@
     <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:S45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -9560,7 +11816,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Product-level performance — best sellers, margin by SKU, and variant performance.</t>
+          <t>Product-level performance dashboard placeholders (Phase 4) PLUS, as of Phase 3, the Product Cost Master — the workbook's historical/versioned SKU costing table.</t>
         </is>
       </c>
     </row>
@@ -9572,7 +11828,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>DIM_Product, FACT_OrderLines.</t>
+          <t>DIM_Product, FACT_OrderLines (Phase 4 dashboard). RAW_Variants, RAW_Collections (Phase 3 Product Cost Master dropdowns).</t>
         </is>
       </c>
     </row>
@@ -9584,7 +11840,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Product KPI row, Top Products table, Product Margin table, Variant Detail table.</t>
+          <t>Product KPI row, Top Products table, Product Margin table, Variant Detail table (Phase 4). tbl_ProductCostMaster feeding DIM_ProductCostHistory (Phase 3, live now).</t>
         </is>
       </c>
     </row>
@@ -9596,7 +11852,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>DIM_Product links to FACT_OrderLines on ProductKey.</t>
+          <t>DIM_Product links to FACT_OrderLines on ProductKey (Phase 4). tbl_ProductCostMaster[SKU] links to RAW_Variants[SKU]; Phase 4's COGS calculation will further match SKU + order date against Effective From/To Date.</t>
         </is>
       </c>
     </row>
@@ -9608,7 +11864,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>RAW_Products / RAW_Variants via Power Query — Phase 2.</t>
+          <t>RAW_Products / RAW_Variants via Power Query — Phase 2 (dashboard). Product Cost Master is manual entry today — see PHASE3_DOCUMENTATION.md §1.</t>
         </is>
       </c>
     </row>
@@ -9686,7 +11942,7 @@
     <row r="17">
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>[ Top 10 Products (Chart)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Top 10 Products (Chart)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="C17" s="14" t="n"/>
@@ -9793,7 +12049,7 @@
     <row r="28">
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>[ Product Margin (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Product Margin (PivotTable)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="C28" s="14" t="n"/>
@@ -9802,7 +12058,7 @@
       <c r="F28" s="14" t="n"/>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>[ Variant Detail (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Variant Detail (PivotTable)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="H28" s="14" t="n"/>
@@ -9917,6 +12173,174 @@
       <c r="I37" s="14" t="n"/>
       <c r="J37" s="14" t="n"/>
       <c r="K37" s="14" t="n"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>PRODUCT COST MASTER  (Phase 3 — green cells = type here; Cost ID, Total Landed Cost, Expected Gross Margin %, and the overlap warning are automatic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>Historical costing: never edit or delete a past row when a cost changes — add a NEW row for the new cost with its own Effective From Date, and set the OLD row's Effective To Date to the day before and its Active Flag to Inactive. Phase 4's COGS calculation will match each order line to the cost row whose SKU matches and whose Effective From/To range contains the order's date — so past orders keep using the cost that was actually active when they happened, even after costs change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>Cost ID</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="inlineStr">
+        <is>
+          <t>Product Name</t>
+        </is>
+      </c>
+      <c r="E44" s="17" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+      <c r="F44" s="17" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="G44" s="17" t="inlineStr">
+        <is>
+          <t>Fabric Cost</t>
+        </is>
+      </c>
+      <c r="H44" s="17" t="inlineStr">
+        <is>
+          <t>Accessories Cost</t>
+        </is>
+      </c>
+      <c r="I44" s="17" t="inlineStr">
+        <is>
+          <t>Manufacturing Cost</t>
+        </is>
+      </c>
+      <c r="J44" s="17" t="inlineStr">
+        <is>
+          <t>Packaging Cost</t>
+        </is>
+      </c>
+      <c r="K44" s="17" t="inlineStr">
+        <is>
+          <t>Shipping Cost</t>
+        </is>
+      </c>
+      <c r="L44" s="17" t="inlineStr">
+        <is>
+          <t>Other Cost</t>
+        </is>
+      </c>
+      <c r="M44" s="17" t="inlineStr">
+        <is>
+          <t>Total Landed Cost</t>
+        </is>
+      </c>
+      <c r="N44" s="17" t="inlineStr">
+        <is>
+          <t>Selling Price</t>
+        </is>
+      </c>
+      <c r="O44" s="17" t="inlineStr">
+        <is>
+          <t>Expected Gross Margin %</t>
+        </is>
+      </c>
+      <c r="P44" s="17" t="inlineStr">
+        <is>
+          <t>Effective From Date</t>
+        </is>
+      </c>
+      <c r="Q44" s="17" t="inlineStr">
+        <is>
+          <t>Effective To Date</t>
+        </is>
+      </c>
+      <c r="R44" s="17" t="inlineStr">
+        <is>
+          <t>Active Flag</t>
+        </is>
+      </c>
+      <c r="S44" s="17" t="inlineStr">
+        <is>
+          <t>Overlap Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="18">
+        <f>"COST-"&amp;TEXT(ROW()-44,"00000")</f>
+        <v/>
+      </c>
+      <c r="C45" s="19" t="n"/>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>EXAMPLE — Amara Wrap Dress</t>
+        </is>
+      </c>
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t>Black / M</t>
+        </is>
+      </c>
+      <c r="F45" s="19" t="n"/>
+      <c r="G45" s="19" t="n">
+        <v>180</v>
+      </c>
+      <c r="H45" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="I45" s="19" t="n">
+        <v>90</v>
+      </c>
+      <c r="J45" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="K45" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="L45" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="20">
+        <f>SUM([@[Fabric Cost]],[@[Accessories Cost]],[@[Manufacturing Cost]],[@[Packaging Cost]],[@[Shipping Cost]],[@[Other Cost]])</f>
+        <v/>
+      </c>
+      <c r="N45" s="19" t="n">
+        <v>650</v>
+      </c>
+      <c r="O45" s="21">
+        <f>IF([@[Selling Price]]=0,"",([@[Selling Price]]-[@[Total Landed Cost]])/[@[Selling Price]])</f>
+        <v/>
+      </c>
+      <c r="P45" s="19" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="Q45" s="19" t="n"/>
+      <c r="R45" s="19" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="S45" s="18">
+        <f>IF(COUNTIFS(tbl_ProductCostMaster[SKU],[@SKU],tbl_ProductCostMaster[Active Flag],"Active")&gt;1,"Multiple Active cost rows for this SKU — deactivate all but the current one","")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
@@ -9941,7 +12365,21 @@
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="B5:L5"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="C45:C501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the SKU list — free text isn't accepted here." promptTitle="SKU" prompt="Choose a live Shopify SKU." type="list" errorStyle="stop">
+      <formula1>=SKUList</formula1>
+    </dataValidation>
+    <dataValidation sqref="F45:F501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the Collection list — free text isn't accepted here." promptTitle="Collection" prompt="Choose a live Shopify collection." type="list" errorStyle="stop">
+      <formula1>=CollectionTitleList</formula1>
+    </dataValidation>
+    <dataValidation sqref="R45:R501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Choose Active or Inactive." promptTitle="Active Flag" prompt="Only ONE row per SKU should be Active at a time — see the historical-costing note above." type="list" errorStyle="stop">
+      <formula1>"Active,Inactive"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -10124,7 +12562,7 @@
     <row r="17">
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>[ Cohort Trend (Chart)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Cohort Trend (Chart)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="C17" s="14" t="n"/>
@@ -10231,7 +12669,7 @@
     <row r="28">
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>[ Cohort Table (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Cohort Table (PivotTable)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="C28" s="14" t="n"/>
@@ -10240,7 +12678,7 @@
       <c r="F28" s="14" t="n"/>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>[ Top Customers (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Top Customers (PivotTable)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="H28" s="14" t="n"/>
@@ -10359,7 +12797,7 @@
     <row r="39">
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>[ Geography (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Geography (PivotTable)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="C39" s="14" t="n"/>
@@ -10637,7 +13075,7 @@
     <row r="17">
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>[ Stock Trend (Chart)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Stock Trend (Chart)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="C17" s="14" t="n"/>
@@ -10744,7 +13182,7 @@
     <row r="28">
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>[ Stock by Location (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Stock by Location (PivotTable)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="C28" s="14" t="n"/>
@@ -10753,7 +13191,7 @@
       <c r="F28" s="14" t="n"/>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>[ Low Stock List (Table)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Low Stock List (Table)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="H28" s="14" t="n"/>
@@ -10872,7 +13310,7 @@
     <row r="39">
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>[ Inventory Valuation (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Inventory Valuation (PivotTable)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="C39" s="14" t="n"/>
@@ -11150,7 +13588,7 @@
     <row r="17">
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>[ P&amp;L Trend (Chart)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ P&amp;L Trend (Chart)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="C17" s="14" t="n"/>
@@ -11257,7 +13695,7 @@
     <row r="28">
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>[ P&amp;L Statement (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ P&amp;L Statement (PivotTable)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="C28" s="14" t="n"/>
@@ -11266,7 +13704,7 @@
       <c r="F28" s="14" t="n"/>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>[ Cash Flow Statement (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Cash Flow Statement (PivotTable)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="H28" s="14" t="n"/>
@@ -11588,7 +14026,7 @@
     <row r="17">
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>[ Margin Trend (Chart)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Margin Trend (Chart)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="C17" s="14" t="n"/>
@@ -11695,7 +14133,7 @@
     <row r="28">
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>[ Margin by Product (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Margin by Product (PivotTable)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="C28" s="14" t="n"/>
@@ -11704,7 +14142,7 @@
       <c r="F28" s="14" t="n"/>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>[ Margin by Collection (PivotTable)  —  Placeholder, built in Phase 3 ]</t>
+          <t>[ Margin by Collection (PivotTable)  —  Placeholder, built in Phase 4 ]</t>
         </is>
       </c>
       <c r="H28" s="14" t="n"/>

--- a/passress-mis/PASSRESS_MIS.xlsx
+++ b/passress-mis/PASSRESS_MIS.xlsx
@@ -501,8 +501,8 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="tbl_VersionLog" displayName="tbl_VersionLog" ref="B36:E40" headerRowCount="1">
-  <autoFilter ref="B36:E40"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="tbl_VersionLog" displayName="tbl_VersionLog" ref="B36:E41" headerRowCount="1">
+  <autoFilter ref="B36:E41"/>
   <tableColumns count="4">
     <tableColumn id="2" name="Version"/>
     <tableColumn id="3" name="Date"/>
@@ -514,8 +514,8 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="tbl_LookupExpenseCategory" displayName="tbl_LookupExpenseCategory" ref="B44:B54" headerRowCount="1">
-  <autoFilter ref="B44:B54"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="tbl_LookupExpenseCategory" displayName="tbl_LookupExpenseCategory" ref="B45:B55" headerRowCount="1">
+  <autoFilter ref="B45:B55"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Expense Category"/>
   </tableColumns>
@@ -524,8 +524,8 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tbl_LookupExpenseSubcategory" displayName="tbl_LookupExpenseSubcategory" ref="B56:B68" headerRowCount="1">
-  <autoFilter ref="B56:B68"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tbl_LookupExpenseSubcategory" displayName="tbl_LookupExpenseSubcategory" ref="B57:B69" headerRowCount="1">
+  <autoFilter ref="B57:B69"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Expense Subcategory"/>
   </tableColumns>
@@ -534,8 +534,8 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="tbl_LookupCostCenter" displayName="tbl_LookupCostCenter" ref="B70:B75" headerRowCount="1">
-  <autoFilter ref="B70:B75"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="tbl_LookupCostCenter" displayName="tbl_LookupCostCenter" ref="B71:B76" headerRowCount="1">
+  <autoFilter ref="B71:B76"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Cost Center"/>
   </tableColumns>
@@ -544,8 +544,8 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="tbl_LookupPaymentMethod" displayName="tbl_LookupPaymentMethod" ref="B77:B83" headerRowCount="1">
-  <autoFilter ref="B77:B83"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="tbl_LookupPaymentMethod" displayName="tbl_LookupPaymentMethod" ref="B78:B84" headerRowCount="1">
+  <autoFilter ref="B78:B84"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Payment Method"/>
   </tableColumns>
@@ -554,8 +554,8 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="tbl_LookupCurrency" displayName="tbl_LookupCurrency" ref="B85:B89" headerRowCount="1">
-  <autoFilter ref="B85:B89"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="tbl_LookupCurrency" displayName="tbl_LookupCurrency" ref="B86:B90" headerRowCount="1">
+  <autoFilter ref="B86:B90"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Currency"/>
   </tableColumns>
@@ -564,8 +564,8 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="tbl_LookupSupplierType" displayName="tbl_LookupSupplierType" ref="B91:B99" headerRowCount="1">
-  <autoFilter ref="B91:B99"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="tbl_LookupSupplierType" displayName="tbl_LookupSupplierType" ref="B92:B100" headerRowCount="1">
+  <autoFilter ref="B92:B100"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Supplier Type"/>
   </tableColumns>
@@ -574,8 +574,8 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="tbl_LookupSupplierStatus" displayName="tbl_LookupSupplierStatus" ref="B101:B104" headerRowCount="1">
-  <autoFilter ref="B101:B104"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="tbl_LookupSupplierStatus" displayName="tbl_LookupSupplierStatus" ref="B102:B105" headerRowCount="1">
+  <autoFilter ref="B102:B105"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Supplier Status"/>
   </tableColumns>
@@ -584,8 +584,8 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tbl_LookupCapitalTransactionType" displayName="tbl_LookupCapitalTransactionType" ref="B106:B108" headerRowCount="1">
-  <autoFilter ref="B106:B108"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tbl_LookupCapitalTransactionType" displayName="tbl_LookupCapitalTransactionType" ref="B107:B109" headerRowCount="1">
+  <autoFilter ref="B107:B109"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Capital Transaction Type"/>
   </tableColumns>
@@ -620,8 +620,8 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="tbl_LookupPOStatus" displayName="tbl_LookupPOStatus" ref="B110:B117" headerRowCount="1">
-  <autoFilter ref="B110:B117"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="tbl_LookupPOStatus" displayName="tbl_LookupPOStatus" ref="B111:B118" headerRowCount="1">
+  <autoFilter ref="B111:B118"/>
   <tableColumns count="1">
     <tableColumn id="2" name="PO Status"/>
   </tableColumns>
@@ -630,8 +630,8 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="tbl_LookupWarehouse" displayName="tbl_LookupWarehouse" ref="B119:B122" headerRowCount="1">
-  <autoFilter ref="B119:B122"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="tbl_LookupWarehouse" displayName="tbl_LookupWarehouse" ref="B120:B123" headerRowCount="1">
+  <autoFilter ref="B120:B123"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Warehouse"/>
   </tableColumns>
@@ -640,8 +640,8 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="tbl_LookupOwner" displayName="tbl_LookupOwner" ref="B124:B125" headerRowCount="1">
-  <autoFilter ref="B124:B125"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="tbl_LookupOwner" displayName="tbl_LookupOwner" ref="B125:B126" headerRowCount="1">
+  <autoFilter ref="B125:B126"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Owner"/>
   </tableColumns>
@@ -991,9 +991,9 @@
 </file>
 
 <file path=xl/tables/table41.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="41" name="tbl_FACT_OrderLines" displayName="tbl_FACT_OrderLines" ref="B11:O12" headerRowCount="1">
-  <autoFilter ref="B11:O12"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="41" name="tbl_FACT_OrderLines" displayName="tbl_FACT_OrderLines" ref="B11:P12" headerRowCount="1">
+  <autoFilter ref="B11:P12"/>
+  <tableColumns count="15">
     <tableColumn id="2" name="OrderLineKey"/>
     <tableColumn id="3" name="OrderID"/>
     <tableColumn id="4" name="DateKey"/>
@@ -1008,6 +1008,7 @@
     <tableColumn id="13" name="NetAmount"/>
     <tableColumn id="14" name="UnitCost"/>
     <tableColumn id="15" name="COGS"/>
+    <tableColumn id="16" name="MissingCostFlag"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1060,50 +1061,53 @@
 </file>
 
 <file path=xl/tables/table45.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="45" name="tbl_FACT_ManualExpenses" displayName="tbl_FACT_ManualExpenses" ref="B11:M12" headerRowCount="1">
-  <autoFilter ref="B11:M12"/>
-  <tableColumns count="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="45" name="tbl_FACT_ManualExpenses" displayName="tbl_FACT_ManualExpenses" ref="B11:N12" headerRowCount="1">
+  <autoFilter ref="B11:N12"/>
+  <tableColumns count="13">
     <tableColumn id="2" name="ExpenseKey"/>
-    <tableColumn id="3" name="ExpenseDate"/>
-    <tableColumn id="4" name="ExpenseCategory"/>
-    <tableColumn id="5" name="ExpenseSubcategory"/>
-    <tableColumn id="6" name="SupplierID"/>
-    <tableColumn id="7" name="Amount"/>
-    <tableColumn id="8" name="Currency"/>
-    <tableColumn id="9" name="PaymentMethod"/>
-    <tableColumn id="10" name="RelatedCollection"/>
-    <tableColumn id="11" name="RelatedSKU"/>
-    <tableColumn id="12" name="CostCenter"/>
-    <tableColumn id="13" name="InvoiceNumber"/>
+    <tableColumn id="3" name="DateKey"/>
+    <tableColumn id="4" name="ExpenseDate"/>
+    <tableColumn id="5" name="ExpenseCategory"/>
+    <tableColumn id="6" name="ExpenseSubcategory"/>
+    <tableColumn id="7" name="SupplierID"/>
+    <tableColumn id="8" name="Amount"/>
+    <tableColumn id="9" name="Currency"/>
+    <tableColumn id="10" name="PaymentMethod"/>
+    <tableColumn id="11" name="RelatedCollection"/>
+    <tableColumn id="12" name="RelatedSKU"/>
+    <tableColumn id="13" name="CostCenter"/>
+    <tableColumn id="14" name="InvoiceNumber"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table46.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="46" name="tbl_FACT_CapitalTransactions" displayName="tbl_FACT_CapitalTransactions" ref="B11:F12" headerRowCount="1">
-  <autoFilter ref="B11:F12"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="46" name="tbl_FACT_CapitalTransactions" displayName="tbl_FACT_CapitalTransactions" ref="B11:G12" headerRowCount="1">
+  <autoFilter ref="B11:G12"/>
+  <tableColumns count="6">
     <tableColumn id="2" name="CapitalKey"/>
-    <tableColumn id="3" name="Date"/>
-    <tableColumn id="4" name="Owner"/>
-    <tableColumn id="5" name="TransactionType"/>
-    <tableColumn id="6" name="Amount"/>
+    <tableColumn id="3" name="DateKey"/>
+    <tableColumn id="4" name="Date"/>
+    <tableColumn id="5" name="Owner"/>
+    <tableColumn id="6" name="TransactionType"/>
+    <tableColumn id="7" name="Amount"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table47.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="47" name="tbl_FACT_PurchaseOrderHeader" displayName="tbl_FACT_PurchaseOrderHeader" ref="B11:G12" headerRowCount="1">
-  <autoFilter ref="B11:G12"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="47" name="tbl_FACT_PurchaseOrderHeader" displayName="tbl_FACT_PurchaseOrderHeader" ref="B11:H12" headerRowCount="1">
+  <autoFilter ref="B11:H12"/>
+  <tableColumns count="7">
     <tableColumn id="2" name="PONumber"/>
-    <tableColumn id="3" name="SupplierID"/>
-    <tableColumn id="4" name="OrderDate"/>
-    <tableColumn id="5" name="ExpectedDeliveryDate"/>
-    <tableColumn id="6" name="Status"/>
-    <tableColumn id="7" name="Currency"/>
+    <tableColumn id="3" name="DateKey"/>
+    <tableColumn id="4" name="SupplierID"/>
+    <tableColumn id="5" name="OrderDate"/>
+    <tableColumn id="6" name="ExpectedDeliveryDate"/>
+    <tableColumn id="7" name="Status"/>
+    <tableColumn id="8" name="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1124,17 +1128,18 @@
 </file>
 
 <file path=xl/tables/table49.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="49" name="tbl_FACT_GoodsReceipt" displayName="tbl_FACT_GoodsReceipt" ref="B11:I12" headerRowCount="1">
-  <autoFilter ref="B11:I12"/>
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="49" name="tbl_FACT_GoodsReceipt" displayName="tbl_FACT_GoodsReceipt" ref="B11:J12" headerRowCount="1">
+  <autoFilter ref="B11:J12"/>
+  <tableColumns count="9">
     <tableColumn id="2" name="PONumber"/>
-    <tableColumn id="3" name="SKU"/>
-    <tableColumn id="4" name="GoodsReceivedDate"/>
-    <tableColumn id="5" name="QuantityReceived"/>
-    <tableColumn id="6" name="RemainingQuantity"/>
-    <tableColumn id="7" name="ActualUnitCost"/>
-    <tableColumn id="8" name="VarianceFromPO"/>
-    <tableColumn id="9" name="Warehouse"/>
+    <tableColumn id="3" name="DateKey"/>
+    <tableColumn id="4" name="SKU"/>
+    <tableColumn id="5" name="GoodsReceivedDate"/>
+    <tableColumn id="6" name="QuantityReceived"/>
+    <tableColumn id="7" name="RemainingQuantity"/>
+    <tableColumn id="8" name="ActualUnitCost"/>
+    <tableColumn id="9" name="VarianceFromPO"/>
+    <tableColumn id="10" name="Warehouse"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -3849,7 +3854,7 @@
     <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4354,512 +4359,534 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="10" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="18" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D41" s="18" t="inlineStr">
+        <is>
+          <t>Phase 4 — Financial Calculation Engine (Data Model + DAX)</t>
+        </is>
+      </c>
+      <c r="E41" s="18" t="inlineStr">
+        <is>
+          <t>Completed the RAW_/manual-table -&gt; star-schema transformation layer Phase 1 sketched but Phase 2-3 left empty (power-query/star-schema/, 18 M files): DIM_Date (generated calendar, fiscal-year aware), DIM_Product/Customer/Location/Collection/Supplier/ProductCostHistory, and every FACT_ table, including historically-correct COGS resolved per order line via fn_GetEffectiveCost (SKU + order date -&gt; the Product Cost Master row active on that date, never today's cost). Full DAX measure library (dax/MEASURES.md): P&amp;L, Balance Sheet, Cash Flow, Product Profitability, Customer Metrics (incl. cohorts), Inventory Metrics, Executive KPIs, and a full time-intelligence layer (MTD/QTD/YTD/previous period/SPLY/rolling 30-90-365) applied to the headline measures with the reusable pattern documented for extending to any other. Built as composable base measures referenced by name from composite ones — no duplicated calculations. Reconciliation section validates Balance Sheet (Assets=Liabilities+Equity), Cash Position (direct vs. indirect), Net Sales (FACT vs. RAW Shopify totals), and refund/cost-coverage integrity. Accounts Payable is a documented proxy (no payment-status field exists yet — flagged, not silently assumed). See /passress-mis/dax/README.md and MEASURES.md. Still no dashboards, PivotTables, PivotCharts, or KPI cards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>MASTER DATA LOOKUP TABLES  (orange cells = configurable — edit freely, every dropdown in the workbook reads from here)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="B44" s="25" t="inlineStr">
+    <row r="45" ht="16" customHeight="1">
+      <c r="B45" s="25" t="inlineStr">
         <is>
           <t>Expense Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="29" t="inlineStr">
-        <is>
-          <t>Rent</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="29" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Rent</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="29" t="inlineStr">
         <is>
-          <t>Salaries</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="29" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Salaries</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="29" t="inlineStr">
         <is>
-          <t>Shipping &amp; Logistics</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="29" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>Shipping &amp; Logistics</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="29" t="inlineStr">
         <is>
-          <t>Software &amp; Subscriptions</t>
+          <t>Packaging</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="29" t="inlineStr">
         <is>
-          <t>Professional Fees</t>
+          <t>Software &amp; Subscriptions</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="29" t="inlineStr">
         <is>
-          <t>Bank Charges</t>
+          <t>Professional Fees</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="29" t="inlineStr">
         <is>
+          <t>Bank Charges</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="29" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="B56" s="25" t="inlineStr">
+    <row r="57" ht="16" customHeight="1">
+      <c r="B57" s="25" t="inlineStr">
         <is>
           <t>Expense Subcategory</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="29" t="inlineStr">
-        <is>
-          <t>General</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="29" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>General</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="29" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="29" t="inlineStr">
         <is>
-          <t>Online Ads</t>
+          <t>Warehouse</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="29" t="inlineStr">
         <is>
-          <t>Influencer</t>
+          <t>Online Ads</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="29" t="inlineStr">
         <is>
-          <t>Photography</t>
+          <t>Influencer</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="29" t="inlineStr">
         <is>
-          <t>Courier</t>
+          <t>Photography</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="29" t="inlineStr">
         <is>
-          <t>Customs &amp; Duties</t>
+          <t>Courier</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="29" t="inlineStr">
         <is>
-          <t>Software License</t>
+          <t>Customs &amp; Duties</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="29" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Software License</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="29" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Legal</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="29" t="inlineStr">
         <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="29" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="B70" s="25" t="inlineStr">
+    <row r="71" ht="16" customHeight="1">
+      <c r="B71" s="25" t="inlineStr">
         <is>
           <t>Cost Center</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="29" t="inlineStr">
-        <is>
-          <t>Head Office</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="29" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Head Office</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="29" t="inlineStr">
         <is>
-          <t>E-Commerce</t>
+          <t>Warehouse</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="29" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>E-Commerce</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" s="29" t="inlineStr">
         <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="29" t="inlineStr">
+        <is>
           <t>Production</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="B77" s="25" t="inlineStr">
+    <row r="78" ht="16" customHeight="1">
+      <c r="B78" s="25" t="inlineStr">
         <is>
           <t>Payment Method</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="29" t="inlineStr">
-        <is>
-          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="29" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="29" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="29" t="inlineStr">
         <is>
-          <t>Instapay</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="29" t="inlineStr">
         <is>
-          <t>Cheque</t>
+          <t>Instapay</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="29" t="inlineStr">
         <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="29" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="16" customHeight="1">
-      <c r="B85" s="25" t="inlineStr">
+    <row r="86" ht="16" customHeight="1">
+      <c r="B86" s="25" t="inlineStr">
         <is>
           <t>Currency</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="29" t="inlineStr">
-        <is>
-          <t>EGP</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="29" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EGP</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="29" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="29" t="inlineStr">
         <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="29" t="inlineStr">
+        <is>
           <t>GBP</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="16" customHeight="1">
-      <c r="B91" s="25" t="inlineStr">
+    <row r="92" ht="16" customHeight="1">
+      <c r="B92" s="25" t="inlineStr">
         <is>
           <t>Supplier Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" s="29" t="inlineStr">
-        <is>
-          <t>Fabric</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" s="29" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Fabric</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="29" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Accessories</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" s="29" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>Manufacturing</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" s="29" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Packaging</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" s="29" t="inlineStr">
         <is>
-          <t>Marketing Agency</t>
+          <t>Logistics</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="29" t="inlineStr">
         <is>
-          <t>Software Vendor</t>
+          <t>Marketing Agency</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" s="29" t="inlineStr">
         <is>
+          <t>Software Vendor</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="29" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="16" customHeight="1">
-      <c r="B101" s="25" t="inlineStr">
+    <row r="102" ht="16" customHeight="1">
+      <c r="B102" s="25" t="inlineStr">
         <is>
           <t>Supplier Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="B102" s="29" t="inlineStr">
-        <is>
-          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="B103" s="29" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="B104" s="29" t="inlineStr">
         <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="29" t="inlineStr">
+        <is>
           <t>On Hold</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="16" customHeight="1">
-      <c r="B106" s="25" t="inlineStr">
+    <row r="107" ht="16" customHeight="1">
+      <c r="B107" s="25" t="inlineStr">
         <is>
           <t>Capital Transaction Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="B107" s="29" t="inlineStr">
-        <is>
-          <t>Capital Contribution</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="B108" s="29" t="inlineStr">
         <is>
+          <t>Capital Contribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="29" t="inlineStr">
+        <is>
           <t>Capital Withdrawal</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="16" customHeight="1">
-      <c r="B110" s="25" t="inlineStr">
+    <row r="111" ht="16" customHeight="1">
+      <c r="B111" s="25" t="inlineStr">
         <is>
           <t>PO Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="B111" s="29" t="inlineStr">
-        <is>
-          <t>Draft</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="B112" s="29" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Draft</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="B113" s="29" t="inlineStr">
         <is>
-          <t>Sent</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="B114" s="29" t="inlineStr">
         <is>
-          <t>Partially Received</t>
+          <t>Sent</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="B115" s="29" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Partially Received</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="B116" s="29" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Received</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="B117" s="29" t="inlineStr">
         <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="29" t="inlineStr">
+        <is>
           <t>Cancelled</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="16" customHeight="1">
-      <c r="B119" s="25" t="inlineStr">
+    <row r="120" ht="16" customHeight="1">
+      <c r="B120" s="25" t="inlineStr">
         <is>
           <t>Warehouse</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="B120" s="29" t="inlineStr">
-        <is>
-          <t>Main Warehouse</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="B121" s="29" t="inlineStr">
         <is>
-          <t>Retail Store</t>
+          <t>Main Warehouse</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="B122" s="29" t="inlineStr">
         <is>
+          <t>Retail Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" s="29" t="inlineStr">
+        <is>
           <t>Third-Party Logistics</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="16" customHeight="1">
-      <c r="B124" s="25" t="inlineStr">
+    <row r="125" ht="16" customHeight="1">
+      <c r="B125" s="25" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="B125" s="29" t="inlineStr">
+    <row r="126">
+      <c r="B126" s="29" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
@@ -7297,7 +7324,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Derived from the matching RAW_ staging table(s).</t>
+          <t>RAW_ staging table(s) built in Phase 2.</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7348,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>One-to-many into the relevant FACT_ table(s) on this dimension's key column.</t>
+          <t>One-to-many into the relevant FACT_ table(s) on this dimension's key column — see dax/README.md for the full relationship list.</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7360,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Built from RAW_ staging data in Power Query — Phase 2/3.</t>
+          <t>Live now: paste passress-mis/power-query/star-schema/DIM_Date.pq — see passress-mis/dax/README.md for setup order.</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7518,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Derived from the matching RAW_ staging table(s).</t>
+          <t>RAW_ staging table(s) built in Phase 2.</t>
         </is>
       </c>
     </row>
@@ -7515,7 +7542,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>One-to-many into the relevant FACT_ table(s) on this dimension's key column.</t>
+          <t>One-to-many into the relevant FACT_ table(s) on this dimension's key column — see dax/README.md for the full relationship list.</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7554,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Built from RAW_ staging data in Power Query — Phase 2/3.</t>
+          <t>Live now: paste passress-mis/power-query/star-schema/DIM_Product.pq — see passress-mis/dax/README.md for setup order.</t>
         </is>
       </c>
     </row>
@@ -7671,7 +7698,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Derived from the matching RAW_ staging table(s).</t>
+          <t>RAW_ staging table(s) built in Phase 2.</t>
         </is>
       </c>
     </row>
@@ -7695,7 +7722,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>One-to-many into the relevant FACT_ table(s) on this dimension's key column.</t>
+          <t>One-to-many into the relevant FACT_ table(s) on this dimension's key column — see dax/README.md for the full relationship list.</t>
         </is>
       </c>
     </row>
@@ -7707,7 +7734,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Built from RAW_ staging data in Power Query — Phase 2/3.</t>
+          <t>Live now: paste passress-mis/power-query/star-schema/DIM_Customer.pq — see passress-mis/dax/README.md for setup order.</t>
         </is>
       </c>
     </row>
@@ -7837,7 +7864,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Derived from the matching RAW_ staging table(s).</t>
+          <t>RAW_ staging table(s) built in Phase 2.</t>
         </is>
       </c>
     </row>
@@ -7861,7 +7888,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>One-to-many into the relevant FACT_ table(s) on this dimension's key column.</t>
+          <t>One-to-many into the relevant FACT_ table(s) on this dimension's key column — see dax/README.md for the full relationship list.</t>
         </is>
       </c>
     </row>
@@ -7873,7 +7900,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Built from RAW_ staging data in Power Query — Phase 2/3.</t>
+          <t>Live now: paste passress-mis/power-query/star-schema/DIM_Location.pq — see passress-mis/dax/README.md for setup order.</t>
         </is>
       </c>
     </row>
@@ -8740,7 +8767,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Derived from the matching RAW_ staging table(s).</t>
+          <t>RAW_ staging table(s) built in Phase 2.</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8791,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>One-to-many into the relevant FACT_ table(s) on this dimension's key column.</t>
+          <t>One-to-many into the relevant FACT_ table(s) on this dimension's key column — see dax/README.md for the full relationship list.</t>
         </is>
       </c>
     </row>
@@ -8776,7 +8803,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Built from RAW_ staging data in Power Query — Phase 2/3.</t>
+          <t>Live now: paste passress-mis/power-query/star-schema/DIM_Collection.pq — see passress-mis/dax/README.md for setup order.</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9073,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>SupplierID relates to FACT_PurchaseOrderHeader (one-to-many).</t>
+          <t>SupplierID relates to FACT_ManualExpenses/FACT_PurchaseOrderHeader; PrimarySupplierID on DIM_Product relates back here (one-to-many).</t>
         </is>
       </c>
     </row>
@@ -9058,7 +9085,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Load 12_Suppliers's table into this mirror — Phase 4 (Data Model wiring).</t>
+          <t>Live now: paste passress-mis/power-query/star-schema/DIM_Supplier.pq — see passress-mis/dax/README.md for setup order.</t>
         </is>
       </c>
     </row>
@@ -9210,7 +9237,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>SKU relates to FACT_OrderLines; EffectiveFromDate/EffectiveToDate bound which cost row applies to a given order date (Phase 4 DAX).</t>
+          <t>SKU relates to FACT_OrderLines; EffectiveFromDate/EffectiveToDate bound which cost row applies to a given order date via fn_GetEffectiveCost (Power Query), not a Data Model relationship — see dax/README.md.</t>
         </is>
       </c>
     </row>
@@ -9222,7 +9249,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Load 05_Products's table into this mirror — Phase 4 (Data Model wiring).</t>
+          <t>Live now: paste passress-mis/power-query/star-schema/DIM_ProductCostHistory.pq — see passress-mis/dax/README.md for setup order.</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9339,7 @@
     <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -9330,6 +9357,7 @@
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -9361,7 +9389,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Fact table for the star schema — transaction-level grain, built from RAW_ staging data plus dimension keys.</t>
+          <t>Fact table for the star schema — transaction-level grain, built from RAW_ staging data plus dimension keys via Power Query (not re-fetched from Shopify).</t>
         </is>
       </c>
     </row>
@@ -9385,7 +9413,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Referenced by DAX measures across all dashboards.</t>
+          <t>Referenced by DAX measures — see passress-mis/dax/MEASURES.md.</t>
         </is>
       </c>
     </row>
@@ -9397,7 +9425,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Many-to-one into each related DIM_ table.</t>
+          <t>Many-to-one into each related DIM_ table — see dax/README.md for the full relationship list.</t>
         </is>
       </c>
     </row>
@@ -9409,7 +9437,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Built in Power Query from RAW_ + DIM_ — Phase 2/3.</t>
+          <t>Live now: paste passress-mis/power-query/star-schema/FACT_OrderLines.pq — see passress-mis/dax/README.md for setup order.</t>
         </is>
       </c>
     </row>
@@ -9484,6 +9512,11 @@
       <c r="O11" s="24" t="inlineStr">
         <is>
           <t>COGS</t>
+        </is>
+      </c>
+      <c r="P11" s="24" t="inlineStr">
+        <is>
+          <t>MissingCostFlag</t>
         </is>
       </c>
     </row>
@@ -9502,18 +9535,19 @@
       <c r="M12" s="18" t="n"/>
       <c r="N12" s="18" t="n"/>
       <c r="O12" s="18" t="n"/>
+      <c r="P12" s="18" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
   <mergeCells count="8">
-    <mergeCell ref="B8:O8"/>
-    <mergeCell ref="B4:O4"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="B6:O6"/>
-    <mergeCell ref="B7:O7"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="B5:O5"/>
-    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="B7:P7"/>
+    <mergeCell ref="B6:P6"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="B5:P5"/>
+    <mergeCell ref="B8:P8"/>
+    <mergeCell ref="A3:P3"/>
+    <mergeCell ref="B4:P4"/>
+    <mergeCell ref="A2:P2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -9569,7 +9603,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Fact table for the star schema — transaction-level grain, built from RAW_ staging data plus dimension keys.</t>
+          <t>Fact table for the star schema — transaction-level grain, built from RAW_ staging data plus dimension keys via Power Query (not re-fetched from Shopify).</t>
         </is>
       </c>
     </row>
@@ -9593,7 +9627,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Referenced by DAX measures across all dashboards.</t>
+          <t>Referenced by DAX measures — see passress-mis/dax/MEASURES.md.</t>
         </is>
       </c>
     </row>
@@ -9605,7 +9639,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Many-to-one into each related DIM_ table.</t>
+          <t>Many-to-one into each related DIM_ table — see dax/README.md for the full relationship list.</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9651,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Built in Power Query from RAW_ + DIM_ — Phase 2/3.</t>
+          <t>Live now: paste passress-mis/power-query/star-schema/FACT_Refunds.pq — see passress-mis/dax/README.md for setup order.</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9759,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Fact table for the star schema — transaction-level grain, built from RAW_ staging data plus dimension keys.</t>
+          <t>Fact table for the star schema — transaction-level grain, built from RAW_ staging data plus dimension keys via Power Query (not re-fetched from Shopify).</t>
         </is>
       </c>
     </row>
@@ -9749,7 +9783,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Referenced by DAX measures across all dashboards.</t>
+          <t>Referenced by DAX measures — see passress-mis/dax/MEASURES.md.</t>
         </is>
       </c>
     </row>
@@ -9761,7 +9795,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Many-to-one into each related DIM_ table.</t>
+          <t>Many-to-one into each related DIM_ table — see dax/README.md for the full relationship list.</t>
         </is>
       </c>
     </row>
@@ -9773,7 +9807,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Built in Power Query from RAW_ + DIM_ — Phase 2/3.</t>
+          <t>Live now: paste passress-mis/power-query/star-schema/FACT_InventoryMovements.pq — see passress-mis/dax/README.md for setup order.</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9927,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Fact table for the star schema — transaction-level grain, built from RAW_ staging data plus dimension keys.</t>
+          <t>Fact table for the star schema — transaction-level grain, built from RAW_ staging data plus dimension keys via Power Query (not re-fetched from Shopify).</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9951,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Referenced by DAX measures across all dashboards.</t>
+          <t>Referenced by DAX measures — see passress-mis/dax/MEASURES.md.</t>
         </is>
       </c>
     </row>
@@ -9929,7 +9963,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Many-to-one into each related DIM_ table.</t>
+          <t>Many-to-one into each related DIM_ table — see dax/README.md for the full relationship list.</t>
         </is>
       </c>
     </row>
@@ -9941,7 +9975,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Built in Power Query from RAW_ + DIM_ — Phase 2/3.</t>
+          <t>Live now: paste passress-mis/power-query/star-schema/FACT_Payments.pq — see passress-mis/dax/README.md for setup order.</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10053,7 @@
     <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -10035,6 +10069,7 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -10090,7 +10125,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Referenced by DAX measures across 08_Finance, 09_Profitability, 02/03 dashboards.</t>
+          <t>Referenced by DAX measures — see passress-mis/dax/MEASURES.md.</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10149,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>10_Expenses (already the source of truth — no external system). Loaded into this mirror in Phase 4 (Data Model wiring).</t>
+          <t>Live now: paste passress-mis/power-query/star-schema/FACT_ManualExpenses.pq — see passress-mis/dax/README.md for setup order.</t>
         </is>
       </c>
     </row>
@@ -10128,55 +10163,60 @@
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
+          <t>DateKey</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
           <t>ExpenseDate</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>ExpenseCategory</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>ExpenseSubcategory</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>SupplierID</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t>PaymentMethod</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="K11" s="17" t="inlineStr">
         <is>
           <t>RelatedCollection</t>
         </is>
       </c>
-      <c r="K11" s="17" t="inlineStr">
+      <c r="L11" s="17" t="inlineStr">
         <is>
           <t>RelatedSKU</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="M11" s="17" t="inlineStr">
         <is>
           <t>CostCenter</t>
         </is>
       </c>
-      <c r="M11" s="17" t="inlineStr">
+      <c r="N11" s="17" t="inlineStr">
         <is>
           <t>InvoiceNumber</t>
         </is>
@@ -10195,18 +10235,19 @@
       <c r="K12" s="32" t="n"/>
       <c r="L12" s="32" t="n"/>
       <c r="M12" s="32" t="n"/>
+      <c r="N12" s="32" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
   <mergeCells count="8">
-    <mergeCell ref="B6:M6"/>
-    <mergeCell ref="B7:M7"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="B5:M5"/>
-    <mergeCell ref="B8:M8"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="B4:M4"/>
-    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="B5:N5"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="B8:N8"/>
+    <mergeCell ref="B4:N4"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="B7:N7"/>
+    <mergeCell ref="B6:N6"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -10222,7 +10263,7 @@
     <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -10231,6 +10272,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -10286,7 +10328,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Referenced by DAX measures across 08_Finance, 09_Profitability, 02/03 dashboards.</t>
+          <t>Referenced by DAX measures — see passress-mis/dax/MEASURES.md.</t>
         </is>
       </c>
     </row>
@@ -10310,7 +10352,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>11_Capital (already the source of truth — no external system). Loaded into this mirror in Phase 4 (Data Model wiring).</t>
+          <t>Live now: paste passress-mis/power-query/star-schema/FACT_CapitalTransactions.pq — see passress-mis/dax/README.md for setup order.</t>
         </is>
       </c>
     </row>
@@ -10324,20 +10366,25 @@
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
+          <t>DateKey</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>TransactionType</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
@@ -10349,18 +10396,19 @@
       <c r="D12" s="32" t="n"/>
       <c r="E12" s="32" t="n"/>
       <c r="F12" s="32" t="n"/>
+      <c r="G12" s="32" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
   <mergeCells count="8">
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -10944,7 +10992,7 @@
     <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -10954,6 +11002,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -11009,7 +11058,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Referenced by DAX measures across 08_Finance, 09_Profitability, 02/03 dashboards.</t>
+          <t>Referenced by DAX measures — see passress-mis/dax/MEASURES.md.</t>
         </is>
       </c>
     </row>
@@ -11033,7 +11082,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>12_Suppliers (PO Header table) (already the source of truth — no external system). Loaded into this mirror in Phase 4 (Data Model wiring).</t>
+          <t>Live now: paste passress-mis/power-query/star-schema/FACT_PurchaseOrderHeader.pq — see passress-mis/dax/README.md for setup order.</t>
         </is>
       </c>
     </row>
@@ -11047,25 +11096,30 @@
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
+          <t>DateKey</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
           <t>SupplierID</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>OrderDate</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>ExpectedDeliveryDate</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -11078,18 +11132,19 @@
       <c r="E12" s="32" t="n"/>
       <c r="F12" s="32" t="n"/>
       <c r="G12" s="32" t="n"/>
+      <c r="H12" s="32" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
   <mergeCells count="8">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -11169,7 +11224,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Referenced by DAX measures across 08_Finance, 09_Profitability, 02/03 dashboards.</t>
+          <t>Referenced by DAX measures — see passress-mis/dax/MEASURES.md.</t>
         </is>
       </c>
     </row>
@@ -11193,7 +11248,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>12_Suppliers (PO Lines table) (already the source of truth — no external system). Loaded into this mirror in Phase 4 (Data Model wiring).</t>
+          <t>Live now: paste passress-mis/power-query/star-schema/FACT_PurchaseOrderLines.pq — see passress-mis/dax/README.md for setup order.</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11314,7 @@
     <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -11271,6 +11326,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -11326,7 +11382,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Referenced by DAX measures across 08_Finance, 09_Profitability, 02/03 dashboards.</t>
+          <t>Referenced by DAX measures — see passress-mis/dax/MEASURES.md.</t>
         </is>
       </c>
     </row>
@@ -11350,7 +11406,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>12_Suppliers (Goods Receipt table) (already the source of truth — no external system). Loaded into this mirror in Phase 4 (Data Model wiring).</t>
+          <t>Live now: paste passress-mis/power-query/star-schema/FACT_GoodsReceipt.pq — see passress-mis/dax/README.md for setup order.</t>
         </is>
       </c>
     </row>
@@ -11364,35 +11420,40 @@
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
+          <t>DateKey</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>GoodsReceivedDate</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>QuantityReceived</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>RemainingQuantity</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>ActualUnitCost</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>VarianceFromPO</t>
         </is>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t>Warehouse</t>
         </is>
@@ -11407,18 +11468,19 @@
       <c r="G12" s="32" t="n"/>
       <c r="H12" s="32" t="n"/>
       <c r="I12" s="32" t="n"/>
+      <c r="J12" s="32" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="1" password="C24F"/>
   <mergeCells count="8">
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B6:I6"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B7:J7"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="B8:J8"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="B6:J6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/passress-mis/PASSRESS_MIS.xlsx
+++ b/passress-mis/PASSRESS_MIS.xlsx
@@ -104,8 +104,8 @@
     <definedName name="LookupAlertSeverity">=tbl_LookupAlertSeverity[Alert Severity]</definedName>
     <definedName name="SupplierNameList">=tbl_SupplierMaster[Supplier Name]</definedName>
     <definedName name="POHeaderList">=tbl_POHeader[PO Number]</definedName>
-    <definedName name="SKUList">=RAW_Variants[SKU]</definedName>
-    <definedName name="CollectionTitleList">=RAW_Collections[Title]</definedName>
+    <definedName name="SKUList">=tbl_RAW_Variants[SKU]</definedName>
+    <definedName name="CollectionTitleList">=tbl_RAW_Collections[Title]</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'02_Partner_Dashboard'!$A$1:$L$140</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'03_CEO_Dashboard'!$A$1:$L$140</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="56">'RPT_ExecutiveBrief'!$A$1:$J$40</definedName>
@@ -3560,8 +3560,8 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tbl_VersionLog" displayName="tbl_VersionLog" ref="B36:E45" headerRowCount="1">
-  <autoFilter ref="B36:E45"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tbl_VersionLog" displayName="tbl_VersionLog" ref="B36:E46" headerRowCount="1">
+  <autoFilter ref="B36:E46"/>
   <tableColumns count="4">
     <tableColumn id="2" name="Version"/>
     <tableColumn id="3" name="Date"/>
@@ -3573,8 +3573,8 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="tbl_LookupExpenseCategory" displayName="tbl_LookupExpenseCategory" ref="B49:B59" headerRowCount="1">
-  <autoFilter ref="B49:B59"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="tbl_LookupExpenseCategory" displayName="tbl_LookupExpenseCategory" ref="B50:B60" headerRowCount="1">
+  <autoFilter ref="B50:B60"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Expense Category"/>
   </tableColumns>
@@ -3583,8 +3583,8 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="tbl_LookupExpenseSubcategory" displayName="tbl_LookupExpenseSubcategory" ref="B61:B73" headerRowCount="1">
-  <autoFilter ref="B61:B73"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="tbl_LookupExpenseSubcategory" displayName="tbl_LookupExpenseSubcategory" ref="B62:B74" headerRowCount="1">
+  <autoFilter ref="B62:B74"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Expense Subcategory"/>
   </tableColumns>
@@ -3593,8 +3593,8 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="tbl_LookupCostCenter" displayName="tbl_LookupCostCenter" ref="B75:B80" headerRowCount="1">
-  <autoFilter ref="B75:B80"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="tbl_LookupCostCenter" displayName="tbl_LookupCostCenter" ref="B76:B81" headerRowCount="1">
+  <autoFilter ref="B76:B81"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Cost Center"/>
   </tableColumns>
@@ -3603,8 +3603,8 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="tbl_LookupPaymentMethod" displayName="tbl_LookupPaymentMethod" ref="B82:B88" headerRowCount="1">
-  <autoFilter ref="B82:B88"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="tbl_LookupPaymentMethod" displayName="tbl_LookupPaymentMethod" ref="B83:B89" headerRowCount="1">
+  <autoFilter ref="B83:B89"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Payment Method"/>
   </tableColumns>
@@ -3613,8 +3613,8 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="tbl_LookupCurrency" displayName="tbl_LookupCurrency" ref="B90:B94" headerRowCount="1">
-  <autoFilter ref="B90:B94"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="tbl_LookupCurrency" displayName="tbl_LookupCurrency" ref="B91:B95" headerRowCount="1">
+  <autoFilter ref="B91:B95"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Currency"/>
   </tableColumns>
@@ -3623,8 +3623,8 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tbl_LookupSupplierType" displayName="tbl_LookupSupplierType" ref="B96:B104" headerRowCount="1">
-  <autoFilter ref="B96:B104"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tbl_LookupSupplierType" displayName="tbl_LookupSupplierType" ref="B97:B105" headerRowCount="1">
+  <autoFilter ref="B97:B105"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Supplier Type"/>
   </tableColumns>
@@ -3648,8 +3648,8 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="tbl_LookupSupplierStatus" displayName="tbl_LookupSupplierStatus" ref="B106:B109" headerRowCount="1">
-  <autoFilter ref="B106:B109"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="tbl_LookupSupplierStatus" displayName="tbl_LookupSupplierStatus" ref="B107:B110" headerRowCount="1">
+  <autoFilter ref="B107:B110"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Supplier Status"/>
   </tableColumns>
@@ -3658,8 +3658,8 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="tbl_LookupCapitalTransactionType" displayName="tbl_LookupCapitalTransactionType" ref="B111:B113" headerRowCount="1">
-  <autoFilter ref="B111:B113"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="tbl_LookupCapitalTransactionType" displayName="tbl_LookupCapitalTransactionType" ref="B112:B114" headerRowCount="1">
+  <autoFilter ref="B112:B114"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Capital Transaction Type"/>
   </tableColumns>
@@ -3668,8 +3668,8 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="tbl_LookupPOStatus" displayName="tbl_LookupPOStatus" ref="B115:B122" headerRowCount="1">
-  <autoFilter ref="B115:B122"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="tbl_LookupPOStatus" displayName="tbl_LookupPOStatus" ref="B116:B123" headerRowCount="1">
+  <autoFilter ref="B116:B123"/>
   <tableColumns count="1">
     <tableColumn id="2" name="PO Status"/>
   </tableColumns>
@@ -3678,8 +3678,8 @@
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="tbl_LookupWarehouse" displayName="tbl_LookupWarehouse" ref="B124:B127" headerRowCount="1">
-  <autoFilter ref="B124:B127"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="tbl_LookupWarehouse" displayName="tbl_LookupWarehouse" ref="B125:B128" headerRowCount="1">
+  <autoFilter ref="B125:B128"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Warehouse"/>
   </tableColumns>
@@ -3688,8 +3688,8 @@
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="tbl_LookupOwner" displayName="tbl_LookupOwner" ref="B129:B130" headerRowCount="1">
-  <autoFilter ref="B129:B130"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="tbl_LookupOwner" displayName="tbl_LookupOwner" ref="B130:B131" headerRowCount="1">
+  <autoFilter ref="B130:B131"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Owner"/>
   </tableColumns>
@@ -3698,8 +3698,8 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="tbl_LookupBudgetPeriod" displayName="tbl_LookupBudgetPeriod" ref="B132:B134" headerRowCount="1">
-  <autoFilter ref="B132:B134"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="tbl_LookupBudgetPeriod" displayName="tbl_LookupBudgetPeriod" ref="B133:B135" headerRowCount="1">
+  <autoFilter ref="B133:B135"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Budget Period"/>
   </tableColumns>
@@ -3708,8 +3708,8 @@
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="tbl_LookupBudgetCategory" displayName="tbl_LookupBudgetCategory" ref="B136:B141" headerRowCount="1">
-  <autoFilter ref="B136:B141"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="tbl_LookupBudgetCategory" displayName="tbl_LookupBudgetCategory" ref="B137:B142" headerRowCount="1">
+  <autoFilter ref="B137:B142"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Budget Category"/>
   </tableColumns>
@@ -3718,8 +3718,8 @@
 </file>
 
 <file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="tbl_LookupAlertSeverity" displayName="tbl_LookupAlertSeverity" ref="B143:B146" headerRowCount="1">
-  <autoFilter ref="B143:B146"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="tbl_LookupAlertSeverity" displayName="tbl_LookupAlertSeverity" ref="B144:B147" headerRowCount="1">
+  <autoFilter ref="B144:B147"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Alert Severity"/>
   </tableColumns>
@@ -3728,8 +3728,8 @@
 </file>
 
 <file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="tbl_KPITargets" displayName="tbl_KPITargets" ref="B150:F160" headerRowCount="1">
-  <autoFilter ref="B150:F160"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="tbl_KPITargets" displayName="tbl_KPITargets" ref="B151:F161" headerRowCount="1">
+  <autoFilter ref="B151:F161"/>
   <tableColumns count="5">
     <tableColumn id="2" name="KPI Name"/>
     <tableColumn id="3" name="Target Value"/>
@@ -3742,8 +3742,8 @@
 </file>
 
 <file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="29" name="tbl_HealthScoreWeights" displayName="tbl_HealthScoreWeights" ref="B164:C174" headerRowCount="1">
-  <autoFilter ref="B164:C174"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="29" name="tbl_HealthScoreWeights" displayName="tbl_HealthScoreWeights" ref="B165:C175" headerRowCount="1">
+  <autoFilter ref="B165:C175"/>
   <tableColumns count="2">
     <tableColumn id="2" name="Component"/>
     <tableColumn id="3" name="Weight"/>
@@ -3779,8 +3779,8 @@
 </file>
 
 <file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="30" name="tbl_Holidays" displayName="tbl_Holidays" ref="B178:C179" headerRowCount="1">
-  <autoFilter ref="B178:C179"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="30" name="tbl_Holidays" displayName="tbl_Holidays" ref="B179:C180" headerRowCount="1">
+  <autoFilter ref="B179:C180"/>
   <tableColumns count="2">
     <tableColumn id="2" name="Date"/>
     <tableColumn id="3" name="Holiday Name"/>
@@ -4992,7 +4992,7 @@
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="8">
-        <f>IFERROR(TEXT(MAX(LOG_RefreshHistory[Timestamp]),"dd-mmm hh:mm"),"—")</f>
+        <f>IFERROR(TEXT(MAX(tbl_LOG_RefreshHistory[Timestamp]),"dd-mmm hh:mm"),"—")</f>
         <v/>
       </c>
       <c r="C12" s="7" t="n"/>
@@ -7172,22 +7172,22 @@
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="8">
-        <f>IFERROR(TEXT(MAX(LOG_RefreshHistory[Timestamp]),"dd-mmm hh:mm"),"—")</f>
+        <f>IFERROR(TEXT(MAX(tbl_LOG_RefreshHistory[Timestamp]),"dd-mmm hh:mm"),"—")</f>
         <v/>
       </c>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="9">
-        <f>IFERROR(SUM(LOG_RefreshHistory[RowsLoaded]),"—")</f>
+        <f>IFERROR(SUM(tbl_LOG_RefreshHistory[RowsLoaded]),"—")</f>
         <v/>
       </c>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="9">
-        <f>IFERROR(COUNTIF(LOG_DataQuality[Status],"WARNING*"),"—")</f>
+        <f>IFERROR(COUNTIF(tbl_LOG_DataQuality[Status],"WARNING*"),"—")</f>
         <v/>
       </c>
       <c r="G12" s="7" t="n"/>
       <c r="H12" s="47">
-        <f>IFERROR(TODAY()-INT(MAX(LOG_RefreshHistory[Timestamp])),"—")</f>
+        <f>IFERROR(TODAY()-INT(MAX(tbl_LOG_RefreshHistory[Timestamp])),"—")</f>
         <v/>
       </c>
       <c r="I12" s="7" t="n"/>
@@ -7334,7 +7334,7 @@
         </is>
       </c>
       <c r="D28" s="52">
-        <f>COUNTIFS(RAW_Variants[SKU],"")</f>
+        <f>COUNTIFS(tbl_RAW_Variants[SKU],"")</f>
         <v/>
       </c>
       <c r="E28" s="30">
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="D30" s="53">
-        <f>COUNTIFS(DIM_Product[PrimarySupplierID],"")</f>
+        <f>COUNTIFS(tbl_DIM_Product[PrimarySupplierID],"")</f>
         <v/>
       </c>
       <c r="E30" s="24">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="F30" s="20" t="inlineStr">
         <is>
-          <t>PrimarySupplierID is best-effort (most recent Goods Receipt per SKU) — see DIM_Product.pq. A count here is expected for never-received SKUs, not necessarily an error.</t>
+          <t>PrimarySupplierID is best-effort (most recent Goods Receipt per SKU) — see DIM_Product.pq. A count here is expected for never-received SKUs, not necessarily an error. Uses tbl_DIM_Product (the placeholder name): DIM_/FACT_ tables go through the exact same Phase-1-placeholder-until-wired lifecycle as RAW_/LOG_ tables (dax/README.md Step 1) — DIM_Product with no prefix doesn't exist until the Data Model is built, same root cause as the RAW_/LOG_ fix above.</t>
         </is>
       </c>
     </row>
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="D31" s="53">
-        <f>SUMPRODUCT((COUNTIF(RAW_Orders[OrderID],RAW_Orders[OrderID])&gt;1)*1)</f>
+        <f>SUMPRODUCT((COUNTIF(tbl_RAW_Orders[OrderID],tbl_RAW_Orders[OrderID])&gt;1)*1)</f>
         <v/>
       </c>
       <c r="E31" s="24">
@@ -7459,7 +7459,7 @@
         </is>
       </c>
       <c r="D33" s="53">
-        <f>COUNTIFS(RAW_Products[CollectionIDs],"")</f>
+        <f>COUNTIFS(tbl_RAW_Products[CollectionIDs],"")</f>
         <v/>
       </c>
       <c r="E33" s="24">
@@ -7505,7 +7505,7 @@
         </is>
       </c>
       <c r="D35" s="53">
-        <f>COUNTIFS(RAW_InventoryLevels[Available],"&lt;0")</f>
+        <f>COUNTIFS(tbl_RAW_InventoryLevels[Available],"&lt;0")</f>
         <v/>
       </c>
       <c r="E35" s="24">
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="D36" s="53">
-        <f>COUNTIFS(RAW_Orders[CustomerID],"")</f>
+        <f>COUNTIFS(tbl_RAW_Orders[CustomerID],"")</f>
         <v/>
       </c>
       <c r="E36" s="24">
@@ -7555,7 +7555,7 @@
         </is>
       </c>
       <c r="D37" s="53">
-        <f>SUMPRODUCT((COUNTIF(RAW_Transactions[OrderID],RAW_Orders[OrderID])=0)*1)</f>
+        <f>SUMPRODUCT((COUNTIF(tbl_RAW_Transactions[OrderID],tbl_RAW_Orders[OrderID])=0)*1)</f>
         <v/>
       </c>
       <c r="E37" s="24">
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="D38" s="53">
-        <f>COUNTIF(LOG_DataQuality[Status],"WARNING*")</f>
+        <f>COUNTIF(tbl_LOG_DataQuality[Status],"WARNING*")</f>
         <v/>
       </c>
       <c r="E38" s="24">
@@ -7651,7 +7651,7 @@
     <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F179"/>
+  <dimension ref="A1:F180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -8266,679 +8266,676 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="11" t="inlineStr">
+    <row r="46">
+      <c r="B46" s="30" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="C46" s="30" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D46" s="30" t="inlineStr">
+        <is>
+          <t>Phase 9 — File-Corruption Hotfix (Real-World Test Finding)</t>
+        </is>
+      </c>
+      <c r="E46" s="30" t="inlineStr">
+        <is>
+          <t>Triggered by the first real Windows Excel open of this workbook, which required a repair just to load ('Removed Records: Named range from workbook.xml' + 'Formula from sheet5/10/12.xml' — confirmed via workbook.xml.rels to be 05_Products/10_Expenses/12_Suppliers, the three sheets sourcing SKU/Collection dropdowns from SKUList/CollectionTitleList). Root cause: those two named ranges (and several worksheet formulas in BI_Alerts, 14_Data_Quality, RPT_Workflow, 01_Home added in Phases 6-8) pointed at the POST-WIRING table name (RAW_Variants, LOG_DataQuality, etc.) rather than the always-present tbl_-prefixed placeholder — a Phase 6 design choice that assumed an unresolved reference would simply show a formula error until Power Query is wired. A real Excel open proved otherwise: a workbook-scoped defined name referencing a table that doesn't exist ANYWHERE in the file is structurally invalid at load time, not just unresolved at calculation time, so Excel strips the name and every Data Validation dropdown depending on it, forcing a file repair. Reverted every affected named range and worksheet formula back to the tbl_-prefixed placeholder name (DAX measures untouched — they read the Data Model, not Excel Table objects, so were never affected). A second, related finding from the same stricter validation: 14_Data_Quality's Missing Supplier check referenced DIM_Product directly, and DIM_/FACT_ tables go through the identical placeholder-until-wired lifecycle as RAW_/LOG_ (dax/README.md Step 1) — fixed to tbl_DIM_Product. Added a permanent build-time check verifying every defined name and every Table[Column] formula reference resolves to a table that actually exists in the generated file — 0 issues found after the fix (previously no such check existed; bracket-balance/XML-well-formedness checks don't catch a semantically invalid table reference). New required manual step added to DEPLOYMENT_GUIDE.md §5.4: rename SKUList/CollectionTitleList via Name Manager to drop the tbl_ prefix once RAW_Variants/RAW_Collections are actually wired — documented as a one-time, unmissable step rather than left to be silently forgotten. Full findings in /passress-mis/PHASE9_DOCUMENTATION.md; PHASE6_PRODUCTION_READINESS_REVIEW.md's original (superseded) fix table annotated, not rewritten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>MASTER DATA LOOKUP TABLES  (orange cells = configurable — edit freely, every dropdown in the workbook reads from here)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="B49" s="55" t="inlineStr">
+    <row r="50" ht="16" customHeight="1">
+      <c r="B50" s="55" t="inlineStr">
         <is>
           <t>Expense Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="57" t="inlineStr">
-        <is>
-          <t>Rent</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="57" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Rent</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="57" t="inlineStr">
         <is>
-          <t>Salaries</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="57" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Salaries</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="57" t="inlineStr">
         <is>
-          <t>Shipping &amp; Logistics</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="57" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>Shipping &amp; Logistics</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="57" t="inlineStr">
         <is>
-          <t>Software &amp; Subscriptions</t>
+          <t>Packaging</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="57" t="inlineStr">
         <is>
-          <t>Professional Fees</t>
+          <t>Software &amp; Subscriptions</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="57" t="inlineStr">
         <is>
-          <t>Bank Charges</t>
+          <t>Professional Fees</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="57" t="inlineStr">
         <is>
+          <t>Bank Charges</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="57" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="B61" s="55" t="inlineStr">
+    <row r="62" ht="16" customHeight="1">
+      <c r="B62" s="55" t="inlineStr">
         <is>
           <t>Expense Subcategory</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="57" t="inlineStr">
-        <is>
-          <t>General</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="57" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>General</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="57" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="57" t="inlineStr">
         <is>
-          <t>Online Ads</t>
+          <t>Warehouse</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="57" t="inlineStr">
         <is>
-          <t>Influencer</t>
+          <t>Online Ads</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="57" t="inlineStr">
         <is>
-          <t>Photography</t>
+          <t>Influencer</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="57" t="inlineStr">
         <is>
-          <t>Courier</t>
+          <t>Photography</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="57" t="inlineStr">
         <is>
-          <t>Customs &amp; Duties</t>
+          <t>Courier</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="57" t="inlineStr">
         <is>
-          <t>Software License</t>
+          <t>Customs &amp; Duties</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="57" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Software License</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="57" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Legal</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="57" t="inlineStr">
         <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="57" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="B75" s="55" t="inlineStr">
+    <row r="76" ht="16" customHeight="1">
+      <c r="B76" s="55" t="inlineStr">
         <is>
           <t>Cost Center</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="57" t="inlineStr">
-        <is>
-          <t>Head Office</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="57" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Head Office</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="57" t="inlineStr">
         <is>
-          <t>E-Commerce</t>
+          <t>Warehouse</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="57" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>E-Commerce</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="57" t="inlineStr">
         <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="57" t="inlineStr">
+        <is>
           <t>Production</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="16" customHeight="1">
-      <c r="B82" s="55" t="inlineStr">
+    <row r="83" ht="16" customHeight="1">
+      <c r="B83" s="55" t="inlineStr">
         <is>
           <t>Payment Method</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="57" t="inlineStr">
-        <is>
-          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="57" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="57" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="57" t="inlineStr">
         <is>
-          <t>Instapay</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="57" t="inlineStr">
         <is>
-          <t>Cheque</t>
+          <t>Instapay</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="57" t="inlineStr">
         <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="57" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="16" customHeight="1">
-      <c r="B90" s="55" t="inlineStr">
+    <row r="91" ht="16" customHeight="1">
+      <c r="B91" s="55" t="inlineStr">
         <is>
           <t>Currency</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" s="57" t="inlineStr">
-        <is>
-          <t>EGP</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="57" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EGP</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" s="57" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="57" t="inlineStr">
         <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="57" t="inlineStr">
+        <is>
           <t>GBP</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="16" customHeight="1">
-      <c r="B96" s="55" t="inlineStr">
+    <row r="97" ht="16" customHeight="1">
+      <c r="B97" s="55" t="inlineStr">
         <is>
           <t>Supplier Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" s="57" t="inlineStr">
-        <is>
-          <t>Fabric</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="57" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Fabric</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" s="57" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Accessories</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="B100" s="57" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>Manufacturing</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="B101" s="57" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Packaging</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="B102" s="57" t="inlineStr">
         <is>
-          <t>Marketing Agency</t>
+          <t>Logistics</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="B103" s="57" t="inlineStr">
         <is>
-          <t>Software Vendor</t>
+          <t>Marketing Agency</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="B104" s="57" t="inlineStr">
         <is>
+          <t>Software Vendor</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="57" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="16" customHeight="1">
-      <c r="B106" s="55" t="inlineStr">
+    <row r="107" ht="16" customHeight="1">
+      <c r="B107" s="55" t="inlineStr">
         <is>
           <t>Supplier Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="B107" s="57" t="inlineStr">
-        <is>
-          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="B108" s="57" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="B109" s="57" t="inlineStr">
         <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="57" t="inlineStr">
+        <is>
           <t>On Hold</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="16" customHeight="1">
-      <c r="B111" s="55" t="inlineStr">
+    <row r="112" ht="16" customHeight="1">
+      <c r="B112" s="55" t="inlineStr">
         <is>
           <t>Capital Transaction Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="B112" s="57" t="inlineStr">
-        <is>
-          <t>Capital Contribution</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="B113" s="57" t="inlineStr">
         <is>
+          <t>Capital Contribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="57" t="inlineStr">
+        <is>
           <t>Capital Withdrawal</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="16" customHeight="1">
-      <c r="B115" s="55" t="inlineStr">
+    <row r="116" ht="16" customHeight="1">
+      <c r="B116" s="55" t="inlineStr">
         <is>
           <t>PO Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="B116" s="57" t="inlineStr">
-        <is>
-          <t>Draft</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="B117" s="57" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Draft</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="B118" s="57" t="inlineStr">
         <is>
-          <t>Sent</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="B119" s="57" t="inlineStr">
         <is>
-          <t>Partially Received</t>
+          <t>Sent</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="B120" s="57" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Partially Received</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="B121" s="57" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Received</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="B122" s="57" t="inlineStr">
         <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" s="57" t="inlineStr">
+        <is>
           <t>Cancelled</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="16" customHeight="1">
-      <c r="B124" s="55" t="inlineStr">
+    <row r="125" ht="16" customHeight="1">
+      <c r="B125" s="55" t="inlineStr">
         <is>
           <t>Warehouse</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="B125" s="57" t="inlineStr">
-        <is>
-          <t>Main Warehouse</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="B126" s="57" t="inlineStr">
         <is>
-          <t>Retail Store</t>
+          <t>Main Warehouse</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="B127" s="57" t="inlineStr">
         <is>
+          <t>Retail Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="57" t="inlineStr">
+        <is>
           <t>Third-Party Logistics</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="16" customHeight="1">
-      <c r="B129" s="55" t="inlineStr">
+    <row r="130" ht="16" customHeight="1">
+      <c r="B130" s="55" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="B130" s="57" t="inlineStr">
+    <row r="131">
+      <c r="B131" s="57" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="16" customHeight="1">
-      <c r="B132" s="55" t="inlineStr">
+    <row r="133" ht="16" customHeight="1">
+      <c r="B133" s="55" t="inlineStr">
         <is>
           <t>Budget Period</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="B133" s="57" t="inlineStr">
-        <is>
-          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="B134" s="57" t="inlineStr">
         <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" s="57" t="inlineStr">
+        <is>
           <t>Yearly</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="16" customHeight="1">
-      <c r="B136" s="55" t="inlineStr">
+    <row r="137" ht="16" customHeight="1">
+      <c r="B137" s="55" t="inlineStr">
         <is>
           <t>Budget Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="B137" s="57" t="inlineStr">
-        <is>
-          <t>Revenue</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="B138" s="57" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Revenue</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="B139" s="57" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Expense</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="B140" s="57" t="inlineStr">
         <is>
-          <t>Purchasing</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="B141" s="57" t="inlineStr">
         <is>
+          <t>Purchasing</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" s="57" t="inlineStr">
+        <is>
           <t>Profit</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="16" customHeight="1">
-      <c r="B143" s="55" t="inlineStr">
+    <row r="144" ht="16" customHeight="1">
+      <c r="B144" s="55" t="inlineStr">
         <is>
           <t>Alert Severity</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="B144" s="57" t="inlineStr">
-        <is>
-          <t>Info</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="B145" s="57" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Info</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="B146" s="57" t="inlineStr">
         <is>
+          <t>Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" s="57" t="inlineStr">
+        <is>
           <t>Critical</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="B149" s="11" t="inlineStr">
+    <row r="150">
+      <c r="B150" s="11" t="inlineStr">
         <is>
           <t>KPI TARGETS  (green Target Value cells = type here)</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="18" customHeight="1">
-      <c r="B150" s="39" t="inlineStr">
+    <row r="151" ht="18" customHeight="1">
+      <c r="B151" s="39" t="inlineStr">
         <is>
           <t>KPI Name</t>
         </is>
       </c>
-      <c r="C150" s="39" t="inlineStr">
+      <c r="C151" s="39" t="inlineStr">
         <is>
           <t>Target Value</t>
         </is>
       </c>
-      <c r="D150" s="39" t="inlineStr">
+      <c r="D151" s="39" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="E150" s="39" t="inlineStr">
+      <c r="E151" s="39" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="F150" s="39" t="inlineStr">
+      <c r="F151" s="39" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="B151" s="30" t="inlineStr">
-        <is>
-          <t>Sales Target</t>
-        </is>
-      </c>
-      <c r="C151" s="58" t="n">
-        <v>500000</v>
-      </c>
-      <c r="D151" s="30" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-      <c r="E151" s="58" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-      <c r="F151" s="30" t="inlineStr">
-        <is>
-          <t>Net Sales target</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="B152" s="30" t="inlineStr">
         <is>
-          <t>Margin Target</t>
+          <t>Sales Target</t>
         </is>
       </c>
       <c r="C152" s="58" t="n">
-        <v>0.55</v>
+        <v>500000</v>
       </c>
       <c r="D152" s="30" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>EGP</t>
         </is>
       </c>
       <c r="E152" s="58" t="inlineStr">
@@ -8948,22 +8945,22 @@
       </c>
       <c r="F152" s="30" t="inlineStr">
         <is>
-          <t>Gross Margin % target</t>
+          <t>Net Sales target</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="B153" s="30" t="inlineStr">
         <is>
-          <t>Orders Target</t>
+          <t>Margin Target</t>
         </is>
       </c>
       <c r="C153" s="58" t="n">
-        <v>400</v>
+        <v>0.55</v>
       </c>
       <c r="D153" s="30" t="inlineStr">
         <is>
-          <t>Count</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E153" s="58" t="inlineStr">
@@ -8973,22 +8970,22 @@
       </c>
       <c r="F153" s="30" t="inlineStr">
         <is>
-          <t>Order Count target</t>
+          <t>Gross Margin % target</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="B154" s="30" t="inlineStr">
         <is>
-          <t>Inventory Target</t>
+          <t>Orders Target</t>
         </is>
       </c>
       <c r="C154" s="58" t="n">
-        <v>300000</v>
+        <v>400</v>
       </c>
       <c r="D154" s="30" t="inlineStr">
         <is>
-          <t>EGP</t>
+          <t>Count</t>
         </is>
       </c>
       <c r="E154" s="58" t="inlineStr">
@@ -8998,18 +8995,18 @@
       </c>
       <c r="F154" s="30" t="inlineStr">
         <is>
-          <t>Inventory Value ceiling (avoid overstock)</t>
+          <t>Order Count target</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="B155" s="30" t="inlineStr">
         <is>
-          <t>AOV Target</t>
+          <t>Inventory Target</t>
         </is>
       </c>
       <c r="C155" s="58" t="n">
-        <v>1200</v>
+        <v>300000</v>
       </c>
       <c r="D155" s="30" t="inlineStr">
         <is>
@@ -9023,18 +9020,18 @@
       </c>
       <c r="F155" s="30" t="inlineStr">
         <is>
-          <t>Average Order Value target</t>
+          <t>Inventory Value ceiling (avoid overstock)</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="B156" s="30" t="inlineStr">
         <is>
-          <t>CAC Target</t>
+          <t>AOV Target</t>
         </is>
       </c>
       <c r="C156" s="58" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="D156" s="30" t="inlineStr">
         <is>
@@ -9048,22 +9045,22 @@
       </c>
       <c r="F156" s="30" t="inlineStr">
         <is>
-          <t>Customer Acquisition Cost ceiling — needs Marketing-Ready spend data (Phase 6+) to compute Actual</t>
+          <t>Average Order Value target</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="B157" s="30" t="inlineStr">
         <is>
-          <t>ROAS Target</t>
+          <t>CAC Target</t>
         </is>
       </c>
       <c r="C157" s="58" t="n">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="D157" s="30" t="inlineStr">
         <is>
-          <t>Ratio</t>
+          <t>EGP</t>
         </is>
       </c>
       <c r="E157" s="58" t="inlineStr">
@@ -9073,22 +9070,22 @@
       </c>
       <c r="F157" s="30" t="inlineStr">
         <is>
-          <t>Return on Ad Spend target — needs Marketing-Ready spend data (Phase 6+) to compute Actual</t>
+          <t>Customer Acquisition Cost ceiling — needs Marketing-Ready spend data (Phase 6+) to compute Actual</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="B158" s="30" t="inlineStr">
         <is>
-          <t>Repeat Customer % Target</t>
+          <t>ROAS Target</t>
         </is>
       </c>
       <c r="C158" s="58" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="D158" s="30" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>Ratio</t>
         </is>
       </c>
       <c r="E158" s="58" t="inlineStr">
@@ -9098,18 +9095,18 @@
       </c>
       <c r="F158" s="30" t="inlineStr">
         <is>
-          <t>Returning Customers / Customers Active target</t>
+          <t>Return on Ad Spend target — needs Marketing-Ready spend data (Phase 6+) to compute Actual</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="B159" s="30" t="inlineStr">
         <is>
-          <t>Conversion Rate Target</t>
+          <t>Repeat Customer % Target</t>
         </is>
       </c>
       <c r="C159" s="58" t="n">
-        <v>0.02</v>
+        <v>0.3</v>
       </c>
       <c r="D159" s="30" t="inlineStr">
         <is>
@@ -9123,68 +9120,83 @@
       </c>
       <c r="F159" s="30" t="inlineStr">
         <is>
-          <t>Needs Shopify session/traffic data (not fetched — Admin API has no storefront analytics) to compute Actual</t>
+          <t>Returning Customers / Customers Active target</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="B160" s="30" t="inlineStr">
         <is>
+          <t>Conversion Rate Target</t>
+        </is>
+      </c>
+      <c r="C160" s="58" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D160" s="30" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E160" s="58" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="F160" s="30" t="inlineStr">
+        <is>
+          <t>Needs Shopify session/traffic data (not fetched — Admin API has no storefront analytics) to compute Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" s="30" t="inlineStr">
+        <is>
           <t>Inventory Turnover Target</t>
         </is>
       </c>
-      <c r="C160" s="58" t="n">
+      <c r="C161" s="58" t="n">
         <v>6</v>
       </c>
-      <c r="D160" s="30" t="inlineStr">
+      <c r="D161" s="30" t="inlineStr">
         <is>
           <t>Ratio</t>
         </is>
       </c>
-      <c r="E160" s="58" t="inlineStr">
+      <c r="E161" s="58" t="inlineStr">
         <is>
           <t>Yearly</t>
         </is>
       </c>
-      <c r="F160" s="30" t="inlineStr">
+      <c r="F161" s="30" t="inlineStr">
         <is>
           <t>COGS / Average Inventory Value target</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="B163" s="11" t="inlineStr">
+    <row r="164">
+      <c r="B164" s="11" t="inlineStr">
         <is>
           <t>BUSINESS HEALTH SCORE WEIGHTS  (green cells = type here — must be numeric, any scale)</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="18" customHeight="1">
-      <c r="B164" s="39" t="inlineStr">
+    <row r="165" ht="18" customHeight="1">
+      <c r="B165" s="39" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="C164" s="39" t="inlineStr">
+      <c r="C165" s="39" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="B165" s="30" t="inlineStr">
-        <is>
-          <t>Revenue Growth</t>
-        </is>
-      </c>
-      <c r="C165" s="58" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="166">
       <c r="B166" s="30" t="inlineStr">
         <is>
-          <t>Gross Margin</t>
+          <t>Revenue Growth</t>
         </is>
       </c>
       <c r="C166" s="58" t="n">
@@ -9194,7 +9206,7 @@
     <row r="167">
       <c r="B167" s="30" t="inlineStr">
         <is>
-          <t>Cash Position</t>
+          <t>Gross Margin</t>
         </is>
       </c>
       <c r="C167" s="58" t="n">
@@ -9204,17 +9216,17 @@
     <row r="168">
       <c r="B168" s="30" t="inlineStr">
         <is>
-          <t>Inventory Health</t>
+          <t>Cash Position</t>
         </is>
       </c>
       <c r="C168" s="58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="169">
       <c r="B169" s="30" t="inlineStr">
         <is>
-          <t>Customer Growth</t>
+          <t>Inventory Health</t>
         </is>
       </c>
       <c r="C169" s="58" t="n">
@@ -9224,7 +9236,7 @@
     <row r="170">
       <c r="B170" s="30" t="inlineStr">
         <is>
-          <t>Repeat Customers</t>
+          <t>Customer Growth</t>
         </is>
       </c>
       <c r="C170" s="58" t="n">
@@ -9234,7 +9246,7 @@
     <row r="171">
       <c r="B171" s="30" t="inlineStr">
         <is>
-          <t>Return Rate</t>
+          <t>Repeat Customers</t>
         </is>
       </c>
       <c r="C171" s="58" t="n">
@@ -9244,17 +9256,17 @@
     <row r="172">
       <c r="B172" s="30" t="inlineStr">
         <is>
-          <t>Budget Performance</t>
+          <t>Return Rate</t>
         </is>
       </c>
       <c r="C172" s="58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="173">
       <c r="B173" s="30" t="inlineStr">
         <is>
-          <t>Data Quality</t>
+          <t>Budget Performance</t>
         </is>
       </c>
       <c r="C173" s="58" t="n">
@@ -9264,35 +9276,45 @@
     <row r="174">
       <c r="B174" s="30" t="inlineStr">
         <is>
-          <t>Alerts</t>
+          <t>Data Quality</t>
         </is>
       </c>
       <c r="C174" s="58" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="177">
-      <c r="B177" s="11" t="inlineStr">
+    <row r="175">
+      <c r="B175" s="30" t="inlineStr">
+        <is>
+          <t>Alerts</t>
+        </is>
+      </c>
+      <c r="C175" s="58" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" s="11" t="inlineStr">
         <is>
           <t>HOLIDAYS  (green cells = type here — optional, empty by default)</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="18" customHeight="1">
-      <c r="B178" s="39" t="inlineStr">
+    <row r="179" ht="18" customHeight="1">
+      <c r="B179" s="39" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C178" s="39" t="inlineStr">
+      <c r="C179" s="39" t="inlineStr">
         <is>
           <t>Holiday Name</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="B179" s="40" t="n"/>
-      <c r="C179" s="40" t="inlineStr">
+    <row r="180">
+      <c r="B180" s="40" t="n"/>
+      <c r="C180" s="40" t="inlineStr">
         <is>
           <t>EXAMPLE — delete or overwrite this row; leave the table empty if no holidays apply</t>
         </is>
@@ -9311,7 +9333,7 @@
     <mergeCell ref="B6:D6"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="E151:E160" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the Period list — free text isn't accepted here." promptTitle="Period" prompt="Monthly or Yearly." type="list" errorStyle="stop">
+    <dataValidation sqref="E152:E161" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the Period list — free text isn't accepted here." promptTitle="Period" prompt="Monthly or Yearly." type="list" errorStyle="stop">
       <formula1>=LookupBudgetPeriod</formula1>
     </dataValidation>
   </dataValidations>
@@ -19247,7 +19269,7 @@
         </is>
       </c>
       <c r="E18" s="24">
-        <f>IF(COUNTIFS(RAW_Variants[SKU],"")&gt;0,"TRIGGERED","OK")</f>
+        <f>IF(COUNTIFS(tbl_RAW_Variants[SKU],"")&gt;0,"TRIGGERED","OK")</f>
         <v/>
       </c>
       <c r="F18" s="24" t="inlineStr">
@@ -19403,7 +19425,7 @@
         </is>
       </c>
       <c r="E24" s="24">
-        <f>IF(COUNTIFS(LOG_RefreshHistory[Timestamp],"&gt;="&amp;TODAY()-2)=0,"TRIGGERED","OK")</f>
+        <f>IF(COUNTIFS(tbl_LOG_RefreshHistory[Timestamp],"&gt;="&amp;TODAY()-2)=0,"TRIGGERED","OK")</f>
         <v/>
       </c>
       <c r="F24" s="24" t="inlineStr">
@@ -19429,7 +19451,7 @@
         </is>
       </c>
       <c r="E25" s="24">
-        <f>IF(COUNTIF(LOG_DataQuality[Status],"WARNING*")&gt;0,"TRIGGERED","OK")</f>
+        <f>IF(COUNTIF(tbl_LOG_DataQuality[Status],"WARNING*")&gt;0,"TRIGGERED","OK")</f>
         <v/>
       </c>
       <c r="F25" s="24" t="inlineStr">
@@ -21227,7 +21249,7 @@
         </is>
       </c>
       <c r="C16" s="53">
-        <f>COUNTIFS(RAW_Orders[FulfillmentStatus],"&lt;&gt;FULFILLED")</f>
+        <f>COUNTIFS(tbl_RAW_Orders[FulfillmentStatus],"&lt;&gt;FULFILLED")</f>
         <v/>
       </c>
       <c r="D16" s="20" t="inlineStr">

--- a/passress-mis/PASSRESS_MIS.xlsx
+++ b/passress-mis/PASSRESS_MIS.xlsx
@@ -685,9 +685,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'02_Partner_Dashboard'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -713,9 +713,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'02_Partner_Dashboard'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -740,9 +740,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'02_Partner_Dashboard'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -767,9 +767,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'02_Partner_Dashboard'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -794,9 +794,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'02_Partner_Dashboard'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -821,9 +821,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'02_Partner_Dashboard'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -848,9 +848,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'02_Partner_Dashboard'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -875,9 +875,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'02_Partner_Dashboard'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -902,9 +902,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'02_Partner_Dashboard'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -929,9 +929,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'02_Partner_Dashboard'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -956,9 +956,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'02_Partner_Dashboard'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -983,9 +983,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'02_Partner_Dashboard'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1066,9 +1066,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'04_Sales'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1094,9 +1094,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'04_Sales'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1121,9 +1121,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'04_Sales'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1148,9 +1148,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'04_Sales'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1175,9 +1175,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'04_Sales'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1202,9 +1202,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'04_Sales'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1229,9 +1229,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'04_Sales'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1256,9 +1256,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'04_Sales'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1283,9 +1283,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'04_Sales'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1310,9 +1310,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'04_Sales'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1337,9 +1337,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'04_Sales'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1364,9 +1364,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'04_Sales'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1440,9 +1440,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'05_Products'!$B$18:$B$27</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1524,9 +1524,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'07_Inventory'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1552,9 +1552,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'07_Inventory'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1579,9 +1579,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'07_Inventory'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1606,9 +1606,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'07_Inventory'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1633,9 +1633,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'07_Inventory'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1660,9 +1660,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'07_Inventory'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1687,9 +1687,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'07_Inventory'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1714,9 +1714,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'07_Inventory'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1741,9 +1741,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'07_Inventory'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1768,9 +1768,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'07_Inventory'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1795,9 +1795,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'07_Inventory'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1822,9 +1822,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'07_Inventory'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1908,9 +1908,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'08_Finance'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1942,9 +1942,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'08_Finance'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1976,9 +1976,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'08_Finance'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2063,9 +2063,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'09_Profitability'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2091,9 +2091,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'09_Profitability'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2118,9 +2118,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'09_Profitability'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2145,9 +2145,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'09_Profitability'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2172,9 +2172,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'09_Profitability'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2199,9 +2199,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'09_Profitability'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2226,9 +2226,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'09_Profitability'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2253,9 +2253,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'09_Profitability'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2280,9 +2280,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'09_Profitability'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2307,9 +2307,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'09_Profitability'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2334,9 +2334,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'09_Profitability'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2361,9 +2361,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'09_Profitability'!$C$19:$N$19</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2444,9 +2444,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'13_Marketing'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2472,9 +2472,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'13_Marketing'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2499,9 +2499,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'13_Marketing'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2526,9 +2526,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'13_Marketing'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2553,9 +2553,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'13_Marketing'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2580,9 +2580,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'13_Marketing'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2607,9 +2607,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'13_Marketing'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2634,9 +2634,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'13_Marketing'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2661,9 +2661,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'13_Marketing'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2688,9 +2688,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'13_Marketing'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2715,9 +2715,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'13_Marketing'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2742,9 +2742,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'13_Marketing'!$C$18:$N$18</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2825,9 +2825,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'LOG_RefreshHistory'!$C$12:$C$500</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2909,9 +2909,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'RPT_Workflow'!$C$35:$N$35</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2937,9 +2937,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'RPT_Workflow'!$C$35:$N$35</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2964,9 +2964,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'RPT_Workflow'!$C$35:$N$35</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -2991,9 +2991,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'RPT_Workflow'!$C$35:$N$35</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -3018,9 +3018,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'RPT_Workflow'!$C$35:$N$35</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -3045,9 +3045,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'RPT_Workflow'!$C$35:$N$35</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -3072,9 +3072,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'RPT_Workflow'!$C$35:$N$35</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -3099,9 +3099,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'RPT_Workflow'!$C$35:$N$35</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -3126,9 +3126,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'RPT_Workflow'!$C$35:$N$35</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -3153,9 +3153,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'RPT_Workflow'!$C$35:$N$35</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -3180,9 +3180,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'RPT_Workflow'!$C$35:$N$35</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -3207,9 +3207,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'RPT_Workflow'!$C$35:$N$35</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -3560,8 +3560,8 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tbl_VersionLog" displayName="tbl_VersionLog" ref="B36:E46" headerRowCount="1">
-  <autoFilter ref="B36:E46"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tbl_VersionLog" displayName="tbl_VersionLog" ref="B36:E47" headerRowCount="1">
+  <autoFilter ref="B36:E47"/>
   <tableColumns count="4">
     <tableColumn id="2" name="Version"/>
     <tableColumn id="3" name="Date"/>
@@ -3573,8 +3573,8 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="tbl_LookupExpenseCategory" displayName="tbl_LookupExpenseCategory" ref="B50:B60" headerRowCount="1">
-  <autoFilter ref="B50:B60"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="tbl_LookupExpenseCategory" displayName="tbl_LookupExpenseCategory" ref="B51:B61" headerRowCount="1">
+  <autoFilter ref="B51:B61"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Expense Category"/>
   </tableColumns>
@@ -3583,8 +3583,8 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="tbl_LookupExpenseSubcategory" displayName="tbl_LookupExpenseSubcategory" ref="B62:B74" headerRowCount="1">
-  <autoFilter ref="B62:B74"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="tbl_LookupExpenseSubcategory" displayName="tbl_LookupExpenseSubcategory" ref="B63:B75" headerRowCount="1">
+  <autoFilter ref="B63:B75"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Expense Subcategory"/>
   </tableColumns>
@@ -3593,8 +3593,8 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="tbl_LookupCostCenter" displayName="tbl_LookupCostCenter" ref="B76:B81" headerRowCount="1">
-  <autoFilter ref="B76:B81"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="tbl_LookupCostCenter" displayName="tbl_LookupCostCenter" ref="B77:B82" headerRowCount="1">
+  <autoFilter ref="B77:B82"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Cost Center"/>
   </tableColumns>
@@ -3603,8 +3603,8 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="tbl_LookupPaymentMethod" displayName="tbl_LookupPaymentMethod" ref="B83:B89" headerRowCount="1">
-  <autoFilter ref="B83:B89"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="tbl_LookupPaymentMethod" displayName="tbl_LookupPaymentMethod" ref="B84:B90" headerRowCount="1">
+  <autoFilter ref="B84:B90"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Payment Method"/>
   </tableColumns>
@@ -3613,8 +3613,8 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="tbl_LookupCurrency" displayName="tbl_LookupCurrency" ref="B91:B95" headerRowCount="1">
-  <autoFilter ref="B91:B95"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="tbl_LookupCurrency" displayName="tbl_LookupCurrency" ref="B92:B96" headerRowCount="1">
+  <autoFilter ref="B92:B96"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Currency"/>
   </tableColumns>
@@ -3623,8 +3623,8 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tbl_LookupSupplierType" displayName="tbl_LookupSupplierType" ref="B97:B105" headerRowCount="1">
-  <autoFilter ref="B97:B105"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tbl_LookupSupplierType" displayName="tbl_LookupSupplierType" ref="B98:B106" headerRowCount="1">
+  <autoFilter ref="B98:B106"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Supplier Type"/>
   </tableColumns>
@@ -3648,8 +3648,8 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="tbl_LookupSupplierStatus" displayName="tbl_LookupSupplierStatus" ref="B107:B110" headerRowCount="1">
-  <autoFilter ref="B107:B110"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="tbl_LookupSupplierStatus" displayName="tbl_LookupSupplierStatus" ref="B108:B111" headerRowCount="1">
+  <autoFilter ref="B108:B111"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Supplier Status"/>
   </tableColumns>
@@ -3658,8 +3658,8 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="tbl_LookupCapitalTransactionType" displayName="tbl_LookupCapitalTransactionType" ref="B112:B114" headerRowCount="1">
-  <autoFilter ref="B112:B114"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="tbl_LookupCapitalTransactionType" displayName="tbl_LookupCapitalTransactionType" ref="B113:B115" headerRowCount="1">
+  <autoFilter ref="B113:B115"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Capital Transaction Type"/>
   </tableColumns>
@@ -3668,8 +3668,8 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="tbl_LookupPOStatus" displayName="tbl_LookupPOStatus" ref="B116:B123" headerRowCount="1">
-  <autoFilter ref="B116:B123"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="tbl_LookupPOStatus" displayName="tbl_LookupPOStatus" ref="B117:B124" headerRowCount="1">
+  <autoFilter ref="B117:B124"/>
   <tableColumns count="1">
     <tableColumn id="2" name="PO Status"/>
   </tableColumns>
@@ -3678,8 +3678,8 @@
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="tbl_LookupWarehouse" displayName="tbl_LookupWarehouse" ref="B125:B128" headerRowCount="1">
-  <autoFilter ref="B125:B128"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="tbl_LookupWarehouse" displayName="tbl_LookupWarehouse" ref="B126:B129" headerRowCount="1">
+  <autoFilter ref="B126:B129"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Warehouse"/>
   </tableColumns>
@@ -3688,8 +3688,8 @@
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="tbl_LookupOwner" displayName="tbl_LookupOwner" ref="B130:B131" headerRowCount="1">
-  <autoFilter ref="B130:B131"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="tbl_LookupOwner" displayName="tbl_LookupOwner" ref="B131:B132" headerRowCount="1">
+  <autoFilter ref="B131:B132"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Owner"/>
   </tableColumns>
@@ -3698,8 +3698,8 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="tbl_LookupBudgetPeriod" displayName="tbl_LookupBudgetPeriod" ref="B133:B135" headerRowCount="1">
-  <autoFilter ref="B133:B135"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="tbl_LookupBudgetPeriod" displayName="tbl_LookupBudgetPeriod" ref="B134:B136" headerRowCount="1">
+  <autoFilter ref="B134:B136"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Budget Period"/>
   </tableColumns>
@@ -3708,8 +3708,8 @@
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="tbl_LookupBudgetCategory" displayName="tbl_LookupBudgetCategory" ref="B137:B142" headerRowCount="1">
-  <autoFilter ref="B137:B142"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="tbl_LookupBudgetCategory" displayName="tbl_LookupBudgetCategory" ref="B138:B143" headerRowCount="1">
+  <autoFilter ref="B138:B143"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Budget Category"/>
   </tableColumns>
@@ -3718,8 +3718,8 @@
 </file>
 
 <file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="tbl_LookupAlertSeverity" displayName="tbl_LookupAlertSeverity" ref="B144:B147" headerRowCount="1">
-  <autoFilter ref="B144:B147"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="tbl_LookupAlertSeverity" displayName="tbl_LookupAlertSeverity" ref="B145:B148" headerRowCount="1">
+  <autoFilter ref="B145:B148"/>
   <tableColumns count="1">
     <tableColumn id="2" name="Alert Severity"/>
   </tableColumns>
@@ -3728,8 +3728,8 @@
 </file>
 
 <file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="tbl_KPITargets" displayName="tbl_KPITargets" ref="B151:F161" headerRowCount="1">
-  <autoFilter ref="B151:F161"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="tbl_KPITargets" displayName="tbl_KPITargets" ref="B152:F162" headerRowCount="1">
+  <autoFilter ref="B152:F162"/>
   <tableColumns count="5">
     <tableColumn id="2" name="KPI Name"/>
     <tableColumn id="3" name="Target Value"/>
@@ -3742,8 +3742,8 @@
 </file>
 
 <file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="29" name="tbl_HealthScoreWeights" displayName="tbl_HealthScoreWeights" ref="B165:C175" headerRowCount="1">
-  <autoFilter ref="B165:C175"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="29" name="tbl_HealthScoreWeights" displayName="tbl_HealthScoreWeights" ref="B166:C176" headerRowCount="1">
+  <autoFilter ref="B166:C176"/>
   <tableColumns count="2">
     <tableColumn id="2" name="Component"/>
     <tableColumn id="3" name="Weight"/>
@@ -3779,8 +3779,8 @@
 </file>
 
 <file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="30" name="tbl_Holidays" displayName="tbl_Holidays" ref="B179:C180" headerRowCount="1">
-  <autoFilter ref="B179:C180"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="30" name="tbl_Holidays" displayName="tbl_Holidays" ref="B180:C181" headerRowCount="1">
+  <autoFilter ref="B180:C181"/>
   <tableColumns count="2">
     <tableColumn id="2" name="Date"/>
     <tableColumn id="3" name="Holiday Name"/>
@@ -7651,7 +7651,7 @@
     <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F180"/>
+  <dimension ref="A1:F181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -8288,679 +8288,676 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="11" t="inlineStr">
+    <row r="47">
+      <c r="B47" s="30" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="C47" s="30" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D47" s="30" t="inlineStr">
+        <is>
+          <t>Phase 9 Addendum — Chart Category Type Fix</t>
+        </is>
+      </c>
+      <c r="E47" s="30" t="inlineStr">
+        <is>
+          <t>A repair prompt was still reported after 9.0's fix, on a fresh Desktop Excel open. Investigated by reading the generated chart XML directly (LibreOffice was tried as an independent second validator but is unusable in this build environment — fails to load even a trivial one-cell test workbook, an environment limitation unrelated to this file). Finding: all 9 charts have text-valued category axes (month labels from a TEXT() formula, or product/customer names from CUBERANKEDMEMBER) but openpyxl's Chart.set_categories() unconditionally writes a numeric reference (&lt;c:numRef&gt;) regardless of the referenced cells' actual content — confirmed by reading openpyxl's own source. Present since the charting pattern was first used in Phase 5, not something Phase 8 introduced; only became visible once the file was actually tested against a repair-capable Desktop Excel. Fixed with a new set_text_categories() helper that builds each chart's category axis explicitly as a string reference (AxDataSource(strRef=StrRef(...))) instead — applied in all three chart-building functions. Verified in the regenerated file: every chart*.xml part now uses &lt;c:strRef&gt; for its category axis. Documented honestly as NOT yet confirmed to be the full explanation for the second repair report (no detailed repair log was available for this occurrence, unlike 9.0's) — a real, independent, spec-level defect fixed on its own merits; the next diagnostic step if a repair prompt still appears is the detailed 'Removed Records' log, not further speculation. Full addendum in /passress-mis/PHASE9_DOCUMENTATION.md §7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>MASTER DATA LOOKUP TABLES  (orange cells = configurable — edit freely, every dropdown in the workbook reads from here)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="B50" s="55" t="inlineStr">
+    <row r="51" ht="16" customHeight="1">
+      <c r="B51" s="55" t="inlineStr">
         <is>
           <t>Expense Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="57" t="inlineStr">
-        <is>
-          <t>Rent</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="57" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Rent</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="57" t="inlineStr">
         <is>
-          <t>Salaries</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="57" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Salaries</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="57" t="inlineStr">
         <is>
-          <t>Shipping &amp; Logistics</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="57" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>Shipping &amp; Logistics</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="57" t="inlineStr">
         <is>
-          <t>Software &amp; Subscriptions</t>
+          <t>Packaging</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="57" t="inlineStr">
         <is>
-          <t>Professional Fees</t>
+          <t>Software &amp; Subscriptions</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="57" t="inlineStr">
         <is>
-          <t>Bank Charges</t>
+          <t>Professional Fees</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="57" t="inlineStr">
         <is>
+          <t>Bank Charges</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="57" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="B62" s="55" t="inlineStr">
+    <row r="63" ht="16" customHeight="1">
+      <c r="B63" s="55" t="inlineStr">
         <is>
           <t>Expense Subcategory</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="57" t="inlineStr">
-        <is>
-          <t>General</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="57" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>General</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="57" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="57" t="inlineStr">
         <is>
-          <t>Online Ads</t>
+          <t>Warehouse</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="57" t="inlineStr">
         <is>
-          <t>Influencer</t>
+          <t>Online Ads</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="57" t="inlineStr">
         <is>
-          <t>Photography</t>
+          <t>Influencer</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="57" t="inlineStr">
         <is>
-          <t>Courier</t>
+          <t>Photography</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="57" t="inlineStr">
         <is>
-          <t>Customs &amp; Duties</t>
+          <t>Courier</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="57" t="inlineStr">
         <is>
-          <t>Software License</t>
+          <t>Customs &amp; Duties</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="57" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Software License</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="57" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Legal</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="57" t="inlineStr">
         <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="57" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="16" customHeight="1">
-      <c r="B76" s="55" t="inlineStr">
+    <row r="77" ht="16" customHeight="1">
+      <c r="B77" s="55" t="inlineStr">
         <is>
           <t>Cost Center</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="57" t="inlineStr">
-        <is>
-          <t>Head Office</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="57" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Head Office</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="57" t="inlineStr">
         <is>
-          <t>E-Commerce</t>
+          <t>Warehouse</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="57" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>E-Commerce</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="57" t="inlineStr">
         <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="57" t="inlineStr">
+        <is>
           <t>Production</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="16" customHeight="1">
-      <c r="B83" s="55" t="inlineStr">
+    <row r="84" ht="16" customHeight="1">
+      <c r="B84" s="55" t="inlineStr">
         <is>
           <t>Payment Method</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="57" t="inlineStr">
-        <is>
-          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="57" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="57" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="57" t="inlineStr">
         <is>
-          <t>Instapay</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="57" t="inlineStr">
         <is>
-          <t>Cheque</t>
+          <t>Instapay</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="57" t="inlineStr">
         <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="57" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="16" customHeight="1">
-      <c r="B91" s="55" t="inlineStr">
+    <row r="92" ht="16" customHeight="1">
+      <c r="B92" s="55" t="inlineStr">
         <is>
           <t>Currency</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" s="57" t="inlineStr">
-        <is>
-          <t>EGP</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" s="57" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EGP</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="57" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" s="57" t="inlineStr">
         <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="57" t="inlineStr">
+        <is>
           <t>GBP</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="16" customHeight="1">
-      <c r="B97" s="55" t="inlineStr">
+    <row r="98" ht="16" customHeight="1">
+      <c r="B98" s="55" t="inlineStr">
         <is>
           <t>Supplier Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="57" t="inlineStr">
-        <is>
-          <t>Fabric</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" s="57" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Fabric</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="B100" s="57" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Accessories</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="B101" s="57" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>Manufacturing</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="B102" s="57" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Packaging</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="B103" s="57" t="inlineStr">
         <is>
-          <t>Marketing Agency</t>
+          <t>Logistics</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="B104" s="57" t="inlineStr">
         <is>
-          <t>Software Vendor</t>
+          <t>Marketing Agency</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="B105" s="57" t="inlineStr">
         <is>
+          <t>Software Vendor</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="57" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="16" customHeight="1">
-      <c r="B107" s="55" t="inlineStr">
+    <row r="108" ht="16" customHeight="1">
+      <c r="B108" s="55" t="inlineStr">
         <is>
           <t>Supplier Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="B108" s="57" t="inlineStr">
-        <is>
-          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="B109" s="57" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="B110" s="57" t="inlineStr">
         <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="57" t="inlineStr">
+        <is>
           <t>On Hold</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="16" customHeight="1">
-      <c r="B112" s="55" t="inlineStr">
+    <row r="113" ht="16" customHeight="1">
+      <c r="B113" s="55" t="inlineStr">
         <is>
           <t>Capital Transaction Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="B113" s="57" t="inlineStr">
-        <is>
-          <t>Capital Contribution</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="B114" s="57" t="inlineStr">
         <is>
+          <t>Capital Contribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="57" t="inlineStr">
+        <is>
           <t>Capital Withdrawal</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="16" customHeight="1">
-      <c r="B116" s="55" t="inlineStr">
+    <row r="117" ht="16" customHeight="1">
+      <c r="B117" s="55" t="inlineStr">
         <is>
           <t>PO Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="B117" s="57" t="inlineStr">
-        <is>
-          <t>Draft</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="B118" s="57" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Draft</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="B119" s="57" t="inlineStr">
         <is>
-          <t>Sent</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="B120" s="57" t="inlineStr">
         <is>
-          <t>Partially Received</t>
+          <t>Sent</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="B121" s="57" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Partially Received</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="B122" s="57" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Received</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="B123" s="57" t="inlineStr">
         <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="57" t="inlineStr">
+        <is>
           <t>Cancelled</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="16" customHeight="1">
-      <c r="B125" s="55" t="inlineStr">
+    <row r="126" ht="16" customHeight="1">
+      <c r="B126" s="55" t="inlineStr">
         <is>
           <t>Warehouse</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="B126" s="57" t="inlineStr">
-        <is>
-          <t>Main Warehouse</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="B127" s="57" t="inlineStr">
         <is>
-          <t>Retail Store</t>
+          <t>Main Warehouse</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="B128" s="57" t="inlineStr">
         <is>
+          <t>Retail Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" s="57" t="inlineStr">
+        <is>
           <t>Third-Party Logistics</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="16" customHeight="1">
-      <c r="B130" s="55" t="inlineStr">
+    <row r="131" ht="16" customHeight="1">
+      <c r="B131" s="55" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="B131" s="57" t="inlineStr">
+    <row r="132">
+      <c r="B132" s="57" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="16" customHeight="1">
-      <c r="B133" s="55" t="inlineStr">
+    <row r="134" ht="16" customHeight="1">
+      <c r="B134" s="55" t="inlineStr">
         <is>
           <t>Budget Period</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="B134" s="57" t="inlineStr">
-        <is>
-          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="B135" s="57" t="inlineStr">
         <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" s="57" t="inlineStr">
+        <is>
           <t>Yearly</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="16" customHeight="1">
-      <c r="B137" s="55" t="inlineStr">
+    <row r="138" ht="16" customHeight="1">
+      <c r="B138" s="55" t="inlineStr">
         <is>
           <t>Budget Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="B138" s="57" t="inlineStr">
-        <is>
-          <t>Revenue</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="B139" s="57" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Revenue</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="B140" s="57" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Expense</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="B141" s="57" t="inlineStr">
         <is>
-          <t>Purchasing</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="B142" s="57" t="inlineStr">
         <is>
+          <t>Purchasing</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" s="57" t="inlineStr">
+        <is>
           <t>Profit</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="16" customHeight="1">
-      <c r="B144" s="55" t="inlineStr">
+    <row r="145" ht="16" customHeight="1">
+      <c r="B145" s="55" t="inlineStr">
         <is>
           <t>Alert Severity</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="B145" s="57" t="inlineStr">
-        <is>
-          <t>Info</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="B146" s="57" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Info</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="B147" s="57" t="inlineStr">
         <is>
+          <t>Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" s="57" t="inlineStr">
+        <is>
           <t>Critical</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="B150" s="11" t="inlineStr">
+    <row r="151">
+      <c r="B151" s="11" t="inlineStr">
         <is>
           <t>KPI TARGETS  (green Target Value cells = type here)</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="18" customHeight="1">
-      <c r="B151" s="39" t="inlineStr">
+    <row r="152" ht="18" customHeight="1">
+      <c r="B152" s="39" t="inlineStr">
         <is>
           <t>KPI Name</t>
         </is>
       </c>
-      <c r="C151" s="39" t="inlineStr">
+      <c r="C152" s="39" t="inlineStr">
         <is>
           <t>Target Value</t>
         </is>
       </c>
-      <c r="D151" s="39" t="inlineStr">
+      <c r="D152" s="39" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="E151" s="39" t="inlineStr">
+      <c r="E152" s="39" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="F151" s="39" t="inlineStr">
+      <c r="F152" s="39" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="B152" s="30" t="inlineStr">
-        <is>
-          <t>Sales Target</t>
-        </is>
-      </c>
-      <c r="C152" s="58" t="n">
-        <v>500000</v>
-      </c>
-      <c r="D152" s="30" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-      <c r="E152" s="58" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-      <c r="F152" s="30" t="inlineStr">
-        <is>
-          <t>Net Sales target</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="B153" s="30" t="inlineStr">
         <is>
-          <t>Margin Target</t>
+          <t>Sales Target</t>
         </is>
       </c>
       <c r="C153" s="58" t="n">
-        <v>0.55</v>
+        <v>500000</v>
       </c>
       <c r="D153" s="30" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>EGP</t>
         </is>
       </c>
       <c r="E153" s="58" t="inlineStr">
@@ -8970,22 +8967,22 @@
       </c>
       <c r="F153" s="30" t="inlineStr">
         <is>
-          <t>Gross Margin % target</t>
+          <t>Net Sales target</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="B154" s="30" t="inlineStr">
         <is>
-          <t>Orders Target</t>
+          <t>Margin Target</t>
         </is>
       </c>
       <c r="C154" s="58" t="n">
-        <v>400</v>
+        <v>0.55</v>
       </c>
       <c r="D154" s="30" t="inlineStr">
         <is>
-          <t>Count</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E154" s="58" t="inlineStr">
@@ -8995,22 +8992,22 @@
       </c>
       <c r="F154" s="30" t="inlineStr">
         <is>
-          <t>Order Count target</t>
+          <t>Gross Margin % target</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="B155" s="30" t="inlineStr">
         <is>
-          <t>Inventory Target</t>
+          <t>Orders Target</t>
         </is>
       </c>
       <c r="C155" s="58" t="n">
-        <v>300000</v>
+        <v>400</v>
       </c>
       <c r="D155" s="30" t="inlineStr">
         <is>
-          <t>EGP</t>
+          <t>Count</t>
         </is>
       </c>
       <c r="E155" s="58" t="inlineStr">
@@ -9020,18 +9017,18 @@
       </c>
       <c r="F155" s="30" t="inlineStr">
         <is>
-          <t>Inventory Value ceiling (avoid overstock)</t>
+          <t>Order Count target</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="B156" s="30" t="inlineStr">
         <is>
-          <t>AOV Target</t>
+          <t>Inventory Target</t>
         </is>
       </c>
       <c r="C156" s="58" t="n">
-        <v>1200</v>
+        <v>300000</v>
       </c>
       <c r="D156" s="30" t="inlineStr">
         <is>
@@ -9045,18 +9042,18 @@
       </c>
       <c r="F156" s="30" t="inlineStr">
         <is>
-          <t>Average Order Value target</t>
+          <t>Inventory Value ceiling (avoid overstock)</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="B157" s="30" t="inlineStr">
         <is>
-          <t>CAC Target</t>
+          <t>AOV Target</t>
         </is>
       </c>
       <c r="C157" s="58" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="D157" s="30" t="inlineStr">
         <is>
@@ -9070,22 +9067,22 @@
       </c>
       <c r="F157" s="30" t="inlineStr">
         <is>
-          <t>Customer Acquisition Cost ceiling — needs Marketing-Ready spend data (Phase 6+) to compute Actual</t>
+          <t>Average Order Value target</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="B158" s="30" t="inlineStr">
         <is>
-          <t>ROAS Target</t>
+          <t>CAC Target</t>
         </is>
       </c>
       <c r="C158" s="58" t="n">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="D158" s="30" t="inlineStr">
         <is>
-          <t>Ratio</t>
+          <t>EGP</t>
         </is>
       </c>
       <c r="E158" s="58" t="inlineStr">
@@ -9095,22 +9092,22 @@
       </c>
       <c r="F158" s="30" t="inlineStr">
         <is>
-          <t>Return on Ad Spend target — needs Marketing-Ready spend data (Phase 6+) to compute Actual</t>
+          <t>Customer Acquisition Cost ceiling — needs Marketing-Ready spend data (Phase 6+) to compute Actual</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="B159" s="30" t="inlineStr">
         <is>
-          <t>Repeat Customer % Target</t>
+          <t>ROAS Target</t>
         </is>
       </c>
       <c r="C159" s="58" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="D159" s="30" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>Ratio</t>
         </is>
       </c>
       <c r="E159" s="58" t="inlineStr">
@@ -9120,18 +9117,18 @@
       </c>
       <c r="F159" s="30" t="inlineStr">
         <is>
-          <t>Returning Customers / Customers Active target</t>
+          <t>Return on Ad Spend target — needs Marketing-Ready spend data (Phase 6+) to compute Actual</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="B160" s="30" t="inlineStr">
         <is>
-          <t>Conversion Rate Target</t>
+          <t>Repeat Customer % Target</t>
         </is>
       </c>
       <c r="C160" s="58" t="n">
-        <v>0.02</v>
+        <v>0.3</v>
       </c>
       <c r="D160" s="30" t="inlineStr">
         <is>
@@ -9145,68 +9142,83 @@
       </c>
       <c r="F160" s="30" t="inlineStr">
         <is>
-          <t>Needs Shopify session/traffic data (not fetched — Admin API has no storefront analytics) to compute Actual</t>
+          <t>Returning Customers / Customers Active target</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="B161" s="30" t="inlineStr">
         <is>
+          <t>Conversion Rate Target</t>
+        </is>
+      </c>
+      <c r="C161" s="58" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D161" s="30" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E161" s="58" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="F161" s="30" t="inlineStr">
+        <is>
+          <t>Needs Shopify session/traffic data (not fetched — Admin API has no storefront analytics) to compute Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" s="30" t="inlineStr">
+        <is>
           <t>Inventory Turnover Target</t>
         </is>
       </c>
-      <c r="C161" s="58" t="n">
+      <c r="C162" s="58" t="n">
         <v>6</v>
       </c>
-      <c r="D161" s="30" t="inlineStr">
+      <c r="D162" s="30" t="inlineStr">
         <is>
           <t>Ratio</t>
         </is>
       </c>
-      <c r="E161" s="58" t="inlineStr">
+      <c r="E162" s="58" t="inlineStr">
         <is>
           <t>Yearly</t>
         </is>
       </c>
-      <c r="F161" s="30" t="inlineStr">
+      <c r="F162" s="30" t="inlineStr">
         <is>
           <t>COGS / Average Inventory Value target</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="B164" s="11" t="inlineStr">
+    <row r="165">
+      <c r="B165" s="11" t="inlineStr">
         <is>
           <t>BUSINESS HEALTH SCORE WEIGHTS  (green cells = type here — must be numeric, any scale)</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="18" customHeight="1">
-      <c r="B165" s="39" t="inlineStr">
+    <row r="166" ht="18" customHeight="1">
+      <c r="B166" s="39" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="C165" s="39" t="inlineStr">
+      <c r="C166" s="39" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="B166" s="30" t="inlineStr">
-        <is>
-          <t>Revenue Growth</t>
-        </is>
-      </c>
-      <c r="C166" s="58" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="167">
       <c r="B167" s="30" t="inlineStr">
         <is>
-          <t>Gross Margin</t>
+          <t>Revenue Growth</t>
         </is>
       </c>
       <c r="C167" s="58" t="n">
@@ -9216,7 +9228,7 @@
     <row r="168">
       <c r="B168" s="30" t="inlineStr">
         <is>
-          <t>Cash Position</t>
+          <t>Gross Margin</t>
         </is>
       </c>
       <c r="C168" s="58" t="n">
@@ -9226,17 +9238,17 @@
     <row r="169">
       <c r="B169" s="30" t="inlineStr">
         <is>
-          <t>Inventory Health</t>
+          <t>Cash Position</t>
         </is>
       </c>
       <c r="C169" s="58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="170">
       <c r="B170" s="30" t="inlineStr">
         <is>
-          <t>Customer Growth</t>
+          <t>Inventory Health</t>
         </is>
       </c>
       <c r="C170" s="58" t="n">
@@ -9246,7 +9258,7 @@
     <row r="171">
       <c r="B171" s="30" t="inlineStr">
         <is>
-          <t>Repeat Customers</t>
+          <t>Customer Growth</t>
         </is>
       </c>
       <c r="C171" s="58" t="n">
@@ -9256,7 +9268,7 @@
     <row r="172">
       <c r="B172" s="30" t="inlineStr">
         <is>
-          <t>Return Rate</t>
+          <t>Repeat Customers</t>
         </is>
       </c>
       <c r="C172" s="58" t="n">
@@ -9266,17 +9278,17 @@
     <row r="173">
       <c r="B173" s="30" t="inlineStr">
         <is>
-          <t>Budget Performance</t>
+          <t>Return Rate</t>
         </is>
       </c>
       <c r="C173" s="58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="174">
       <c r="B174" s="30" t="inlineStr">
         <is>
-          <t>Data Quality</t>
+          <t>Budget Performance</t>
         </is>
       </c>
       <c r="C174" s="58" t="n">
@@ -9286,35 +9298,45 @@
     <row r="175">
       <c r="B175" s="30" t="inlineStr">
         <is>
-          <t>Alerts</t>
+          <t>Data Quality</t>
         </is>
       </c>
       <c r="C175" s="58" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="178">
-      <c r="B178" s="11" t="inlineStr">
+    <row r="176">
+      <c r="B176" s="30" t="inlineStr">
+        <is>
+          <t>Alerts</t>
+        </is>
+      </c>
+      <c r="C176" s="58" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" s="11" t="inlineStr">
         <is>
           <t>HOLIDAYS  (green cells = type here — optional, empty by default)</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="18" customHeight="1">
-      <c r="B179" s="39" t="inlineStr">
+    <row r="180" ht="18" customHeight="1">
+      <c r="B180" s="39" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C179" s="39" t="inlineStr">
+      <c r="C180" s="39" t="inlineStr">
         <is>
           <t>Holiday Name</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="B180" s="40" t="n"/>
-      <c r="C180" s="40" t="inlineStr">
+    <row r="181">
+      <c r="B181" s="40" t="n"/>
+      <c r="C181" s="40" t="inlineStr">
         <is>
           <t>EXAMPLE — delete or overwrite this row; leave the table empty if no holidays apply</t>
         </is>
@@ -9333,7 +9355,7 @@
     <mergeCell ref="B6:D6"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="E152:E161" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the Period list — free text isn't accepted here." promptTitle="Period" prompt="Monthly or Yearly." type="list" errorStyle="stop">
+    <dataValidation sqref="E153:E162" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the Period list — free text isn't accepted here." promptTitle="Period" prompt="Monthly or Yearly." type="list" errorStyle="stop">
       <formula1>=LookupBudgetPeriod</formula1>
     </dataValidation>
   </dataValidations>
